--- a/public/templates/yctt_template.xlsx
+++ b/public/templates/yctt_template.xlsx
@@ -1,371 +1,178 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5bf7285fc3bfd881/Documents/THIEN NHAT/Hanoi Office/Mua hàng/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBCCF3E5-B915-8649-8B1C-EC5EC8B487D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" xr2:uid="{EA749819-DB55-490C-B101-06A76E086EA8}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="600" windowWidth="28160" windowHeight="15520" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$J$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Sheet1'!$A$1:$J$32</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{B1CFA6DC-3077-484B-A32A-571CCF914548}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="163"/>
-          </rPr>
-          <t>Author:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="163"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="163"/>
-          </rPr>
-          <t xml:space="preserve">Bấm vào đây để thay đổi số thứ tự in chứng từ
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="163"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t xml:space="preserve">                              PHIẾU ĐỀ NGHỊ THANH TOÁN</t>
-  </si>
-  <si>
-    <t>BM-03TH</t>
-  </si>
-  <si>
-    <t>Thanh toán</t>
-  </si>
-  <si>
-    <t>VND</t>
-  </si>
-  <si>
-    <t>Chuyển khoản</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Số chứng từ</t>
-  </si>
-  <si>
-    <t>Ngày chứng từ</t>
-  </si>
-  <si>
-    <t>Diễn giải</t>
-  </si>
-  <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>Đơn Giá</t>
-  </si>
-  <si>
-    <t>Thành Tiền</t>
-  </si>
-  <si>
-    <t>TỔNG CỘNG</t>
-  </si>
-  <si>
-    <t>Trừ tạm ứng hoặc trả trước</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhận  từ công ty </t>
-  </si>
-  <si>
-    <t>Tổng Giám Đốc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Kế toán trưởng</t>
-  </si>
-  <si>
-    <t>Cán bộ theo dõi</t>
-  </si>
-  <si>
-    <t>Người đề nghị</t>
-  </si>
-  <si>
-    <t xml:space="preserve">         ………………….</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Thuân</t>
-  </si>
-  <si>
-    <t>Lê Thị Kim Thanh</t>
-  </si>
-  <si>
-    <t>………………….</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG VÀ TM THIÊN NHẬT
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="18"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="163"/>
-      </rPr>
-      <t>Địa chỉ: Thôn Quán Trắng, xã Liên Sơn, tỉnh Phú Thọ</t>
-    </r>
-  </si>
-  <si>
-    <t>00000411</t>
-  </si>
-  <si>
-    <t>LÊ ANH HUY</t>
-  </si>
-  <si>
-    <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN THỦ ĐÔ</t>
-  </si>
-  <si>
-    <t>Ngân hàng Vietin Bank - Chi nhánh Thanh Xuân, Hà Nội</t>
-  </si>
-  <si>
-    <t>Nhập dầu cầu TITAN SuperGear 85W-140 (205l/phuy) - FUSCH</t>
-  </si>
-  <si>
-    <t>Nhập dầu thủy lực Renolin B68 Plus (205l/phuy) - FUSCH</t>
-  </si>
-  <si>
-    <t>Liên Sơn, ngày 21/05/2026</t>
-  </si>
-  <si>
-    <t>Lê Anh Huy</t>
-  </si>
-  <si>
-    <t>Kế hoạch-Vật tư</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
+      <name val="Times New Roman"/>
+      <charset val="163"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <charset val="163"/>
     </font>
     <font>
+      <name val="Times New Roman"/>
+      <charset val="163"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <charset val="163"/>
     </font>
     <font>
-      <b/>
+      <name val="Times New Roman"/>
+      <charset val="163"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color indexed="18"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="163"/>
+      <family val="1"/>
       <color indexed="18"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="163"/>
+      <b val="1"/>
+      <color indexed="18"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="18"/>
+      <name val="Times New Roman"/>
+      <charset val="163"/>
+      <family val="1"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="24"/>
+    </font>
+    <font>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="163"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="18"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <sz val="18"/>
     </font>
     <font>
-      <b/>
-      <sz val="24"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <charset val="163"/>
+      <sz val="22"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <sz val="20"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <sz val="22"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color indexed="12"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color indexed="61"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color indexed="12"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color indexed="61"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="61"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <b val="1"/>
+      <color indexed="12"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Tahoma"/>
+      <charset val="163"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="61"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Tahoma"/>
+      <charset val="163"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="163"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="163"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -394,8 +201,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -586,1882 +403,611 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="007F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="007F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="007F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="007F7F7F"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="148">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="AutoShape 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{921DDB8E-401A-40D9-A82D-5527B360A666}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="247650" y="3362325"/>
-          <a:ext cx="1390650" cy="161925"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFCC99"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="27432" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Tại Ngân hà</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>ng</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Text Box 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CB527F3-618E-4384-8139-7439CF612871}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5267325" y="8058150"/>
-          <a:ext cx="1285875" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Text Box 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06F52E9A-5335-4E0B-8E11-F1960303F593}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5267325" y="8058150"/>
-          <a:ext cx="5848350" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Text Box 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E213010F-07A9-4B36-9974-9B1C563D2617}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5267325" y="8058150"/>
-          <a:ext cx="5848350" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Text Box 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0601B10E-9106-4A83-BC4B-8E06EE00099A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5267325" y="8058150"/>
-          <a:ext cx="5810250" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Text Box 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0646C548-8993-4E43-83DF-E99BC8331A84}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2200275" y="8058150"/>
-          <a:ext cx="161925" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Text Box 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BB70A60-23BF-444A-9822-3BF0C360ADB7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1076325" y="8058150"/>
-          <a:ext cx="19050" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Text Box 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D818212-1985-4A30-AD2E-963E598D349E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1076325" y="8058150"/>
-          <a:ext cx="19050" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="Text Box 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5640808-F92F-4672-901C-C652B6181E4B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm rot="10800000">
-          <a:off x="1752600" y="8058150"/>
-          <a:ext cx="990600" cy="419100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>295276</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="AutoShape 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ADD92E1F-C44B-4A9C-975C-71224A767F1E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="295276" y="1314450"/>
-          <a:ext cx="1371599" cy="228599"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Yêu cầu bởi</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="AutoShape 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCBC3A10-286E-48C3-9681-989BEAB3AEC9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="257175" y="1704975"/>
-          <a:ext cx="1390650" cy="257175"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Bộ phận</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>257176</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="AutoShape 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{86479984-03BF-4596-B749-AD0A3BE23CC8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="257176" y="2143126"/>
-          <a:ext cx="1400174" cy="228600"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Loại tiền</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="AutoShape 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E3FEB2A-B3F8-42E1-9DAB-F51E94FC45EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3228975" y="1733550"/>
-          <a:ext cx="933450" cy="209550"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1050" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Mục đích</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>104775</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1028700</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="AutoShape 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7768560E-6E3A-4669-8FD1-65946446AE13}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3238500" y="2133600"/>
-          <a:ext cx="923925" cy="190500"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="CCFFFF"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="22860" rIns="36576" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Trả bằng</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>238127</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="AutoShape 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F81156C4-2304-4942-AB2E-8E3C900FBDB1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="238127" y="2524126"/>
-          <a:ext cx="1409699" cy="276224"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFCC99"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="27432" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Người hưởng</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>266701</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="AutoShape 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61CD4315-3A8D-4EA5-A8CB-112E42E02338}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr>
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="266701" y="2962276"/>
-          <a:ext cx="1381125" cy="171449"/>
-        </a:xfrm>
-        <a:prstGeom prst="flowChartAlternateProcess">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFCC99"/>
-        </a:solidFill>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-          <a:headEnd/>
-          <a:tailEnd/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="27432" bIns="22860" anchor="ctr" upright="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1000"/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="vi-VN" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:cs typeface="Arial"/>
-            </a:rPr>
-            <a:t>Tài khoản</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="Text Box 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76B121B3-E8C6-4E33-A240-6EB29DDAD9E9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5267325" y="8058150"/>
-          <a:ext cx="1285875" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="Text Box 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91DF8E60-1D6B-4DA1-98C3-36B726A463B8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5267325" y="8058150"/>
-          <a:ext cx="5905500" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="Text Box 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F67D8DB3-EA17-4FD7-95AA-FA14DB1C2E4C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5267325" y="8058150"/>
-          <a:ext cx="5905500" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>314325</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="Straight Connector 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12A3569F-B8EE-43E8-8BF8-27AECEBAD798}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2571750" y="4905375"/>
-          <a:ext cx="3009900" cy="771525"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Text Box 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE9B97ED-D18C-4AD8-B8D4-878F47D84865}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2200275" y="8058150"/>
-          <a:ext cx="161925" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="Text Box 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57A2DDA7-E563-448F-9894-A656ADA412E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1076325" y="8058150"/>
-          <a:ext cx="19050" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>742950</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="Text Box 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABC58178-1253-4C19-AD60-50830E58A3BC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1076325" y="8058150"/>
-          <a:ext cx="19050" cy="342900"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="Text Box 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BD54C8B-B9C1-4969-A110-34BF673B6D05}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1">
-          <a:spLocks noChangeArrowheads="1"/>
-        </xdr:cNvSpPr>
-      </xdr:nvSpPr>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm rot="10800000">
-          <a:off x="1752600" y="8058150"/>
-          <a:ext cx="990600" cy="419100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Author:
+Bấm vào đây để thay đổi số thứ tự in chứng từ
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="YCTT (2)"/>
@@ -12110,1430 +10656,1539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38EFE0C6-43E3-46DC-9C38-C8EA73E24CF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="5.5" style="4" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.1640625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="11" style="4" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="4" customWidth="1"/>
-    <col min="7" max="7" width="15.5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="5.6640625" style="5" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="0.5" style="4" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="8.33203125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="7.6640625" style="4" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="9.1640625" style="4"/>
-    <col min="14" max="14" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.83203125" style="4" customWidth="1"/>
-    <col min="16" max="17" width="9.1640625" style="4"/>
-    <col min="18" max="18" width="15.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="258" width="9.1640625" style="4"/>
-    <col min="259" max="259" width="5.5" style="4" customWidth="1"/>
-    <col min="260" max="260" width="16.5" style="4" customWidth="1"/>
-    <col min="261" max="261" width="11.5" style="4" customWidth="1"/>
-    <col min="262" max="262" width="12.5" style="4" customWidth="1"/>
-    <col min="263" max="263" width="19.33203125" style="4" customWidth="1"/>
-    <col min="264" max="264" width="16.5" style="4" customWidth="1"/>
-    <col min="265" max="266" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="267" max="267" width="15.5" style="4" customWidth="1"/>
-    <col min="268" max="269" width="9.1640625" style="4"/>
-    <col min="270" max="270" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="271" max="514" width="9.1640625" style="4"/>
-    <col min="515" max="515" width="5.5" style="4" customWidth="1"/>
-    <col min="516" max="516" width="16.5" style="4" customWidth="1"/>
-    <col min="517" max="517" width="11.5" style="4" customWidth="1"/>
-    <col min="518" max="518" width="12.5" style="4" customWidth="1"/>
-    <col min="519" max="519" width="19.33203125" style="4" customWidth="1"/>
-    <col min="520" max="520" width="16.5" style="4" customWidth="1"/>
-    <col min="521" max="522" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="523" max="523" width="15.5" style="4" customWidth="1"/>
-    <col min="524" max="525" width="9.1640625" style="4"/>
-    <col min="526" max="526" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="527" max="770" width="9.1640625" style="4"/>
-    <col min="771" max="771" width="5.5" style="4" customWidth="1"/>
-    <col min="772" max="772" width="16.5" style="4" customWidth="1"/>
-    <col min="773" max="773" width="11.5" style="4" customWidth="1"/>
-    <col min="774" max="774" width="12.5" style="4" customWidth="1"/>
-    <col min="775" max="775" width="19.33203125" style="4" customWidth="1"/>
-    <col min="776" max="776" width="16.5" style="4" customWidth="1"/>
-    <col min="777" max="778" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="779" max="779" width="15.5" style="4" customWidth="1"/>
-    <col min="780" max="781" width="9.1640625" style="4"/>
-    <col min="782" max="782" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="783" max="1026" width="9.1640625" style="4"/>
-    <col min="1027" max="1027" width="5.5" style="4" customWidth="1"/>
-    <col min="1028" max="1028" width="16.5" style="4" customWidth="1"/>
-    <col min="1029" max="1029" width="11.5" style="4" customWidth="1"/>
-    <col min="1030" max="1030" width="12.5" style="4" customWidth="1"/>
-    <col min="1031" max="1031" width="19.33203125" style="4" customWidth="1"/>
-    <col min="1032" max="1032" width="16.5" style="4" customWidth="1"/>
-    <col min="1033" max="1034" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1035" max="1035" width="15.5" style="4" customWidth="1"/>
-    <col min="1036" max="1037" width="9.1640625" style="4"/>
-    <col min="1038" max="1038" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="1039" max="1282" width="9.1640625" style="4"/>
-    <col min="1283" max="1283" width="5.5" style="4" customWidth="1"/>
-    <col min="1284" max="1284" width="16.5" style="4" customWidth="1"/>
-    <col min="1285" max="1285" width="11.5" style="4" customWidth="1"/>
-    <col min="1286" max="1286" width="12.5" style="4" customWidth="1"/>
-    <col min="1287" max="1287" width="19.33203125" style="4" customWidth="1"/>
-    <col min="1288" max="1288" width="16.5" style="4" customWidth="1"/>
-    <col min="1289" max="1290" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1291" max="1291" width="15.5" style="4" customWidth="1"/>
-    <col min="1292" max="1293" width="9.1640625" style="4"/>
-    <col min="1294" max="1294" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="1295" max="1538" width="9.1640625" style="4"/>
-    <col min="1539" max="1539" width="5.5" style="4" customWidth="1"/>
-    <col min="1540" max="1540" width="16.5" style="4" customWidth="1"/>
-    <col min="1541" max="1541" width="11.5" style="4" customWidth="1"/>
-    <col min="1542" max="1542" width="12.5" style="4" customWidth="1"/>
-    <col min="1543" max="1543" width="19.33203125" style="4" customWidth="1"/>
-    <col min="1544" max="1544" width="16.5" style="4" customWidth="1"/>
-    <col min="1545" max="1546" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1547" max="1547" width="15.5" style="4" customWidth="1"/>
-    <col min="1548" max="1549" width="9.1640625" style="4"/>
-    <col min="1550" max="1550" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="1551" max="1794" width="9.1640625" style="4"/>
-    <col min="1795" max="1795" width="5.5" style="4" customWidth="1"/>
-    <col min="1796" max="1796" width="16.5" style="4" customWidth="1"/>
-    <col min="1797" max="1797" width="11.5" style="4" customWidth="1"/>
-    <col min="1798" max="1798" width="12.5" style="4" customWidth="1"/>
-    <col min="1799" max="1799" width="19.33203125" style="4" customWidth="1"/>
-    <col min="1800" max="1800" width="16.5" style="4" customWidth="1"/>
-    <col min="1801" max="1802" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="1803" max="1803" width="15.5" style="4" customWidth="1"/>
-    <col min="1804" max="1805" width="9.1640625" style="4"/>
-    <col min="1806" max="1806" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="1807" max="2050" width="9.1640625" style="4"/>
-    <col min="2051" max="2051" width="5.5" style="4" customWidth="1"/>
-    <col min="2052" max="2052" width="16.5" style="4" customWidth="1"/>
-    <col min="2053" max="2053" width="11.5" style="4" customWidth="1"/>
-    <col min="2054" max="2054" width="12.5" style="4" customWidth="1"/>
-    <col min="2055" max="2055" width="19.33203125" style="4" customWidth="1"/>
-    <col min="2056" max="2056" width="16.5" style="4" customWidth="1"/>
-    <col min="2057" max="2058" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2059" max="2059" width="15.5" style="4" customWidth="1"/>
-    <col min="2060" max="2061" width="9.1640625" style="4"/>
-    <col min="2062" max="2062" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2063" max="2306" width="9.1640625" style="4"/>
-    <col min="2307" max="2307" width="5.5" style="4" customWidth="1"/>
-    <col min="2308" max="2308" width="16.5" style="4" customWidth="1"/>
-    <col min="2309" max="2309" width="11.5" style="4" customWidth="1"/>
-    <col min="2310" max="2310" width="12.5" style="4" customWidth="1"/>
-    <col min="2311" max="2311" width="19.33203125" style="4" customWidth="1"/>
-    <col min="2312" max="2312" width="16.5" style="4" customWidth="1"/>
-    <col min="2313" max="2314" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2315" max="2315" width="15.5" style="4" customWidth="1"/>
-    <col min="2316" max="2317" width="9.1640625" style="4"/>
-    <col min="2318" max="2318" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2319" max="2562" width="9.1640625" style="4"/>
-    <col min="2563" max="2563" width="5.5" style="4" customWidth="1"/>
-    <col min="2564" max="2564" width="16.5" style="4" customWidth="1"/>
-    <col min="2565" max="2565" width="11.5" style="4" customWidth="1"/>
-    <col min="2566" max="2566" width="12.5" style="4" customWidth="1"/>
-    <col min="2567" max="2567" width="19.33203125" style="4" customWidth="1"/>
-    <col min="2568" max="2568" width="16.5" style="4" customWidth="1"/>
-    <col min="2569" max="2570" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2571" max="2571" width="15.5" style="4" customWidth="1"/>
-    <col min="2572" max="2573" width="9.1640625" style="4"/>
-    <col min="2574" max="2574" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2575" max="2818" width="9.1640625" style="4"/>
-    <col min="2819" max="2819" width="5.5" style="4" customWidth="1"/>
-    <col min="2820" max="2820" width="16.5" style="4" customWidth="1"/>
-    <col min="2821" max="2821" width="11.5" style="4" customWidth="1"/>
-    <col min="2822" max="2822" width="12.5" style="4" customWidth="1"/>
-    <col min="2823" max="2823" width="19.33203125" style="4" customWidth="1"/>
-    <col min="2824" max="2824" width="16.5" style="4" customWidth="1"/>
-    <col min="2825" max="2826" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="2827" max="2827" width="15.5" style="4" customWidth="1"/>
-    <col min="2828" max="2829" width="9.1640625" style="4"/>
-    <col min="2830" max="2830" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2831" max="3074" width="9.1640625" style="4"/>
-    <col min="3075" max="3075" width="5.5" style="4" customWidth="1"/>
-    <col min="3076" max="3076" width="16.5" style="4" customWidth="1"/>
-    <col min="3077" max="3077" width="11.5" style="4" customWidth="1"/>
-    <col min="3078" max="3078" width="12.5" style="4" customWidth="1"/>
-    <col min="3079" max="3079" width="19.33203125" style="4" customWidth="1"/>
-    <col min="3080" max="3080" width="16.5" style="4" customWidth="1"/>
-    <col min="3081" max="3082" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3083" max="3083" width="15.5" style="4" customWidth="1"/>
-    <col min="3084" max="3085" width="9.1640625" style="4"/>
-    <col min="3086" max="3086" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3087" max="3330" width="9.1640625" style="4"/>
-    <col min="3331" max="3331" width="5.5" style="4" customWidth="1"/>
-    <col min="3332" max="3332" width="16.5" style="4" customWidth="1"/>
-    <col min="3333" max="3333" width="11.5" style="4" customWidth="1"/>
-    <col min="3334" max="3334" width="12.5" style="4" customWidth="1"/>
-    <col min="3335" max="3335" width="19.33203125" style="4" customWidth="1"/>
-    <col min="3336" max="3336" width="16.5" style="4" customWidth="1"/>
-    <col min="3337" max="3338" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3339" max="3339" width="15.5" style="4" customWidth="1"/>
-    <col min="3340" max="3341" width="9.1640625" style="4"/>
-    <col min="3342" max="3342" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3343" max="3586" width="9.1640625" style="4"/>
-    <col min="3587" max="3587" width="5.5" style="4" customWidth="1"/>
-    <col min="3588" max="3588" width="16.5" style="4" customWidth="1"/>
-    <col min="3589" max="3589" width="11.5" style="4" customWidth="1"/>
-    <col min="3590" max="3590" width="12.5" style="4" customWidth="1"/>
-    <col min="3591" max="3591" width="19.33203125" style="4" customWidth="1"/>
-    <col min="3592" max="3592" width="16.5" style="4" customWidth="1"/>
-    <col min="3593" max="3594" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3595" max="3595" width="15.5" style="4" customWidth="1"/>
-    <col min="3596" max="3597" width="9.1640625" style="4"/>
-    <col min="3598" max="3598" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3599" max="3842" width="9.1640625" style="4"/>
-    <col min="3843" max="3843" width="5.5" style="4" customWidth="1"/>
-    <col min="3844" max="3844" width="16.5" style="4" customWidth="1"/>
-    <col min="3845" max="3845" width="11.5" style="4" customWidth="1"/>
-    <col min="3846" max="3846" width="12.5" style="4" customWidth="1"/>
-    <col min="3847" max="3847" width="19.33203125" style="4" customWidth="1"/>
-    <col min="3848" max="3848" width="16.5" style="4" customWidth="1"/>
-    <col min="3849" max="3850" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="3851" max="3851" width="15.5" style="4" customWidth="1"/>
-    <col min="3852" max="3853" width="9.1640625" style="4"/>
-    <col min="3854" max="3854" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3855" max="4098" width="9.1640625" style="4"/>
-    <col min="4099" max="4099" width="5.5" style="4" customWidth="1"/>
-    <col min="4100" max="4100" width="16.5" style="4" customWidth="1"/>
-    <col min="4101" max="4101" width="11.5" style="4" customWidth="1"/>
-    <col min="4102" max="4102" width="12.5" style="4" customWidth="1"/>
-    <col min="4103" max="4103" width="19.33203125" style="4" customWidth="1"/>
-    <col min="4104" max="4104" width="16.5" style="4" customWidth="1"/>
-    <col min="4105" max="4106" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4107" max="4107" width="15.5" style="4" customWidth="1"/>
-    <col min="4108" max="4109" width="9.1640625" style="4"/>
-    <col min="4110" max="4110" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4111" max="4354" width="9.1640625" style="4"/>
-    <col min="4355" max="4355" width="5.5" style="4" customWidth="1"/>
-    <col min="4356" max="4356" width="16.5" style="4" customWidth="1"/>
-    <col min="4357" max="4357" width="11.5" style="4" customWidth="1"/>
-    <col min="4358" max="4358" width="12.5" style="4" customWidth="1"/>
-    <col min="4359" max="4359" width="19.33203125" style="4" customWidth="1"/>
-    <col min="4360" max="4360" width="16.5" style="4" customWidth="1"/>
-    <col min="4361" max="4362" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4363" max="4363" width="15.5" style="4" customWidth="1"/>
-    <col min="4364" max="4365" width="9.1640625" style="4"/>
-    <col min="4366" max="4366" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4367" max="4610" width="9.1640625" style="4"/>
-    <col min="4611" max="4611" width="5.5" style="4" customWidth="1"/>
-    <col min="4612" max="4612" width="16.5" style="4" customWidth="1"/>
-    <col min="4613" max="4613" width="11.5" style="4" customWidth="1"/>
-    <col min="4614" max="4614" width="12.5" style="4" customWidth="1"/>
-    <col min="4615" max="4615" width="19.33203125" style="4" customWidth="1"/>
-    <col min="4616" max="4616" width="16.5" style="4" customWidth="1"/>
-    <col min="4617" max="4618" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4619" max="4619" width="15.5" style="4" customWidth="1"/>
-    <col min="4620" max="4621" width="9.1640625" style="4"/>
-    <col min="4622" max="4622" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4623" max="4866" width="9.1640625" style="4"/>
-    <col min="4867" max="4867" width="5.5" style="4" customWidth="1"/>
-    <col min="4868" max="4868" width="16.5" style="4" customWidth="1"/>
-    <col min="4869" max="4869" width="11.5" style="4" customWidth="1"/>
-    <col min="4870" max="4870" width="12.5" style="4" customWidth="1"/>
-    <col min="4871" max="4871" width="19.33203125" style="4" customWidth="1"/>
-    <col min="4872" max="4872" width="16.5" style="4" customWidth="1"/>
-    <col min="4873" max="4874" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="4875" max="4875" width="15.5" style="4" customWidth="1"/>
-    <col min="4876" max="4877" width="9.1640625" style="4"/>
-    <col min="4878" max="4878" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4879" max="5122" width="9.1640625" style="4"/>
-    <col min="5123" max="5123" width="5.5" style="4" customWidth="1"/>
-    <col min="5124" max="5124" width="16.5" style="4" customWidth="1"/>
-    <col min="5125" max="5125" width="11.5" style="4" customWidth="1"/>
-    <col min="5126" max="5126" width="12.5" style="4" customWidth="1"/>
-    <col min="5127" max="5127" width="19.33203125" style="4" customWidth="1"/>
-    <col min="5128" max="5128" width="16.5" style="4" customWidth="1"/>
-    <col min="5129" max="5130" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5131" max="5131" width="15.5" style="4" customWidth="1"/>
-    <col min="5132" max="5133" width="9.1640625" style="4"/>
-    <col min="5134" max="5134" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5135" max="5378" width="9.1640625" style="4"/>
-    <col min="5379" max="5379" width="5.5" style="4" customWidth="1"/>
-    <col min="5380" max="5380" width="16.5" style="4" customWidth="1"/>
-    <col min="5381" max="5381" width="11.5" style="4" customWidth="1"/>
-    <col min="5382" max="5382" width="12.5" style="4" customWidth="1"/>
-    <col min="5383" max="5383" width="19.33203125" style="4" customWidth="1"/>
-    <col min="5384" max="5384" width="16.5" style="4" customWidth="1"/>
-    <col min="5385" max="5386" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5387" max="5387" width="15.5" style="4" customWidth="1"/>
-    <col min="5388" max="5389" width="9.1640625" style="4"/>
-    <col min="5390" max="5390" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5391" max="5634" width="9.1640625" style="4"/>
-    <col min="5635" max="5635" width="5.5" style="4" customWidth="1"/>
-    <col min="5636" max="5636" width="16.5" style="4" customWidth="1"/>
-    <col min="5637" max="5637" width="11.5" style="4" customWidth="1"/>
-    <col min="5638" max="5638" width="12.5" style="4" customWidth="1"/>
-    <col min="5639" max="5639" width="19.33203125" style="4" customWidth="1"/>
-    <col min="5640" max="5640" width="16.5" style="4" customWidth="1"/>
-    <col min="5641" max="5642" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5643" max="5643" width="15.5" style="4" customWidth="1"/>
-    <col min="5644" max="5645" width="9.1640625" style="4"/>
-    <col min="5646" max="5646" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5647" max="5890" width="9.1640625" style="4"/>
-    <col min="5891" max="5891" width="5.5" style="4" customWidth="1"/>
-    <col min="5892" max="5892" width="16.5" style="4" customWidth="1"/>
-    <col min="5893" max="5893" width="11.5" style="4" customWidth="1"/>
-    <col min="5894" max="5894" width="12.5" style="4" customWidth="1"/>
-    <col min="5895" max="5895" width="19.33203125" style="4" customWidth="1"/>
-    <col min="5896" max="5896" width="16.5" style="4" customWidth="1"/>
-    <col min="5897" max="5898" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="5899" max="5899" width="15.5" style="4" customWidth="1"/>
-    <col min="5900" max="5901" width="9.1640625" style="4"/>
-    <col min="5902" max="5902" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5903" max="6146" width="9.1640625" style="4"/>
-    <col min="6147" max="6147" width="5.5" style="4" customWidth="1"/>
-    <col min="6148" max="6148" width="16.5" style="4" customWidth="1"/>
-    <col min="6149" max="6149" width="11.5" style="4" customWidth="1"/>
-    <col min="6150" max="6150" width="12.5" style="4" customWidth="1"/>
-    <col min="6151" max="6151" width="19.33203125" style="4" customWidth="1"/>
-    <col min="6152" max="6152" width="16.5" style="4" customWidth="1"/>
-    <col min="6153" max="6154" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6155" max="6155" width="15.5" style="4" customWidth="1"/>
-    <col min="6156" max="6157" width="9.1640625" style="4"/>
-    <col min="6158" max="6158" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6159" max="6402" width="9.1640625" style="4"/>
-    <col min="6403" max="6403" width="5.5" style="4" customWidth="1"/>
-    <col min="6404" max="6404" width="16.5" style="4" customWidth="1"/>
-    <col min="6405" max="6405" width="11.5" style="4" customWidth="1"/>
-    <col min="6406" max="6406" width="12.5" style="4" customWidth="1"/>
-    <col min="6407" max="6407" width="19.33203125" style="4" customWidth="1"/>
-    <col min="6408" max="6408" width="16.5" style="4" customWidth="1"/>
-    <col min="6409" max="6410" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6411" max="6411" width="15.5" style="4" customWidth="1"/>
-    <col min="6412" max="6413" width="9.1640625" style="4"/>
-    <col min="6414" max="6414" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6415" max="6658" width="9.1640625" style="4"/>
-    <col min="6659" max="6659" width="5.5" style="4" customWidth="1"/>
-    <col min="6660" max="6660" width="16.5" style="4" customWidth="1"/>
-    <col min="6661" max="6661" width="11.5" style="4" customWidth="1"/>
-    <col min="6662" max="6662" width="12.5" style="4" customWidth="1"/>
-    <col min="6663" max="6663" width="19.33203125" style="4" customWidth="1"/>
-    <col min="6664" max="6664" width="16.5" style="4" customWidth="1"/>
-    <col min="6665" max="6666" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6667" max="6667" width="15.5" style="4" customWidth="1"/>
-    <col min="6668" max="6669" width="9.1640625" style="4"/>
-    <col min="6670" max="6670" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6671" max="6914" width="9.1640625" style="4"/>
-    <col min="6915" max="6915" width="5.5" style="4" customWidth="1"/>
-    <col min="6916" max="6916" width="16.5" style="4" customWidth="1"/>
-    <col min="6917" max="6917" width="11.5" style="4" customWidth="1"/>
-    <col min="6918" max="6918" width="12.5" style="4" customWidth="1"/>
-    <col min="6919" max="6919" width="19.33203125" style="4" customWidth="1"/>
-    <col min="6920" max="6920" width="16.5" style="4" customWidth="1"/>
-    <col min="6921" max="6922" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="6923" max="6923" width="15.5" style="4" customWidth="1"/>
-    <col min="6924" max="6925" width="9.1640625" style="4"/>
-    <col min="6926" max="6926" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="6927" max="7170" width="9.1640625" style="4"/>
-    <col min="7171" max="7171" width="5.5" style="4" customWidth="1"/>
-    <col min="7172" max="7172" width="16.5" style="4" customWidth="1"/>
-    <col min="7173" max="7173" width="11.5" style="4" customWidth="1"/>
-    <col min="7174" max="7174" width="12.5" style="4" customWidth="1"/>
-    <col min="7175" max="7175" width="19.33203125" style="4" customWidth="1"/>
-    <col min="7176" max="7176" width="16.5" style="4" customWidth="1"/>
-    <col min="7177" max="7178" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7179" max="7179" width="15.5" style="4" customWidth="1"/>
-    <col min="7180" max="7181" width="9.1640625" style="4"/>
-    <col min="7182" max="7182" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7183" max="7426" width="9.1640625" style="4"/>
-    <col min="7427" max="7427" width="5.5" style="4" customWidth="1"/>
-    <col min="7428" max="7428" width="16.5" style="4" customWidth="1"/>
-    <col min="7429" max="7429" width="11.5" style="4" customWidth="1"/>
-    <col min="7430" max="7430" width="12.5" style="4" customWidth="1"/>
-    <col min="7431" max="7431" width="19.33203125" style="4" customWidth="1"/>
-    <col min="7432" max="7432" width="16.5" style="4" customWidth="1"/>
-    <col min="7433" max="7434" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7435" max="7435" width="15.5" style="4" customWidth="1"/>
-    <col min="7436" max="7437" width="9.1640625" style="4"/>
-    <col min="7438" max="7438" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7439" max="7682" width="9.1640625" style="4"/>
-    <col min="7683" max="7683" width="5.5" style="4" customWidth="1"/>
-    <col min="7684" max="7684" width="16.5" style="4" customWidth="1"/>
-    <col min="7685" max="7685" width="11.5" style="4" customWidth="1"/>
-    <col min="7686" max="7686" width="12.5" style="4" customWidth="1"/>
-    <col min="7687" max="7687" width="19.33203125" style="4" customWidth="1"/>
-    <col min="7688" max="7688" width="16.5" style="4" customWidth="1"/>
-    <col min="7689" max="7690" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7691" max="7691" width="15.5" style="4" customWidth="1"/>
-    <col min="7692" max="7693" width="9.1640625" style="4"/>
-    <col min="7694" max="7694" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7695" max="7938" width="9.1640625" style="4"/>
-    <col min="7939" max="7939" width="5.5" style="4" customWidth="1"/>
-    <col min="7940" max="7940" width="16.5" style="4" customWidth="1"/>
-    <col min="7941" max="7941" width="11.5" style="4" customWidth="1"/>
-    <col min="7942" max="7942" width="12.5" style="4" customWidth="1"/>
-    <col min="7943" max="7943" width="19.33203125" style="4" customWidth="1"/>
-    <col min="7944" max="7944" width="16.5" style="4" customWidth="1"/>
-    <col min="7945" max="7946" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="7947" max="7947" width="15.5" style="4" customWidth="1"/>
-    <col min="7948" max="7949" width="9.1640625" style="4"/>
-    <col min="7950" max="7950" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7951" max="8194" width="9.1640625" style="4"/>
-    <col min="8195" max="8195" width="5.5" style="4" customWidth="1"/>
-    <col min="8196" max="8196" width="16.5" style="4" customWidth="1"/>
-    <col min="8197" max="8197" width="11.5" style="4" customWidth="1"/>
-    <col min="8198" max="8198" width="12.5" style="4" customWidth="1"/>
-    <col min="8199" max="8199" width="19.33203125" style="4" customWidth="1"/>
-    <col min="8200" max="8200" width="16.5" style="4" customWidth="1"/>
-    <col min="8201" max="8202" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8203" max="8203" width="15.5" style="4" customWidth="1"/>
-    <col min="8204" max="8205" width="9.1640625" style="4"/>
-    <col min="8206" max="8206" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8207" max="8450" width="9.1640625" style="4"/>
-    <col min="8451" max="8451" width="5.5" style="4" customWidth="1"/>
-    <col min="8452" max="8452" width="16.5" style="4" customWidth="1"/>
-    <col min="8453" max="8453" width="11.5" style="4" customWidth="1"/>
-    <col min="8454" max="8454" width="12.5" style="4" customWidth="1"/>
-    <col min="8455" max="8455" width="19.33203125" style="4" customWidth="1"/>
-    <col min="8456" max="8456" width="16.5" style="4" customWidth="1"/>
-    <col min="8457" max="8458" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8459" max="8459" width="15.5" style="4" customWidth="1"/>
-    <col min="8460" max="8461" width="9.1640625" style="4"/>
-    <col min="8462" max="8462" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8463" max="8706" width="9.1640625" style="4"/>
-    <col min="8707" max="8707" width="5.5" style="4" customWidth="1"/>
-    <col min="8708" max="8708" width="16.5" style="4" customWidth="1"/>
-    <col min="8709" max="8709" width="11.5" style="4" customWidth="1"/>
-    <col min="8710" max="8710" width="12.5" style="4" customWidth="1"/>
-    <col min="8711" max="8711" width="19.33203125" style="4" customWidth="1"/>
-    <col min="8712" max="8712" width="16.5" style="4" customWidth="1"/>
-    <col min="8713" max="8714" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8715" max="8715" width="15.5" style="4" customWidth="1"/>
-    <col min="8716" max="8717" width="9.1640625" style="4"/>
-    <col min="8718" max="8718" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8719" max="8962" width="9.1640625" style="4"/>
-    <col min="8963" max="8963" width="5.5" style="4" customWidth="1"/>
-    <col min="8964" max="8964" width="16.5" style="4" customWidth="1"/>
-    <col min="8965" max="8965" width="11.5" style="4" customWidth="1"/>
-    <col min="8966" max="8966" width="12.5" style="4" customWidth="1"/>
-    <col min="8967" max="8967" width="19.33203125" style="4" customWidth="1"/>
-    <col min="8968" max="8968" width="16.5" style="4" customWidth="1"/>
-    <col min="8969" max="8970" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="8971" max="8971" width="15.5" style="4" customWidth="1"/>
-    <col min="8972" max="8973" width="9.1640625" style="4"/>
-    <col min="8974" max="8974" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8975" max="9218" width="9.1640625" style="4"/>
-    <col min="9219" max="9219" width="5.5" style="4" customWidth="1"/>
-    <col min="9220" max="9220" width="16.5" style="4" customWidth="1"/>
-    <col min="9221" max="9221" width="11.5" style="4" customWidth="1"/>
-    <col min="9222" max="9222" width="12.5" style="4" customWidth="1"/>
-    <col min="9223" max="9223" width="19.33203125" style="4" customWidth="1"/>
-    <col min="9224" max="9224" width="16.5" style="4" customWidth="1"/>
-    <col min="9225" max="9226" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9227" max="9227" width="15.5" style="4" customWidth="1"/>
-    <col min="9228" max="9229" width="9.1640625" style="4"/>
-    <col min="9230" max="9230" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9231" max="9474" width="9.1640625" style="4"/>
-    <col min="9475" max="9475" width="5.5" style="4" customWidth="1"/>
-    <col min="9476" max="9476" width="16.5" style="4" customWidth="1"/>
-    <col min="9477" max="9477" width="11.5" style="4" customWidth="1"/>
-    <col min="9478" max="9478" width="12.5" style="4" customWidth="1"/>
-    <col min="9479" max="9479" width="19.33203125" style="4" customWidth="1"/>
-    <col min="9480" max="9480" width="16.5" style="4" customWidth="1"/>
-    <col min="9481" max="9482" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9483" max="9483" width="15.5" style="4" customWidth="1"/>
-    <col min="9484" max="9485" width="9.1640625" style="4"/>
-    <col min="9486" max="9486" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9487" max="9730" width="9.1640625" style="4"/>
-    <col min="9731" max="9731" width="5.5" style="4" customWidth="1"/>
-    <col min="9732" max="9732" width="16.5" style="4" customWidth="1"/>
-    <col min="9733" max="9733" width="11.5" style="4" customWidth="1"/>
-    <col min="9734" max="9734" width="12.5" style="4" customWidth="1"/>
-    <col min="9735" max="9735" width="19.33203125" style="4" customWidth="1"/>
-    <col min="9736" max="9736" width="16.5" style="4" customWidth="1"/>
-    <col min="9737" max="9738" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9739" max="9739" width="15.5" style="4" customWidth="1"/>
-    <col min="9740" max="9741" width="9.1640625" style="4"/>
-    <col min="9742" max="9742" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9743" max="9986" width="9.1640625" style="4"/>
-    <col min="9987" max="9987" width="5.5" style="4" customWidth="1"/>
-    <col min="9988" max="9988" width="16.5" style="4" customWidth="1"/>
-    <col min="9989" max="9989" width="11.5" style="4" customWidth="1"/>
-    <col min="9990" max="9990" width="12.5" style="4" customWidth="1"/>
-    <col min="9991" max="9991" width="19.33203125" style="4" customWidth="1"/>
-    <col min="9992" max="9992" width="16.5" style="4" customWidth="1"/>
-    <col min="9993" max="9994" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="9995" max="9995" width="15.5" style="4" customWidth="1"/>
-    <col min="9996" max="9997" width="9.1640625" style="4"/>
-    <col min="9998" max="9998" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9999" max="10242" width="9.1640625" style="4"/>
-    <col min="10243" max="10243" width="5.5" style="4" customWidth="1"/>
-    <col min="10244" max="10244" width="16.5" style="4" customWidth="1"/>
-    <col min="10245" max="10245" width="11.5" style="4" customWidth="1"/>
-    <col min="10246" max="10246" width="12.5" style="4" customWidth="1"/>
-    <col min="10247" max="10247" width="19.33203125" style="4" customWidth="1"/>
-    <col min="10248" max="10248" width="16.5" style="4" customWidth="1"/>
-    <col min="10249" max="10250" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10251" max="10251" width="15.5" style="4" customWidth="1"/>
-    <col min="10252" max="10253" width="9.1640625" style="4"/>
-    <col min="10254" max="10254" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10255" max="10498" width="9.1640625" style="4"/>
-    <col min="10499" max="10499" width="5.5" style="4" customWidth="1"/>
-    <col min="10500" max="10500" width="16.5" style="4" customWidth="1"/>
-    <col min="10501" max="10501" width="11.5" style="4" customWidth="1"/>
-    <col min="10502" max="10502" width="12.5" style="4" customWidth="1"/>
-    <col min="10503" max="10503" width="19.33203125" style="4" customWidth="1"/>
-    <col min="10504" max="10504" width="16.5" style="4" customWidth="1"/>
-    <col min="10505" max="10506" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10507" max="10507" width="15.5" style="4" customWidth="1"/>
-    <col min="10508" max="10509" width="9.1640625" style="4"/>
-    <col min="10510" max="10510" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10511" max="10754" width="9.1640625" style="4"/>
-    <col min="10755" max="10755" width="5.5" style="4" customWidth="1"/>
-    <col min="10756" max="10756" width="16.5" style="4" customWidth="1"/>
-    <col min="10757" max="10757" width="11.5" style="4" customWidth="1"/>
-    <col min="10758" max="10758" width="12.5" style="4" customWidth="1"/>
-    <col min="10759" max="10759" width="19.33203125" style="4" customWidth="1"/>
-    <col min="10760" max="10760" width="16.5" style="4" customWidth="1"/>
-    <col min="10761" max="10762" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="10763" max="10763" width="15.5" style="4" customWidth="1"/>
-    <col min="10764" max="10765" width="9.1640625" style="4"/>
-    <col min="10766" max="10766" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10767" max="11010" width="9.1640625" style="4"/>
-    <col min="11011" max="11011" width="5.5" style="4" customWidth="1"/>
-    <col min="11012" max="11012" width="16.5" style="4" customWidth="1"/>
-    <col min="11013" max="11013" width="11.5" style="4" customWidth="1"/>
-    <col min="11014" max="11014" width="12.5" style="4" customWidth="1"/>
-    <col min="11015" max="11015" width="19.33203125" style="4" customWidth="1"/>
-    <col min="11016" max="11016" width="16.5" style="4" customWidth="1"/>
-    <col min="11017" max="11018" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11019" max="11019" width="15.5" style="4" customWidth="1"/>
-    <col min="11020" max="11021" width="9.1640625" style="4"/>
-    <col min="11022" max="11022" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11023" max="11266" width="9.1640625" style="4"/>
-    <col min="11267" max="11267" width="5.5" style="4" customWidth="1"/>
-    <col min="11268" max="11268" width="16.5" style="4" customWidth="1"/>
-    <col min="11269" max="11269" width="11.5" style="4" customWidth="1"/>
-    <col min="11270" max="11270" width="12.5" style="4" customWidth="1"/>
-    <col min="11271" max="11271" width="19.33203125" style="4" customWidth="1"/>
-    <col min="11272" max="11272" width="16.5" style="4" customWidth="1"/>
-    <col min="11273" max="11274" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11275" max="11275" width="15.5" style="4" customWidth="1"/>
-    <col min="11276" max="11277" width="9.1640625" style="4"/>
-    <col min="11278" max="11278" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11279" max="11522" width="9.1640625" style="4"/>
-    <col min="11523" max="11523" width="5.5" style="4" customWidth="1"/>
-    <col min="11524" max="11524" width="16.5" style="4" customWidth="1"/>
-    <col min="11525" max="11525" width="11.5" style="4" customWidth="1"/>
-    <col min="11526" max="11526" width="12.5" style="4" customWidth="1"/>
-    <col min="11527" max="11527" width="19.33203125" style="4" customWidth="1"/>
-    <col min="11528" max="11528" width="16.5" style="4" customWidth="1"/>
-    <col min="11529" max="11530" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11531" max="11531" width="15.5" style="4" customWidth="1"/>
-    <col min="11532" max="11533" width="9.1640625" style="4"/>
-    <col min="11534" max="11534" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11535" max="11778" width="9.1640625" style="4"/>
-    <col min="11779" max="11779" width="5.5" style="4" customWidth="1"/>
-    <col min="11780" max="11780" width="16.5" style="4" customWidth="1"/>
-    <col min="11781" max="11781" width="11.5" style="4" customWidth="1"/>
-    <col min="11782" max="11782" width="12.5" style="4" customWidth="1"/>
-    <col min="11783" max="11783" width="19.33203125" style="4" customWidth="1"/>
-    <col min="11784" max="11784" width="16.5" style="4" customWidth="1"/>
-    <col min="11785" max="11786" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="11787" max="11787" width="15.5" style="4" customWidth="1"/>
-    <col min="11788" max="11789" width="9.1640625" style="4"/>
-    <col min="11790" max="11790" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="11791" max="12034" width="9.1640625" style="4"/>
-    <col min="12035" max="12035" width="5.5" style="4" customWidth="1"/>
-    <col min="12036" max="12036" width="16.5" style="4" customWidth="1"/>
-    <col min="12037" max="12037" width="11.5" style="4" customWidth="1"/>
-    <col min="12038" max="12038" width="12.5" style="4" customWidth="1"/>
-    <col min="12039" max="12039" width="19.33203125" style="4" customWidth="1"/>
-    <col min="12040" max="12040" width="16.5" style="4" customWidth="1"/>
-    <col min="12041" max="12042" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12043" max="12043" width="15.5" style="4" customWidth="1"/>
-    <col min="12044" max="12045" width="9.1640625" style="4"/>
-    <col min="12046" max="12046" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12047" max="12290" width="9.1640625" style="4"/>
-    <col min="12291" max="12291" width="5.5" style="4" customWidth="1"/>
-    <col min="12292" max="12292" width="16.5" style="4" customWidth="1"/>
-    <col min="12293" max="12293" width="11.5" style="4" customWidth="1"/>
-    <col min="12294" max="12294" width="12.5" style="4" customWidth="1"/>
-    <col min="12295" max="12295" width="19.33203125" style="4" customWidth="1"/>
-    <col min="12296" max="12296" width="16.5" style="4" customWidth="1"/>
-    <col min="12297" max="12298" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12299" max="12299" width="15.5" style="4" customWidth="1"/>
-    <col min="12300" max="12301" width="9.1640625" style="4"/>
-    <col min="12302" max="12302" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12303" max="12546" width="9.1640625" style="4"/>
-    <col min="12547" max="12547" width="5.5" style="4" customWidth="1"/>
-    <col min="12548" max="12548" width="16.5" style="4" customWidth="1"/>
-    <col min="12549" max="12549" width="11.5" style="4" customWidth="1"/>
-    <col min="12550" max="12550" width="12.5" style="4" customWidth="1"/>
-    <col min="12551" max="12551" width="19.33203125" style="4" customWidth="1"/>
-    <col min="12552" max="12552" width="16.5" style="4" customWidth="1"/>
-    <col min="12553" max="12554" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12555" max="12555" width="15.5" style="4" customWidth="1"/>
-    <col min="12556" max="12557" width="9.1640625" style="4"/>
-    <col min="12558" max="12558" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12559" max="12802" width="9.1640625" style="4"/>
-    <col min="12803" max="12803" width="5.5" style="4" customWidth="1"/>
-    <col min="12804" max="12804" width="16.5" style="4" customWidth="1"/>
-    <col min="12805" max="12805" width="11.5" style="4" customWidth="1"/>
-    <col min="12806" max="12806" width="12.5" style="4" customWidth="1"/>
-    <col min="12807" max="12807" width="19.33203125" style="4" customWidth="1"/>
-    <col min="12808" max="12808" width="16.5" style="4" customWidth="1"/>
-    <col min="12809" max="12810" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="12811" max="12811" width="15.5" style="4" customWidth="1"/>
-    <col min="12812" max="12813" width="9.1640625" style="4"/>
-    <col min="12814" max="12814" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12815" max="13058" width="9.1640625" style="4"/>
-    <col min="13059" max="13059" width="5.5" style="4" customWidth="1"/>
-    <col min="13060" max="13060" width="16.5" style="4" customWidth="1"/>
-    <col min="13061" max="13061" width="11.5" style="4" customWidth="1"/>
-    <col min="13062" max="13062" width="12.5" style="4" customWidth="1"/>
-    <col min="13063" max="13063" width="19.33203125" style="4" customWidth="1"/>
-    <col min="13064" max="13064" width="16.5" style="4" customWidth="1"/>
-    <col min="13065" max="13066" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13067" max="13067" width="15.5" style="4" customWidth="1"/>
-    <col min="13068" max="13069" width="9.1640625" style="4"/>
-    <col min="13070" max="13070" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13071" max="13314" width="9.1640625" style="4"/>
-    <col min="13315" max="13315" width="5.5" style="4" customWidth="1"/>
-    <col min="13316" max="13316" width="16.5" style="4" customWidth="1"/>
-    <col min="13317" max="13317" width="11.5" style="4" customWidth="1"/>
-    <col min="13318" max="13318" width="12.5" style="4" customWidth="1"/>
-    <col min="13319" max="13319" width="19.33203125" style="4" customWidth="1"/>
-    <col min="13320" max="13320" width="16.5" style="4" customWidth="1"/>
-    <col min="13321" max="13322" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13323" max="13323" width="15.5" style="4" customWidth="1"/>
-    <col min="13324" max="13325" width="9.1640625" style="4"/>
-    <col min="13326" max="13326" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13327" max="13570" width="9.1640625" style="4"/>
-    <col min="13571" max="13571" width="5.5" style="4" customWidth="1"/>
-    <col min="13572" max="13572" width="16.5" style="4" customWidth="1"/>
-    <col min="13573" max="13573" width="11.5" style="4" customWidth="1"/>
-    <col min="13574" max="13574" width="12.5" style="4" customWidth="1"/>
-    <col min="13575" max="13575" width="19.33203125" style="4" customWidth="1"/>
-    <col min="13576" max="13576" width="16.5" style="4" customWidth="1"/>
-    <col min="13577" max="13578" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13579" max="13579" width="15.5" style="4" customWidth="1"/>
-    <col min="13580" max="13581" width="9.1640625" style="4"/>
-    <col min="13582" max="13582" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13583" max="13826" width="9.1640625" style="4"/>
-    <col min="13827" max="13827" width="5.5" style="4" customWidth="1"/>
-    <col min="13828" max="13828" width="16.5" style="4" customWidth="1"/>
-    <col min="13829" max="13829" width="11.5" style="4" customWidth="1"/>
-    <col min="13830" max="13830" width="12.5" style="4" customWidth="1"/>
-    <col min="13831" max="13831" width="19.33203125" style="4" customWidth="1"/>
-    <col min="13832" max="13832" width="16.5" style="4" customWidth="1"/>
-    <col min="13833" max="13834" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="13835" max="13835" width="15.5" style="4" customWidth="1"/>
-    <col min="13836" max="13837" width="9.1640625" style="4"/>
-    <col min="13838" max="13838" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="13839" max="14082" width="9.1640625" style="4"/>
-    <col min="14083" max="14083" width="5.5" style="4" customWidth="1"/>
-    <col min="14084" max="14084" width="16.5" style="4" customWidth="1"/>
-    <col min="14085" max="14085" width="11.5" style="4" customWidth="1"/>
-    <col min="14086" max="14086" width="12.5" style="4" customWidth="1"/>
-    <col min="14087" max="14087" width="19.33203125" style="4" customWidth="1"/>
-    <col min="14088" max="14088" width="16.5" style="4" customWidth="1"/>
-    <col min="14089" max="14090" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14091" max="14091" width="15.5" style="4" customWidth="1"/>
-    <col min="14092" max="14093" width="9.1640625" style="4"/>
-    <col min="14094" max="14094" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14095" max="14338" width="9.1640625" style="4"/>
-    <col min="14339" max="14339" width="5.5" style="4" customWidth="1"/>
-    <col min="14340" max="14340" width="16.5" style="4" customWidth="1"/>
-    <col min="14341" max="14341" width="11.5" style="4" customWidth="1"/>
-    <col min="14342" max="14342" width="12.5" style="4" customWidth="1"/>
-    <col min="14343" max="14343" width="19.33203125" style="4" customWidth="1"/>
-    <col min="14344" max="14344" width="16.5" style="4" customWidth="1"/>
-    <col min="14345" max="14346" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14347" max="14347" width="15.5" style="4" customWidth="1"/>
-    <col min="14348" max="14349" width="9.1640625" style="4"/>
-    <col min="14350" max="14350" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14351" max="14594" width="9.1640625" style="4"/>
-    <col min="14595" max="14595" width="5.5" style="4" customWidth="1"/>
-    <col min="14596" max="14596" width="16.5" style="4" customWidth="1"/>
-    <col min="14597" max="14597" width="11.5" style="4" customWidth="1"/>
-    <col min="14598" max="14598" width="12.5" style="4" customWidth="1"/>
-    <col min="14599" max="14599" width="19.33203125" style="4" customWidth="1"/>
-    <col min="14600" max="14600" width="16.5" style="4" customWidth="1"/>
-    <col min="14601" max="14602" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14603" max="14603" width="15.5" style="4" customWidth="1"/>
-    <col min="14604" max="14605" width="9.1640625" style="4"/>
-    <col min="14606" max="14606" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14607" max="14850" width="9.1640625" style="4"/>
-    <col min="14851" max="14851" width="5.5" style="4" customWidth="1"/>
-    <col min="14852" max="14852" width="16.5" style="4" customWidth="1"/>
-    <col min="14853" max="14853" width="11.5" style="4" customWidth="1"/>
-    <col min="14854" max="14854" width="12.5" style="4" customWidth="1"/>
-    <col min="14855" max="14855" width="19.33203125" style="4" customWidth="1"/>
-    <col min="14856" max="14856" width="16.5" style="4" customWidth="1"/>
-    <col min="14857" max="14858" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="14859" max="14859" width="15.5" style="4" customWidth="1"/>
-    <col min="14860" max="14861" width="9.1640625" style="4"/>
-    <col min="14862" max="14862" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="14863" max="15106" width="9.1640625" style="4"/>
-    <col min="15107" max="15107" width="5.5" style="4" customWidth="1"/>
-    <col min="15108" max="15108" width="16.5" style="4" customWidth="1"/>
-    <col min="15109" max="15109" width="11.5" style="4" customWidth="1"/>
-    <col min="15110" max="15110" width="12.5" style="4" customWidth="1"/>
-    <col min="15111" max="15111" width="19.33203125" style="4" customWidth="1"/>
-    <col min="15112" max="15112" width="16.5" style="4" customWidth="1"/>
-    <col min="15113" max="15114" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15115" max="15115" width="15.5" style="4" customWidth="1"/>
-    <col min="15116" max="15117" width="9.1640625" style="4"/>
-    <col min="15118" max="15118" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15119" max="15362" width="9.1640625" style="4"/>
-    <col min="15363" max="15363" width="5.5" style="4" customWidth="1"/>
-    <col min="15364" max="15364" width="16.5" style="4" customWidth="1"/>
-    <col min="15365" max="15365" width="11.5" style="4" customWidth="1"/>
-    <col min="15366" max="15366" width="12.5" style="4" customWidth="1"/>
-    <col min="15367" max="15367" width="19.33203125" style="4" customWidth="1"/>
-    <col min="15368" max="15368" width="16.5" style="4" customWidth="1"/>
-    <col min="15369" max="15370" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15371" max="15371" width="15.5" style="4" customWidth="1"/>
-    <col min="15372" max="15373" width="9.1640625" style="4"/>
-    <col min="15374" max="15374" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15375" max="15618" width="9.1640625" style="4"/>
-    <col min="15619" max="15619" width="5.5" style="4" customWidth="1"/>
-    <col min="15620" max="15620" width="16.5" style="4" customWidth="1"/>
-    <col min="15621" max="15621" width="11.5" style="4" customWidth="1"/>
-    <col min="15622" max="15622" width="12.5" style="4" customWidth="1"/>
-    <col min="15623" max="15623" width="19.33203125" style="4" customWidth="1"/>
-    <col min="15624" max="15624" width="16.5" style="4" customWidth="1"/>
-    <col min="15625" max="15626" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15627" max="15627" width="15.5" style="4" customWidth="1"/>
-    <col min="15628" max="15629" width="9.1640625" style="4"/>
-    <col min="15630" max="15630" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15631" max="15874" width="9.1640625" style="4"/>
-    <col min="15875" max="15875" width="5.5" style="4" customWidth="1"/>
-    <col min="15876" max="15876" width="16.5" style="4" customWidth="1"/>
-    <col min="15877" max="15877" width="11.5" style="4" customWidth="1"/>
-    <col min="15878" max="15878" width="12.5" style="4" customWidth="1"/>
-    <col min="15879" max="15879" width="19.33203125" style="4" customWidth="1"/>
-    <col min="15880" max="15880" width="16.5" style="4" customWidth="1"/>
-    <col min="15881" max="15882" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="15883" max="15883" width="15.5" style="4" customWidth="1"/>
-    <col min="15884" max="15885" width="9.1640625" style="4"/>
-    <col min="15886" max="15886" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15887" max="16130" width="9.1640625" style="4"/>
-    <col min="16131" max="16131" width="5.5" style="4" customWidth="1"/>
-    <col min="16132" max="16132" width="16.5" style="4" customWidth="1"/>
-    <col min="16133" max="16133" width="11.5" style="4" customWidth="1"/>
-    <col min="16134" max="16134" width="12.5" style="4" customWidth="1"/>
-    <col min="16135" max="16135" width="19.33203125" style="4" customWidth="1"/>
-    <col min="16136" max="16136" width="16.5" style="4" customWidth="1"/>
-    <col min="16137" max="16138" width="0" style="4" hidden="1" customWidth="1"/>
-    <col min="16139" max="16139" width="15.5" style="4" customWidth="1"/>
-    <col min="16140" max="16141" width="9.1640625" style="4"/>
-    <col min="16142" max="16142" width="15.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="16143" max="16384" width="9.1640625" style="4"/>
+    <col width="5.5" customWidth="1" style="4" min="1" max="1"/>
+    <col width="10.6640625" customWidth="1" style="4" min="2" max="2"/>
+    <col width="10.1640625" customWidth="1" style="4" min="3" max="3"/>
+    <col width="11" customWidth="1" style="4" min="4" max="4"/>
+    <col width="9.6640625" customWidth="1" style="4" min="5" max="5"/>
+    <col width="16.5" customWidth="1" style="4" min="6" max="6"/>
+    <col width="15.5" customWidth="1" style="4" min="7" max="7"/>
+    <col hidden="1" width="5.6640625" customWidth="1" style="103" min="8" max="8"/>
+    <col hidden="1" width="0.5" customWidth="1" style="4" min="9" max="9"/>
+    <col width="14.6640625" customWidth="1" style="103" min="10" max="10"/>
+    <col width="8.33203125" customWidth="1" style="103" min="11" max="11"/>
+    <col hidden="1" width="7.6640625" customWidth="1" style="4" min="12" max="12"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13" max="13"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="14" max="14"/>
+    <col width="17.83203125" customWidth="1" style="4" min="15" max="15"/>
+    <col width="9.1640625" customWidth="1" style="4" min="16" max="17"/>
+    <col width="15.5" bestFit="1" customWidth="1" style="4" min="18" max="18"/>
+    <col width="9.1640625" customWidth="1" style="4" min="19" max="258"/>
+    <col width="5.5" customWidth="1" style="4" min="259" max="259"/>
+    <col width="16.5" customWidth="1" style="4" min="260" max="260"/>
+    <col width="11.5" customWidth="1" style="4" min="261" max="261"/>
+    <col width="12.5" customWidth="1" style="4" min="262" max="262"/>
+    <col width="19.33203125" customWidth="1" style="4" min="263" max="263"/>
+    <col width="16.5" customWidth="1" style="4" min="264" max="264"/>
+    <col hidden="1" style="4" min="265" max="266"/>
+    <col width="15.5" customWidth="1" style="4" min="267" max="267"/>
+    <col width="9.1640625" customWidth="1" style="4" min="268" max="269"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="270" max="270"/>
+    <col width="9.1640625" customWidth="1" style="4" min="271" max="514"/>
+    <col width="5.5" customWidth="1" style="4" min="515" max="515"/>
+    <col width="16.5" customWidth="1" style="4" min="516" max="516"/>
+    <col width="11.5" customWidth="1" style="4" min="517" max="517"/>
+    <col width="12.5" customWidth="1" style="4" min="518" max="518"/>
+    <col width="19.33203125" customWidth="1" style="4" min="519" max="519"/>
+    <col width="16.5" customWidth="1" style="4" min="520" max="520"/>
+    <col hidden="1" style="4" min="521" max="522"/>
+    <col width="15.5" customWidth="1" style="4" min="523" max="523"/>
+    <col width="9.1640625" customWidth="1" style="4" min="524" max="525"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="526" max="526"/>
+    <col width="9.1640625" customWidth="1" style="4" min="527" max="770"/>
+    <col width="5.5" customWidth="1" style="4" min="771" max="771"/>
+    <col width="16.5" customWidth="1" style="4" min="772" max="772"/>
+    <col width="11.5" customWidth="1" style="4" min="773" max="773"/>
+    <col width="12.5" customWidth="1" style="4" min="774" max="774"/>
+    <col width="19.33203125" customWidth="1" style="4" min="775" max="775"/>
+    <col width="16.5" customWidth="1" style="4" min="776" max="776"/>
+    <col hidden="1" style="4" min="777" max="778"/>
+    <col width="15.5" customWidth="1" style="4" min="779" max="779"/>
+    <col width="9.1640625" customWidth="1" style="4" min="780" max="781"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="782" max="782"/>
+    <col width="9.1640625" customWidth="1" style="4" min="783" max="1026"/>
+    <col width="5.5" customWidth="1" style="4" min="1027" max="1027"/>
+    <col width="16.5" customWidth="1" style="4" min="1028" max="1028"/>
+    <col width="11.5" customWidth="1" style="4" min="1029" max="1029"/>
+    <col width="12.5" customWidth="1" style="4" min="1030" max="1030"/>
+    <col width="19.33203125" customWidth="1" style="4" min="1031" max="1031"/>
+    <col width="16.5" customWidth="1" style="4" min="1032" max="1032"/>
+    <col hidden="1" style="4" min="1033" max="1034"/>
+    <col width="15.5" customWidth="1" style="4" min="1035" max="1035"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1036" max="1037"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="1038" max="1038"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1039" max="1282"/>
+    <col width="5.5" customWidth="1" style="4" min="1283" max="1283"/>
+    <col width="16.5" customWidth="1" style="4" min="1284" max="1284"/>
+    <col width="11.5" customWidth="1" style="4" min="1285" max="1285"/>
+    <col width="12.5" customWidth="1" style="4" min="1286" max="1286"/>
+    <col width="19.33203125" customWidth="1" style="4" min="1287" max="1287"/>
+    <col width="16.5" customWidth="1" style="4" min="1288" max="1288"/>
+    <col hidden="1" style="4" min="1289" max="1290"/>
+    <col width="15.5" customWidth="1" style="4" min="1291" max="1291"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1292" max="1293"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="1294" max="1294"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1295" max="1538"/>
+    <col width="5.5" customWidth="1" style="4" min="1539" max="1539"/>
+    <col width="16.5" customWidth="1" style="4" min="1540" max="1540"/>
+    <col width="11.5" customWidth="1" style="4" min="1541" max="1541"/>
+    <col width="12.5" customWidth="1" style="4" min="1542" max="1542"/>
+    <col width="19.33203125" customWidth="1" style="4" min="1543" max="1543"/>
+    <col width="16.5" customWidth="1" style="4" min="1544" max="1544"/>
+    <col hidden="1" style="4" min="1545" max="1546"/>
+    <col width="15.5" customWidth="1" style="4" min="1547" max="1547"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1548" max="1549"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="1550" max="1550"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1551" max="1794"/>
+    <col width="5.5" customWidth="1" style="4" min="1795" max="1795"/>
+    <col width="16.5" customWidth="1" style="4" min="1796" max="1796"/>
+    <col width="11.5" customWidth="1" style="4" min="1797" max="1797"/>
+    <col width="12.5" customWidth="1" style="4" min="1798" max="1798"/>
+    <col width="19.33203125" customWidth="1" style="4" min="1799" max="1799"/>
+    <col width="16.5" customWidth="1" style="4" min="1800" max="1800"/>
+    <col hidden="1" style="4" min="1801" max="1802"/>
+    <col width="15.5" customWidth="1" style="4" min="1803" max="1803"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1804" max="1805"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="1806" max="1806"/>
+    <col width="9.1640625" customWidth="1" style="4" min="1807" max="2050"/>
+    <col width="5.5" customWidth="1" style="4" min="2051" max="2051"/>
+    <col width="16.5" customWidth="1" style="4" min="2052" max="2052"/>
+    <col width="11.5" customWidth="1" style="4" min="2053" max="2053"/>
+    <col width="12.5" customWidth="1" style="4" min="2054" max="2054"/>
+    <col width="19.33203125" customWidth="1" style="4" min="2055" max="2055"/>
+    <col width="16.5" customWidth="1" style="4" min="2056" max="2056"/>
+    <col hidden="1" style="4" min="2057" max="2058"/>
+    <col width="15.5" customWidth="1" style="4" min="2059" max="2059"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2060" max="2061"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="2062" max="2062"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2063" max="2306"/>
+    <col width="5.5" customWidth="1" style="4" min="2307" max="2307"/>
+    <col width="16.5" customWidth="1" style="4" min="2308" max="2308"/>
+    <col width="11.5" customWidth="1" style="4" min="2309" max="2309"/>
+    <col width="12.5" customWidth="1" style="4" min="2310" max="2310"/>
+    <col width="19.33203125" customWidth="1" style="4" min="2311" max="2311"/>
+    <col width="16.5" customWidth="1" style="4" min="2312" max="2312"/>
+    <col hidden="1" style="4" min="2313" max="2314"/>
+    <col width="15.5" customWidth="1" style="4" min="2315" max="2315"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2316" max="2317"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="2318" max="2318"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2319" max="2562"/>
+    <col width="5.5" customWidth="1" style="4" min="2563" max="2563"/>
+    <col width="16.5" customWidth="1" style="4" min="2564" max="2564"/>
+    <col width="11.5" customWidth="1" style="4" min="2565" max="2565"/>
+    <col width="12.5" customWidth="1" style="4" min="2566" max="2566"/>
+    <col width="19.33203125" customWidth="1" style="4" min="2567" max="2567"/>
+    <col width="16.5" customWidth="1" style="4" min="2568" max="2568"/>
+    <col hidden="1" style="4" min="2569" max="2570"/>
+    <col width="15.5" customWidth="1" style="4" min="2571" max="2571"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2572" max="2573"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="2574" max="2574"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2575" max="2818"/>
+    <col width="5.5" customWidth="1" style="4" min="2819" max="2819"/>
+    <col width="16.5" customWidth="1" style="4" min="2820" max="2820"/>
+    <col width="11.5" customWidth="1" style="4" min="2821" max="2821"/>
+    <col width="12.5" customWidth="1" style="4" min="2822" max="2822"/>
+    <col width="19.33203125" customWidth="1" style="4" min="2823" max="2823"/>
+    <col width="16.5" customWidth="1" style="4" min="2824" max="2824"/>
+    <col hidden="1" style="4" min="2825" max="2826"/>
+    <col width="15.5" customWidth="1" style="4" min="2827" max="2827"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2828" max="2829"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="2830" max="2830"/>
+    <col width="9.1640625" customWidth="1" style="4" min="2831" max="3074"/>
+    <col width="5.5" customWidth="1" style="4" min="3075" max="3075"/>
+    <col width="16.5" customWidth="1" style="4" min="3076" max="3076"/>
+    <col width="11.5" customWidth="1" style="4" min="3077" max="3077"/>
+    <col width="12.5" customWidth="1" style="4" min="3078" max="3078"/>
+    <col width="19.33203125" customWidth="1" style="4" min="3079" max="3079"/>
+    <col width="16.5" customWidth="1" style="4" min="3080" max="3080"/>
+    <col hidden="1" style="4" min="3081" max="3082"/>
+    <col width="15.5" customWidth="1" style="4" min="3083" max="3083"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3084" max="3085"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="3086" max="3086"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3087" max="3330"/>
+    <col width="5.5" customWidth="1" style="4" min="3331" max="3331"/>
+    <col width="16.5" customWidth="1" style="4" min="3332" max="3332"/>
+    <col width="11.5" customWidth="1" style="4" min="3333" max="3333"/>
+    <col width="12.5" customWidth="1" style="4" min="3334" max="3334"/>
+    <col width="19.33203125" customWidth="1" style="4" min="3335" max="3335"/>
+    <col width="16.5" customWidth="1" style="4" min="3336" max="3336"/>
+    <col hidden="1" style="4" min="3337" max="3338"/>
+    <col width="15.5" customWidth="1" style="4" min="3339" max="3339"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3340" max="3341"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="3342" max="3342"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3343" max="3586"/>
+    <col width="5.5" customWidth="1" style="4" min="3587" max="3587"/>
+    <col width="16.5" customWidth="1" style="4" min="3588" max="3588"/>
+    <col width="11.5" customWidth="1" style="4" min="3589" max="3589"/>
+    <col width="12.5" customWidth="1" style="4" min="3590" max="3590"/>
+    <col width="19.33203125" customWidth="1" style="4" min="3591" max="3591"/>
+    <col width="16.5" customWidth="1" style="4" min="3592" max="3592"/>
+    <col hidden="1" style="4" min="3593" max="3594"/>
+    <col width="15.5" customWidth="1" style="4" min="3595" max="3595"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3596" max="3597"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="3598" max="3598"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3599" max="3842"/>
+    <col width="5.5" customWidth="1" style="4" min="3843" max="3843"/>
+    <col width="16.5" customWidth="1" style="4" min="3844" max="3844"/>
+    <col width="11.5" customWidth="1" style="4" min="3845" max="3845"/>
+    <col width="12.5" customWidth="1" style="4" min="3846" max="3846"/>
+    <col width="19.33203125" customWidth="1" style="4" min="3847" max="3847"/>
+    <col width="16.5" customWidth="1" style="4" min="3848" max="3848"/>
+    <col hidden="1" style="4" min="3849" max="3850"/>
+    <col width="15.5" customWidth="1" style="4" min="3851" max="3851"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3852" max="3853"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="3854" max="3854"/>
+    <col width="9.1640625" customWidth="1" style="4" min="3855" max="4098"/>
+    <col width="5.5" customWidth="1" style="4" min="4099" max="4099"/>
+    <col width="16.5" customWidth="1" style="4" min="4100" max="4100"/>
+    <col width="11.5" customWidth="1" style="4" min="4101" max="4101"/>
+    <col width="12.5" customWidth="1" style="4" min="4102" max="4102"/>
+    <col width="19.33203125" customWidth="1" style="4" min="4103" max="4103"/>
+    <col width="16.5" customWidth="1" style="4" min="4104" max="4104"/>
+    <col hidden="1" style="4" min="4105" max="4106"/>
+    <col width="15.5" customWidth="1" style="4" min="4107" max="4107"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4108" max="4109"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="4110" max="4110"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4111" max="4354"/>
+    <col width="5.5" customWidth="1" style="4" min="4355" max="4355"/>
+    <col width="16.5" customWidth="1" style="4" min="4356" max="4356"/>
+    <col width="11.5" customWidth="1" style="4" min="4357" max="4357"/>
+    <col width="12.5" customWidth="1" style="4" min="4358" max="4358"/>
+    <col width="19.33203125" customWidth="1" style="4" min="4359" max="4359"/>
+    <col width="16.5" customWidth="1" style="4" min="4360" max="4360"/>
+    <col hidden="1" style="4" min="4361" max="4362"/>
+    <col width="15.5" customWidth="1" style="4" min="4363" max="4363"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4364" max="4365"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="4366" max="4366"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4367" max="4610"/>
+    <col width="5.5" customWidth="1" style="4" min="4611" max="4611"/>
+    <col width="16.5" customWidth="1" style="4" min="4612" max="4612"/>
+    <col width="11.5" customWidth="1" style="4" min="4613" max="4613"/>
+    <col width="12.5" customWidth="1" style="4" min="4614" max="4614"/>
+    <col width="19.33203125" customWidth="1" style="4" min="4615" max="4615"/>
+    <col width="16.5" customWidth="1" style="4" min="4616" max="4616"/>
+    <col hidden="1" style="4" min="4617" max="4618"/>
+    <col width="15.5" customWidth="1" style="4" min="4619" max="4619"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4620" max="4621"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="4622" max="4622"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4623" max="4866"/>
+    <col width="5.5" customWidth="1" style="4" min="4867" max="4867"/>
+    <col width="16.5" customWidth="1" style="4" min="4868" max="4868"/>
+    <col width="11.5" customWidth="1" style="4" min="4869" max="4869"/>
+    <col width="12.5" customWidth="1" style="4" min="4870" max="4870"/>
+    <col width="19.33203125" customWidth="1" style="4" min="4871" max="4871"/>
+    <col width="16.5" customWidth="1" style="4" min="4872" max="4872"/>
+    <col hidden="1" style="4" min="4873" max="4874"/>
+    <col width="15.5" customWidth="1" style="4" min="4875" max="4875"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4876" max="4877"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="4878" max="4878"/>
+    <col width="9.1640625" customWidth="1" style="4" min="4879" max="5122"/>
+    <col width="5.5" customWidth="1" style="4" min="5123" max="5123"/>
+    <col width="16.5" customWidth="1" style="4" min="5124" max="5124"/>
+    <col width="11.5" customWidth="1" style="4" min="5125" max="5125"/>
+    <col width="12.5" customWidth="1" style="4" min="5126" max="5126"/>
+    <col width="19.33203125" customWidth="1" style="4" min="5127" max="5127"/>
+    <col width="16.5" customWidth="1" style="4" min="5128" max="5128"/>
+    <col hidden="1" style="4" min="5129" max="5130"/>
+    <col width="15.5" customWidth="1" style="4" min="5131" max="5131"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5132" max="5133"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="5134" max="5134"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5135" max="5378"/>
+    <col width="5.5" customWidth="1" style="4" min="5379" max="5379"/>
+    <col width="16.5" customWidth="1" style="4" min="5380" max="5380"/>
+    <col width="11.5" customWidth="1" style="4" min="5381" max="5381"/>
+    <col width="12.5" customWidth="1" style="4" min="5382" max="5382"/>
+    <col width="19.33203125" customWidth="1" style="4" min="5383" max="5383"/>
+    <col width="16.5" customWidth="1" style="4" min="5384" max="5384"/>
+    <col hidden="1" style="4" min="5385" max="5386"/>
+    <col width="15.5" customWidth="1" style="4" min="5387" max="5387"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5388" max="5389"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="5390" max="5390"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5391" max="5634"/>
+    <col width="5.5" customWidth="1" style="4" min="5635" max="5635"/>
+    <col width="16.5" customWidth="1" style="4" min="5636" max="5636"/>
+    <col width="11.5" customWidth="1" style="4" min="5637" max="5637"/>
+    <col width="12.5" customWidth="1" style="4" min="5638" max="5638"/>
+    <col width="19.33203125" customWidth="1" style="4" min="5639" max="5639"/>
+    <col width="16.5" customWidth="1" style="4" min="5640" max="5640"/>
+    <col hidden="1" style="4" min="5641" max="5642"/>
+    <col width="15.5" customWidth="1" style="4" min="5643" max="5643"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5644" max="5645"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="5646" max="5646"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5647" max="5890"/>
+    <col width="5.5" customWidth="1" style="4" min="5891" max="5891"/>
+    <col width="16.5" customWidth="1" style="4" min="5892" max="5892"/>
+    <col width="11.5" customWidth="1" style="4" min="5893" max="5893"/>
+    <col width="12.5" customWidth="1" style="4" min="5894" max="5894"/>
+    <col width="19.33203125" customWidth="1" style="4" min="5895" max="5895"/>
+    <col width="16.5" customWidth="1" style="4" min="5896" max="5896"/>
+    <col hidden="1" style="4" min="5897" max="5898"/>
+    <col width="15.5" customWidth="1" style="4" min="5899" max="5899"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5900" max="5901"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="5902" max="5902"/>
+    <col width="9.1640625" customWidth="1" style="4" min="5903" max="6146"/>
+    <col width="5.5" customWidth="1" style="4" min="6147" max="6147"/>
+    <col width="16.5" customWidth="1" style="4" min="6148" max="6148"/>
+    <col width="11.5" customWidth="1" style="4" min="6149" max="6149"/>
+    <col width="12.5" customWidth="1" style="4" min="6150" max="6150"/>
+    <col width="19.33203125" customWidth="1" style="4" min="6151" max="6151"/>
+    <col width="16.5" customWidth="1" style="4" min="6152" max="6152"/>
+    <col hidden="1" style="4" min="6153" max="6154"/>
+    <col width="15.5" customWidth="1" style="4" min="6155" max="6155"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6156" max="6157"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="6158" max="6158"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6159" max="6402"/>
+    <col width="5.5" customWidth="1" style="4" min="6403" max="6403"/>
+    <col width="16.5" customWidth="1" style="4" min="6404" max="6404"/>
+    <col width="11.5" customWidth="1" style="4" min="6405" max="6405"/>
+    <col width="12.5" customWidth="1" style="4" min="6406" max="6406"/>
+    <col width="19.33203125" customWidth="1" style="4" min="6407" max="6407"/>
+    <col width="16.5" customWidth="1" style="4" min="6408" max="6408"/>
+    <col hidden="1" style="4" min="6409" max="6410"/>
+    <col width="15.5" customWidth="1" style="4" min="6411" max="6411"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6412" max="6413"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="6414" max="6414"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6415" max="6658"/>
+    <col width="5.5" customWidth="1" style="4" min="6659" max="6659"/>
+    <col width="16.5" customWidth="1" style="4" min="6660" max="6660"/>
+    <col width="11.5" customWidth="1" style="4" min="6661" max="6661"/>
+    <col width="12.5" customWidth="1" style="4" min="6662" max="6662"/>
+    <col width="19.33203125" customWidth="1" style="4" min="6663" max="6663"/>
+    <col width="16.5" customWidth="1" style="4" min="6664" max="6664"/>
+    <col hidden="1" style="4" min="6665" max="6666"/>
+    <col width="15.5" customWidth="1" style="4" min="6667" max="6667"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6668" max="6669"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="6670" max="6670"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6671" max="6914"/>
+    <col width="5.5" customWidth="1" style="4" min="6915" max="6915"/>
+    <col width="16.5" customWidth="1" style="4" min="6916" max="6916"/>
+    <col width="11.5" customWidth="1" style="4" min="6917" max="6917"/>
+    <col width="12.5" customWidth="1" style="4" min="6918" max="6918"/>
+    <col width="19.33203125" customWidth="1" style="4" min="6919" max="6919"/>
+    <col width="16.5" customWidth="1" style="4" min="6920" max="6920"/>
+    <col hidden="1" style="4" min="6921" max="6922"/>
+    <col width="15.5" customWidth="1" style="4" min="6923" max="6923"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6924" max="6925"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="6926" max="6926"/>
+    <col width="9.1640625" customWidth="1" style="4" min="6927" max="7170"/>
+    <col width="5.5" customWidth="1" style="4" min="7171" max="7171"/>
+    <col width="16.5" customWidth="1" style="4" min="7172" max="7172"/>
+    <col width="11.5" customWidth="1" style="4" min="7173" max="7173"/>
+    <col width="12.5" customWidth="1" style="4" min="7174" max="7174"/>
+    <col width="19.33203125" customWidth="1" style="4" min="7175" max="7175"/>
+    <col width="16.5" customWidth="1" style="4" min="7176" max="7176"/>
+    <col hidden="1" style="4" min="7177" max="7178"/>
+    <col width="15.5" customWidth="1" style="4" min="7179" max="7179"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7180" max="7181"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="7182" max="7182"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7183" max="7426"/>
+    <col width="5.5" customWidth="1" style="4" min="7427" max="7427"/>
+    <col width="16.5" customWidth="1" style="4" min="7428" max="7428"/>
+    <col width="11.5" customWidth="1" style="4" min="7429" max="7429"/>
+    <col width="12.5" customWidth="1" style="4" min="7430" max="7430"/>
+    <col width="19.33203125" customWidth="1" style="4" min="7431" max="7431"/>
+    <col width="16.5" customWidth="1" style="4" min="7432" max="7432"/>
+    <col hidden="1" style="4" min="7433" max="7434"/>
+    <col width="15.5" customWidth="1" style="4" min="7435" max="7435"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7436" max="7437"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="7438" max="7438"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7439" max="7682"/>
+    <col width="5.5" customWidth="1" style="4" min="7683" max="7683"/>
+    <col width="16.5" customWidth="1" style="4" min="7684" max="7684"/>
+    <col width="11.5" customWidth="1" style="4" min="7685" max="7685"/>
+    <col width="12.5" customWidth="1" style="4" min="7686" max="7686"/>
+    <col width="19.33203125" customWidth="1" style="4" min="7687" max="7687"/>
+    <col width="16.5" customWidth="1" style="4" min="7688" max="7688"/>
+    <col hidden="1" style="4" min="7689" max="7690"/>
+    <col width="15.5" customWidth="1" style="4" min="7691" max="7691"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7692" max="7693"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="7694" max="7694"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7695" max="7938"/>
+    <col width="5.5" customWidth="1" style="4" min="7939" max="7939"/>
+    <col width="16.5" customWidth="1" style="4" min="7940" max="7940"/>
+    <col width="11.5" customWidth="1" style="4" min="7941" max="7941"/>
+    <col width="12.5" customWidth="1" style="4" min="7942" max="7942"/>
+    <col width="19.33203125" customWidth="1" style="4" min="7943" max="7943"/>
+    <col width="16.5" customWidth="1" style="4" min="7944" max="7944"/>
+    <col hidden="1" style="4" min="7945" max="7946"/>
+    <col width="15.5" customWidth="1" style="4" min="7947" max="7947"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7948" max="7949"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="7950" max="7950"/>
+    <col width="9.1640625" customWidth="1" style="4" min="7951" max="8194"/>
+    <col width="5.5" customWidth="1" style="4" min="8195" max="8195"/>
+    <col width="16.5" customWidth="1" style="4" min="8196" max="8196"/>
+    <col width="11.5" customWidth="1" style="4" min="8197" max="8197"/>
+    <col width="12.5" customWidth="1" style="4" min="8198" max="8198"/>
+    <col width="19.33203125" customWidth="1" style="4" min="8199" max="8199"/>
+    <col width="16.5" customWidth="1" style="4" min="8200" max="8200"/>
+    <col hidden="1" style="4" min="8201" max="8202"/>
+    <col width="15.5" customWidth="1" style="4" min="8203" max="8203"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8204" max="8205"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="8206" max="8206"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8207" max="8450"/>
+    <col width="5.5" customWidth="1" style="4" min="8451" max="8451"/>
+    <col width="16.5" customWidth="1" style="4" min="8452" max="8452"/>
+    <col width="11.5" customWidth="1" style="4" min="8453" max="8453"/>
+    <col width="12.5" customWidth="1" style="4" min="8454" max="8454"/>
+    <col width="19.33203125" customWidth="1" style="4" min="8455" max="8455"/>
+    <col width="16.5" customWidth="1" style="4" min="8456" max="8456"/>
+    <col hidden="1" style="4" min="8457" max="8458"/>
+    <col width="15.5" customWidth="1" style="4" min="8459" max="8459"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8460" max="8461"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="8462" max="8462"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8463" max="8706"/>
+    <col width="5.5" customWidth="1" style="4" min="8707" max="8707"/>
+    <col width="16.5" customWidth="1" style="4" min="8708" max="8708"/>
+    <col width="11.5" customWidth="1" style="4" min="8709" max="8709"/>
+    <col width="12.5" customWidth="1" style="4" min="8710" max="8710"/>
+    <col width="19.33203125" customWidth="1" style="4" min="8711" max="8711"/>
+    <col width="16.5" customWidth="1" style="4" min="8712" max="8712"/>
+    <col hidden="1" style="4" min="8713" max="8714"/>
+    <col width="15.5" customWidth="1" style="4" min="8715" max="8715"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8716" max="8717"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="8718" max="8718"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8719" max="8962"/>
+    <col width="5.5" customWidth="1" style="4" min="8963" max="8963"/>
+    <col width="16.5" customWidth="1" style="4" min="8964" max="8964"/>
+    <col width="11.5" customWidth="1" style="4" min="8965" max="8965"/>
+    <col width="12.5" customWidth="1" style="4" min="8966" max="8966"/>
+    <col width="19.33203125" customWidth="1" style="4" min="8967" max="8967"/>
+    <col width="16.5" customWidth="1" style="4" min="8968" max="8968"/>
+    <col hidden="1" style="4" min="8969" max="8970"/>
+    <col width="15.5" customWidth="1" style="4" min="8971" max="8971"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8972" max="8973"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="8974" max="8974"/>
+    <col width="9.1640625" customWidth="1" style="4" min="8975" max="9218"/>
+    <col width="5.5" customWidth="1" style="4" min="9219" max="9219"/>
+    <col width="16.5" customWidth="1" style="4" min="9220" max="9220"/>
+    <col width="11.5" customWidth="1" style="4" min="9221" max="9221"/>
+    <col width="12.5" customWidth="1" style="4" min="9222" max="9222"/>
+    <col width="19.33203125" customWidth="1" style="4" min="9223" max="9223"/>
+    <col width="16.5" customWidth="1" style="4" min="9224" max="9224"/>
+    <col hidden="1" style="4" min="9225" max="9226"/>
+    <col width="15.5" customWidth="1" style="4" min="9227" max="9227"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9228" max="9229"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="9230" max="9230"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9231" max="9474"/>
+    <col width="5.5" customWidth="1" style="4" min="9475" max="9475"/>
+    <col width="16.5" customWidth="1" style="4" min="9476" max="9476"/>
+    <col width="11.5" customWidth="1" style="4" min="9477" max="9477"/>
+    <col width="12.5" customWidth="1" style="4" min="9478" max="9478"/>
+    <col width="19.33203125" customWidth="1" style="4" min="9479" max="9479"/>
+    <col width="16.5" customWidth="1" style="4" min="9480" max="9480"/>
+    <col hidden="1" style="4" min="9481" max="9482"/>
+    <col width="15.5" customWidth="1" style="4" min="9483" max="9483"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9484" max="9485"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="9486" max="9486"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9487" max="9730"/>
+    <col width="5.5" customWidth="1" style="4" min="9731" max="9731"/>
+    <col width="16.5" customWidth="1" style="4" min="9732" max="9732"/>
+    <col width="11.5" customWidth="1" style="4" min="9733" max="9733"/>
+    <col width="12.5" customWidth="1" style="4" min="9734" max="9734"/>
+    <col width="19.33203125" customWidth="1" style="4" min="9735" max="9735"/>
+    <col width="16.5" customWidth="1" style="4" min="9736" max="9736"/>
+    <col hidden="1" style="4" min="9737" max="9738"/>
+    <col width="15.5" customWidth="1" style="4" min="9739" max="9739"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9740" max="9741"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="9742" max="9742"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9743" max="9986"/>
+    <col width="5.5" customWidth="1" style="4" min="9987" max="9987"/>
+    <col width="16.5" customWidth="1" style="4" min="9988" max="9988"/>
+    <col width="11.5" customWidth="1" style="4" min="9989" max="9989"/>
+    <col width="12.5" customWidth="1" style="4" min="9990" max="9990"/>
+    <col width="19.33203125" customWidth="1" style="4" min="9991" max="9991"/>
+    <col width="16.5" customWidth="1" style="4" min="9992" max="9992"/>
+    <col hidden="1" style="4" min="9993" max="9994"/>
+    <col width="15.5" customWidth="1" style="4" min="9995" max="9995"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9996" max="9997"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="9998" max="9998"/>
+    <col width="9.1640625" customWidth="1" style="4" min="9999" max="10242"/>
+    <col width="5.5" customWidth="1" style="4" min="10243" max="10243"/>
+    <col width="16.5" customWidth="1" style="4" min="10244" max="10244"/>
+    <col width="11.5" customWidth="1" style="4" min="10245" max="10245"/>
+    <col width="12.5" customWidth="1" style="4" min="10246" max="10246"/>
+    <col width="19.33203125" customWidth="1" style="4" min="10247" max="10247"/>
+    <col width="16.5" customWidth="1" style="4" min="10248" max="10248"/>
+    <col hidden="1" style="4" min="10249" max="10250"/>
+    <col width="15.5" customWidth="1" style="4" min="10251" max="10251"/>
+    <col width="9.1640625" customWidth="1" style="4" min="10252" max="10253"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="10254" max="10254"/>
+    <col width="9.1640625" customWidth="1" style="4" min="10255" max="10498"/>
+    <col width="5.5" customWidth="1" style="4" min="10499" max="10499"/>
+    <col width="16.5" customWidth="1" style="4" min="10500" max="10500"/>
+    <col width="11.5" customWidth="1" style="4" min="10501" max="10501"/>
+    <col width="12.5" customWidth="1" style="4" min="10502" max="10502"/>
+    <col width="19.33203125" customWidth="1" style="4" min="10503" max="10503"/>
+    <col width="16.5" customWidth="1" style="4" min="10504" max="10504"/>
+    <col hidden="1" style="4" min="10505" max="10506"/>
+    <col width="15.5" customWidth="1" style="4" min="10507" max="10507"/>
+    <col width="9.1640625" customWidth="1" style="4" min="10508" max="10509"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="10510" max="10510"/>
+    <col width="9.1640625" customWidth="1" style="4" min="10511" max="10754"/>
+    <col width="5.5" customWidth="1" style="4" min="10755" max="10755"/>
+    <col width="16.5" customWidth="1" style="4" min="10756" max="10756"/>
+    <col width="11.5" customWidth="1" style="4" min="10757" max="10757"/>
+    <col width="12.5" customWidth="1" style="4" min="10758" max="10758"/>
+    <col width="19.33203125" customWidth="1" style="4" min="10759" max="10759"/>
+    <col width="16.5" customWidth="1" style="4" min="10760" max="10760"/>
+    <col hidden="1" style="4" min="10761" max="10762"/>
+    <col width="15.5" customWidth="1" style="4" min="10763" max="10763"/>
+    <col width="9.1640625" customWidth="1" style="4" min="10764" max="10765"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="10766" max="10766"/>
+    <col width="9.1640625" customWidth="1" style="4" min="10767" max="11010"/>
+    <col width="5.5" customWidth="1" style="4" min="11011" max="11011"/>
+    <col width="16.5" customWidth="1" style="4" min="11012" max="11012"/>
+    <col width="11.5" customWidth="1" style="4" min="11013" max="11013"/>
+    <col width="12.5" customWidth="1" style="4" min="11014" max="11014"/>
+    <col width="19.33203125" customWidth="1" style="4" min="11015" max="11015"/>
+    <col width="16.5" customWidth="1" style="4" min="11016" max="11016"/>
+    <col hidden="1" style="4" min="11017" max="11018"/>
+    <col width="15.5" customWidth="1" style="4" min="11019" max="11019"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11020" max="11021"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="11022" max="11022"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11023" max="11266"/>
+    <col width="5.5" customWidth="1" style="4" min="11267" max="11267"/>
+    <col width="16.5" customWidth="1" style="4" min="11268" max="11268"/>
+    <col width="11.5" customWidth="1" style="4" min="11269" max="11269"/>
+    <col width="12.5" customWidth="1" style="4" min="11270" max="11270"/>
+    <col width="19.33203125" customWidth="1" style="4" min="11271" max="11271"/>
+    <col width="16.5" customWidth="1" style="4" min="11272" max="11272"/>
+    <col hidden="1" style="4" min="11273" max="11274"/>
+    <col width="15.5" customWidth="1" style="4" min="11275" max="11275"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11276" max="11277"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="11278" max="11278"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11279" max="11522"/>
+    <col width="5.5" customWidth="1" style="4" min="11523" max="11523"/>
+    <col width="16.5" customWidth="1" style="4" min="11524" max="11524"/>
+    <col width="11.5" customWidth="1" style="4" min="11525" max="11525"/>
+    <col width="12.5" customWidth="1" style="4" min="11526" max="11526"/>
+    <col width="19.33203125" customWidth="1" style="4" min="11527" max="11527"/>
+    <col width="16.5" customWidth="1" style="4" min="11528" max="11528"/>
+    <col hidden="1" style="4" min="11529" max="11530"/>
+    <col width="15.5" customWidth="1" style="4" min="11531" max="11531"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11532" max="11533"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="11534" max="11534"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11535" max="11778"/>
+    <col width="5.5" customWidth="1" style="4" min="11779" max="11779"/>
+    <col width="16.5" customWidth="1" style="4" min="11780" max="11780"/>
+    <col width="11.5" customWidth="1" style="4" min="11781" max="11781"/>
+    <col width="12.5" customWidth="1" style="4" min="11782" max="11782"/>
+    <col width="19.33203125" customWidth="1" style="4" min="11783" max="11783"/>
+    <col width="16.5" customWidth="1" style="4" min="11784" max="11784"/>
+    <col hidden="1" style="4" min="11785" max="11786"/>
+    <col width="15.5" customWidth="1" style="4" min="11787" max="11787"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11788" max="11789"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="11790" max="11790"/>
+    <col width="9.1640625" customWidth="1" style="4" min="11791" max="12034"/>
+    <col width="5.5" customWidth="1" style="4" min="12035" max="12035"/>
+    <col width="16.5" customWidth="1" style="4" min="12036" max="12036"/>
+    <col width="11.5" customWidth="1" style="4" min="12037" max="12037"/>
+    <col width="12.5" customWidth="1" style="4" min="12038" max="12038"/>
+    <col width="19.33203125" customWidth="1" style="4" min="12039" max="12039"/>
+    <col width="16.5" customWidth="1" style="4" min="12040" max="12040"/>
+    <col hidden="1" style="4" min="12041" max="12042"/>
+    <col width="15.5" customWidth="1" style="4" min="12043" max="12043"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12044" max="12045"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="12046" max="12046"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12047" max="12290"/>
+    <col width="5.5" customWidth="1" style="4" min="12291" max="12291"/>
+    <col width="16.5" customWidth="1" style="4" min="12292" max="12292"/>
+    <col width="11.5" customWidth="1" style="4" min="12293" max="12293"/>
+    <col width="12.5" customWidth="1" style="4" min="12294" max="12294"/>
+    <col width="19.33203125" customWidth="1" style="4" min="12295" max="12295"/>
+    <col width="16.5" customWidth="1" style="4" min="12296" max="12296"/>
+    <col hidden="1" style="4" min="12297" max="12298"/>
+    <col width="15.5" customWidth="1" style="4" min="12299" max="12299"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12300" max="12301"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="12302" max="12302"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12303" max="12546"/>
+    <col width="5.5" customWidth="1" style="4" min="12547" max="12547"/>
+    <col width="16.5" customWidth="1" style="4" min="12548" max="12548"/>
+    <col width="11.5" customWidth="1" style="4" min="12549" max="12549"/>
+    <col width="12.5" customWidth="1" style="4" min="12550" max="12550"/>
+    <col width="19.33203125" customWidth="1" style="4" min="12551" max="12551"/>
+    <col width="16.5" customWidth="1" style="4" min="12552" max="12552"/>
+    <col hidden="1" style="4" min="12553" max="12554"/>
+    <col width="15.5" customWidth="1" style="4" min="12555" max="12555"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12556" max="12557"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="12558" max="12558"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12559" max="12802"/>
+    <col width="5.5" customWidth="1" style="4" min="12803" max="12803"/>
+    <col width="16.5" customWidth="1" style="4" min="12804" max="12804"/>
+    <col width="11.5" customWidth="1" style="4" min="12805" max="12805"/>
+    <col width="12.5" customWidth="1" style="4" min="12806" max="12806"/>
+    <col width="19.33203125" customWidth="1" style="4" min="12807" max="12807"/>
+    <col width="16.5" customWidth="1" style="4" min="12808" max="12808"/>
+    <col hidden="1" style="4" min="12809" max="12810"/>
+    <col width="15.5" customWidth="1" style="4" min="12811" max="12811"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12812" max="12813"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="12814" max="12814"/>
+    <col width="9.1640625" customWidth="1" style="4" min="12815" max="13058"/>
+    <col width="5.5" customWidth="1" style="4" min="13059" max="13059"/>
+    <col width="16.5" customWidth="1" style="4" min="13060" max="13060"/>
+    <col width="11.5" customWidth="1" style="4" min="13061" max="13061"/>
+    <col width="12.5" customWidth="1" style="4" min="13062" max="13062"/>
+    <col width="19.33203125" customWidth="1" style="4" min="13063" max="13063"/>
+    <col width="16.5" customWidth="1" style="4" min="13064" max="13064"/>
+    <col hidden="1" style="4" min="13065" max="13066"/>
+    <col width="15.5" customWidth="1" style="4" min="13067" max="13067"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13068" max="13069"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="13070" max="13070"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13071" max="13314"/>
+    <col width="5.5" customWidth="1" style="4" min="13315" max="13315"/>
+    <col width="16.5" customWidth="1" style="4" min="13316" max="13316"/>
+    <col width="11.5" customWidth="1" style="4" min="13317" max="13317"/>
+    <col width="12.5" customWidth="1" style="4" min="13318" max="13318"/>
+    <col width="19.33203125" customWidth="1" style="4" min="13319" max="13319"/>
+    <col width="16.5" customWidth="1" style="4" min="13320" max="13320"/>
+    <col hidden="1" style="4" min="13321" max="13322"/>
+    <col width="15.5" customWidth="1" style="4" min="13323" max="13323"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13324" max="13325"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="13326" max="13326"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13327" max="13570"/>
+    <col width="5.5" customWidth="1" style="4" min="13571" max="13571"/>
+    <col width="16.5" customWidth="1" style="4" min="13572" max="13572"/>
+    <col width="11.5" customWidth="1" style="4" min="13573" max="13573"/>
+    <col width="12.5" customWidth="1" style="4" min="13574" max="13574"/>
+    <col width="19.33203125" customWidth="1" style="4" min="13575" max="13575"/>
+    <col width="16.5" customWidth="1" style="4" min="13576" max="13576"/>
+    <col hidden="1" style="4" min="13577" max="13578"/>
+    <col width="15.5" customWidth="1" style="4" min="13579" max="13579"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13580" max="13581"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="13582" max="13582"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13583" max="13826"/>
+    <col width="5.5" customWidth="1" style="4" min="13827" max="13827"/>
+    <col width="16.5" customWidth="1" style="4" min="13828" max="13828"/>
+    <col width="11.5" customWidth="1" style="4" min="13829" max="13829"/>
+    <col width="12.5" customWidth="1" style="4" min="13830" max="13830"/>
+    <col width="19.33203125" customWidth="1" style="4" min="13831" max="13831"/>
+    <col width="16.5" customWidth="1" style="4" min="13832" max="13832"/>
+    <col hidden="1" style="4" min="13833" max="13834"/>
+    <col width="15.5" customWidth="1" style="4" min="13835" max="13835"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13836" max="13837"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="13838" max="13838"/>
+    <col width="9.1640625" customWidth="1" style="4" min="13839" max="14082"/>
+    <col width="5.5" customWidth="1" style="4" min="14083" max="14083"/>
+    <col width="16.5" customWidth="1" style="4" min="14084" max="14084"/>
+    <col width="11.5" customWidth="1" style="4" min="14085" max="14085"/>
+    <col width="12.5" customWidth="1" style="4" min="14086" max="14086"/>
+    <col width="19.33203125" customWidth="1" style="4" min="14087" max="14087"/>
+    <col width="16.5" customWidth="1" style="4" min="14088" max="14088"/>
+    <col hidden="1" style="4" min="14089" max="14090"/>
+    <col width="15.5" customWidth="1" style="4" min="14091" max="14091"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14092" max="14093"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="14094" max="14094"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14095" max="14338"/>
+    <col width="5.5" customWidth="1" style="4" min="14339" max="14339"/>
+    <col width="16.5" customWidth="1" style="4" min="14340" max="14340"/>
+    <col width="11.5" customWidth="1" style="4" min="14341" max="14341"/>
+    <col width="12.5" customWidth="1" style="4" min="14342" max="14342"/>
+    <col width="19.33203125" customWidth="1" style="4" min="14343" max="14343"/>
+    <col width="16.5" customWidth="1" style="4" min="14344" max="14344"/>
+    <col hidden="1" style="4" min="14345" max="14346"/>
+    <col width="15.5" customWidth="1" style="4" min="14347" max="14347"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14348" max="14349"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="14350" max="14350"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14351" max="14594"/>
+    <col width="5.5" customWidth="1" style="4" min="14595" max="14595"/>
+    <col width="16.5" customWidth="1" style="4" min="14596" max="14596"/>
+    <col width="11.5" customWidth="1" style="4" min="14597" max="14597"/>
+    <col width="12.5" customWidth="1" style="4" min="14598" max="14598"/>
+    <col width="19.33203125" customWidth="1" style="4" min="14599" max="14599"/>
+    <col width="16.5" customWidth="1" style="4" min="14600" max="14600"/>
+    <col hidden="1" style="4" min="14601" max="14602"/>
+    <col width="15.5" customWidth="1" style="4" min="14603" max="14603"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14604" max="14605"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="14606" max="14606"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14607" max="14850"/>
+    <col width="5.5" customWidth="1" style="4" min="14851" max="14851"/>
+    <col width="16.5" customWidth="1" style="4" min="14852" max="14852"/>
+    <col width="11.5" customWidth="1" style="4" min="14853" max="14853"/>
+    <col width="12.5" customWidth="1" style="4" min="14854" max="14854"/>
+    <col width="19.33203125" customWidth="1" style="4" min="14855" max="14855"/>
+    <col width="16.5" customWidth="1" style="4" min="14856" max="14856"/>
+    <col hidden="1" style="4" min="14857" max="14858"/>
+    <col width="15.5" customWidth="1" style="4" min="14859" max="14859"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14860" max="14861"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="14862" max="14862"/>
+    <col width="9.1640625" customWidth="1" style="4" min="14863" max="15106"/>
+    <col width="5.5" customWidth="1" style="4" min="15107" max="15107"/>
+    <col width="16.5" customWidth="1" style="4" min="15108" max="15108"/>
+    <col width="11.5" customWidth="1" style="4" min="15109" max="15109"/>
+    <col width="12.5" customWidth="1" style="4" min="15110" max="15110"/>
+    <col width="19.33203125" customWidth="1" style="4" min="15111" max="15111"/>
+    <col width="16.5" customWidth="1" style="4" min="15112" max="15112"/>
+    <col hidden="1" style="4" min="15113" max="15114"/>
+    <col width="15.5" customWidth="1" style="4" min="15115" max="15115"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15116" max="15117"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="15118" max="15118"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15119" max="15362"/>
+    <col width="5.5" customWidth="1" style="4" min="15363" max="15363"/>
+    <col width="16.5" customWidth="1" style="4" min="15364" max="15364"/>
+    <col width="11.5" customWidth="1" style="4" min="15365" max="15365"/>
+    <col width="12.5" customWidth="1" style="4" min="15366" max="15366"/>
+    <col width="19.33203125" customWidth="1" style="4" min="15367" max="15367"/>
+    <col width="16.5" customWidth="1" style="4" min="15368" max="15368"/>
+    <col hidden="1" style="4" min="15369" max="15370"/>
+    <col width="15.5" customWidth="1" style="4" min="15371" max="15371"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15372" max="15373"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="15374" max="15374"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15375" max="15618"/>
+    <col width="5.5" customWidth="1" style="4" min="15619" max="15619"/>
+    <col width="16.5" customWidth="1" style="4" min="15620" max="15620"/>
+    <col width="11.5" customWidth="1" style="4" min="15621" max="15621"/>
+    <col width="12.5" customWidth="1" style="4" min="15622" max="15622"/>
+    <col width="19.33203125" customWidth="1" style="4" min="15623" max="15623"/>
+    <col width="16.5" customWidth="1" style="4" min="15624" max="15624"/>
+    <col hidden="1" style="4" min="15625" max="15626"/>
+    <col width="15.5" customWidth="1" style="4" min="15627" max="15627"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15628" max="15629"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="15630" max="15630"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15631" max="15874"/>
+    <col width="5.5" customWidth="1" style="4" min="15875" max="15875"/>
+    <col width="16.5" customWidth="1" style="4" min="15876" max="15876"/>
+    <col width="11.5" customWidth="1" style="4" min="15877" max="15877"/>
+    <col width="12.5" customWidth="1" style="4" min="15878" max="15878"/>
+    <col width="19.33203125" customWidth="1" style="4" min="15879" max="15879"/>
+    <col width="16.5" customWidth="1" style="4" min="15880" max="15880"/>
+    <col hidden="1" style="4" min="15881" max="15882"/>
+    <col width="15.5" customWidth="1" style="4" min="15883" max="15883"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15884" max="15885"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="15886" max="15886"/>
+    <col width="9.1640625" customWidth="1" style="4" min="15887" max="16130"/>
+    <col width="5.5" customWidth="1" style="4" min="16131" max="16131"/>
+    <col width="16.5" customWidth="1" style="4" min="16132" max="16132"/>
+    <col width="11.5" customWidth="1" style="4" min="16133" max="16133"/>
+    <col width="12.5" customWidth="1" style="4" min="16134" max="16134"/>
+    <col width="19.33203125" customWidth="1" style="4" min="16135" max="16135"/>
+    <col width="16.5" customWidth="1" style="4" min="16136" max="16136"/>
+    <col hidden="1" style="4" min="16137" max="16138"/>
+    <col width="15.5" customWidth="1" style="4" min="16139" max="16139"/>
+    <col width="9.1640625" customWidth="1" style="4" min="16140" max="16141"/>
+    <col width="15.6640625" bestFit="1" customWidth="1" style="4" min="16142" max="16142"/>
+    <col width="9.1640625" customWidth="1" style="4" min="16143" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="31" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="94" t="s">
-        <v>23</v>
+    <row r="1" ht="31" customFormat="1" customHeight="1" s="3" thickBot="1">
+      <c r="A1" s="94" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG VÀ TM THIÊN NHẬT
+Địa chỉ: Thôn Quán Trắng, xã Liên Sơn, tỉnh Phú Thọ</t>
+        </is>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2">
+      <c r="B1" s="104" t="n"/>
+      <c r="C1" s="104" t="n"/>
+      <c r="D1" s="104" t="n"/>
+      <c r="E1" s="104" t="n"/>
+      <c r="F1" s="104" t="n"/>
+      <c r="G1" s="104" t="n"/>
+      <c r="H1" s="104" t="n"/>
+      <c r="I1" s="104" t="n"/>
+      <c r="J1" s="104" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="17" thickTop="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:15" ht="28" x14ac:dyDescent="0.2">
-      <c r="A3" s="96" t="s">
-        <v>0</v>
+    <row r="2" ht="17" customHeight="1" thickTop="1"/>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                              PHIẾU ĐỀ NGHỊ THANH TOÁN</t>
+        </is>
       </c>
-      <c r="B3" s="96"/>
-      <c r="C3" s="96"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="96"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="96"/>
-      <c r="H3" s="6"/>
-      <c r="J3" s="7" t="s">
+      <c r="H3" s="105" t="n"/>
+      <c r="J3" s="106" t="inlineStr">
+        <is>
+          <t>BM-03TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="107" t="n"/>
+      <c r="H4" s="107" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="108" t="inlineStr">
+        <is>
+          <t>Yêu cầu bởi</t>
+        </is>
+      </c>
+      <c r="B5" s="109" t="n"/>
+      <c r="C5" s="109" t="n"/>
+      <c r="D5" s="110" t="inlineStr">
+        <is>
+          <t>LÊ ANH HUY</t>
+        </is>
+      </c>
+      <c r="E5" s="111" t="n"/>
+      <c r="F5" s="111" t="n"/>
+      <c r="G5" s="112" t="n"/>
+      <c r="H5" s="103" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="108" t="inlineStr">
+        <is>
+          <t>Bộ phận</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+      <c r="C7" s="109" t="n"/>
+      <c r="D7" s="79" t="inlineStr">
+        <is>
+          <t>Kế hoạch-Vật tư</t>
+        </is>
+      </c>
+      <c r="E7" s="108" t="inlineStr">
+        <is>
+          <t>Mục đích</t>
+        </is>
+      </c>
+      <c r="F7" s="109" t="n"/>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Thanh toán</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="74" t="n"/>
+    </row>
+    <row r="8">
+      <c r="H8" s="103" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="108" t="inlineStr">
+        <is>
+          <t>Loại tiền</t>
+        </is>
+      </c>
+      <c r="B9" s="109" t="n"/>
+      <c r="C9" s="109" t="n"/>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="E9" s="108" t="inlineStr">
+        <is>
+          <t>Trả bằng</t>
+        </is>
+      </c>
+      <c r="F9" s="109" t="n"/>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>Chuyển khoản</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17.25" customHeight="1">
+      <c r="A11" s="113" t="inlineStr">
+        <is>
+          <t>Người hưởng</t>
+        </is>
+      </c>
+      <c r="B11" s="109" t="n"/>
+      <c r="C11" s="109" t="n"/>
+      <c r="D11" s="102" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN THỦ ĐÔ</t>
+        </is>
+      </c>
+      <c r="E11" s="111" t="n"/>
+      <c r="F11" s="111" t="n"/>
+      <c r="G11" s="112" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="113" t="inlineStr">
+        <is>
+          <t>Tài khoản</t>
+        </is>
+      </c>
+      <c r="B13" s="109" t="n"/>
+      <c r="C13" s="109" t="n"/>
+      <c r="D13" s="114" t="n">
+        <v>118000183348</v>
+      </c>
+      <c r="E13" s="111" t="n"/>
+      <c r="F13" s="111" t="n"/>
+      <c r="G13" s="112" t="n"/>
+    </row>
+    <row r="14">
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="O14" s="103" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="113" t="inlineStr">
+        <is>
+          <t>Tại Ngân hàng</t>
+        </is>
+      </c>
+      <c r="B15" s="109" t="n"/>
+      <c r="C15" s="109" t="n"/>
+      <c r="D15" s="79" t="inlineStr">
+        <is>
+          <t>Ngân hàng Vietin Bank - Chi nhánh Thanh Xuân, Hà Nội</t>
+        </is>
+      </c>
+      <c r="E15" s="111" t="n"/>
+      <c r="F15" s="111" t="n"/>
+      <c r="G15" s="112" t="n"/>
+      <c r="O15" s="103" t="n"/>
+    </row>
+    <row r="16">
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="O16" s="103" t="n"/>
+    </row>
+    <row r="17" ht="39" customFormat="1" customHeight="1" s="25">
+      <c r="A17" s="82" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="inlineStr">
+        <is>
+          <t>Số chứng từ</t>
+        </is>
+      </c>
+      <c r="C17" s="115" t="n"/>
+      <c r="D17" s="82" t="inlineStr">
+        <is>
+          <t>Ngày chứng từ</t>
+        </is>
+      </c>
+      <c r="E17" s="82" t="inlineStr">
+        <is>
+          <t>Diễn giải</t>
+        </is>
+      </c>
+      <c r="F17" s="116" t="n"/>
+      <c r="G17" s="115" t="n"/>
+      <c r="H17" s="117" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="I17" s="82" t="inlineStr">
+        <is>
+          <t>Đơn Giá</t>
+        </is>
+      </c>
+      <c r="J17" s="118" t="inlineStr">
+        <is>
+          <t>Thành Tiền</t>
+        </is>
+      </c>
+      <c r="K17" s="119" t="n"/>
+      <c r="N17" s="119" t="n"/>
+      <c r="W17" s="27">
+        <f>399/21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="51" customFormat="1" customHeight="1" s="3">
+      <c r="A18" s="28" t="n">
         <v>1</v>
       </c>
+      <c r="B18" s="120" t="inlineStr">
+        <is>
+          <t>00000411</t>
+        </is>
+      </c>
+      <c r="C18" s="121" t="n"/>
+      <c r="D18" s="72" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E18" s="122" t="inlineStr">
+        <is>
+          <t>Nhập dầu cầu TITAN SuperGear 85W-140 (205l/phuy) - FUSCH</t>
+        </is>
+      </c>
+      <c r="F18" s="123" t="n"/>
+      <c r="G18" s="121" t="n"/>
+      <c r="H18" s="124" t="n"/>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="125" t="n">
+        <v>44999999</v>
+      </c>
+      <c r="K18" s="126" t="n"/>
+      <c r="N18" s="127" t="n"/>
+      <c r="O18" s="32" t="n"/>
+      <c r="R18" s="127" t="n"/>
     </row>
-    <row r="4" spans="1:15" ht="28" x14ac:dyDescent="0.2">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-    </row>
-    <row r="5" spans="1:15" ht="18" x14ac:dyDescent="0.2">
-      <c r="D5" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="12"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D7" s="100" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="101"/>
-      <c r="G7" s="13" t="s">
+    <row r="19" ht="39" customFormat="1" customHeight="1" s="3">
+      <c r="A19" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="14"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D9" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D11" s="102" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D13" s="91">
-        <v>118000183348</v>
-      </c>
-      <c r="E13" s="92"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="93"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="O14" s="20"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D15" s="79" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="O15" s="20"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="O16" s="20"/>
-    </row>
-    <row r="17" spans="1:23" s="25" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="81"/>
-      <c r="D17" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="24"/>
-      <c r="N17" s="26"/>
-      <c r="W17" s="27">
-        <f>399/21</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" s="3" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="28">
-        <v>1</v>
-      </c>
-      <c r="B18" s="83" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="84"/>
-      <c r="D18" s="72">
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="35" t="n"/>
+      <c r="D19" s="72" t="n">
         <v>46163</v>
       </c>
-      <c r="E18" s="85" t="s">
-        <v>28</v>
+      <c r="E19" s="128" t="inlineStr">
+        <is>
+          <t>Nhập dầu thủy lực Renolin B68 Plus (205l/phuy) - FUSCH</t>
+        </is>
       </c>
-      <c r="F18" s="86"/>
-      <c r="G18" s="87"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="73">
-        <v>44999999</v>
-      </c>
-      <c r="K18" s="30"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="32"/>
-      <c r="R18" s="33"/>
-    </row>
-    <row r="19" spans="1:23" s="3" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="28">
-        <v>2</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="72">
-        <v>46163</v>
-      </c>
-      <c r="E19" s="88" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="89"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="36">
+      <c r="F19" s="129" t="n"/>
+      <c r="G19" s="130" t="n"/>
+      <c r="H19" s="124" t="n"/>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="131" t="n">
         <v>33600001</v>
       </c>
-      <c r="K19" s="30"/>
-      <c r="N19" s="31"/>
-      <c r="R19" s="37"/>
+      <c r="K19" s="126" t="n"/>
+      <c r="N19" s="127" t="n"/>
+      <c r="R19" s="132" t="n"/>
     </row>
-    <row r="20" spans="1:23" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="38"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="75" t="s">
-        <v>12</v>
+    <row r="20" ht="18" customFormat="1" customHeight="1" s="3">
+      <c r="A20" s="38" t="n"/>
+      <c r="B20" s="39" t="n"/>
+      <c r="C20" s="40" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="75" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG</t>
+        </is>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="42">
+      <c r="F20" s="111" t="n"/>
+      <c r="G20" s="112" t="n"/>
+      <c r="H20" s="133" t="n"/>
+      <c r="I20" s="38" t="n"/>
+      <c r="J20" s="134">
         <f>SUM(J18:J19)</f>
-        <v>78600000</v>
+        <v/>
       </c>
-      <c r="K20" s="43"/>
+      <c r="K20" s="135" t="n"/>
     </row>
-    <row r="21" spans="1:23" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="44"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="46"/>
-      <c r="H21" s="47"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="48"/>
+    <row r="21" ht="18" customFormat="1" customHeight="1" s="3">
+      <c r="A21" s="44" t="n"/>
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="45" t="n"/>
+      <c r="F21" s="45" t="n"/>
+      <c r="G21" s="46" t="n"/>
+      <c r="H21" s="136" t="n"/>
+      <c r="J21" s="127" t="n"/>
+      <c r="K21" s="127" t="n"/>
     </row>
-    <row r="22" spans="1:23" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E22" s="49" t="s">
-        <v>13</v>
+    <row r="22" ht="18" customFormat="1" customHeight="1" s="3">
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t>Trừ tạm ứng hoặc trả trước</t>
+        </is>
       </c>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="50">
+      <c r="F22" s="49" t="n"/>
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="137">
         <f>+VLOOKUP(L1,'[1]Dữ liệu'!A3:I942,9,0)</f>
-        <v>0</v>
+        <v/>
       </c>
-      <c r="K22" s="51"/>
-      <c r="N22" s="37"/>
+      <c r="K22" s="138" t="n"/>
+      <c r="N22" s="132" t="n"/>
     </row>
-    <row r="23" spans="1:23" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="53"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="48"/>
+    <row r="23" ht="18" customFormat="1" customHeight="1" s="3">
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="139" t="n"/>
+      <c r="J23" s="127" t="n"/>
+      <c r="K23" s="127" t="n"/>
     </row>
-    <row r="24" spans="1:23" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E24" s="49" t="s">
-        <v>14</v>
+    <row r="24" ht="18" customFormat="1" customHeight="1" s="3">
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhận  từ công ty </t>
+        </is>
       </c>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="55">
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="54" t="n"/>
+      <c r="J24" s="140">
         <f>+J20-J22</f>
-        <v>78600000</v>
+        <v/>
       </c>
-      <c r="K24" s="56"/>
+      <c r="K24" s="141" t="n"/>
     </row>
-    <row r="25" spans="1:23" s="3" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="59">
+    <row r="25" customFormat="1" s="3">
+      <c r="E25" s="57" t="n"/>
+      <c r="F25" s="57" t="n"/>
+      <c r="G25" s="57" t="n"/>
+      <c r="H25" s="142" t="n"/>
+      <c r="I25" s="143">
         <f>+I21-J23</f>
-        <v>0</v>
+        <v/>
       </c>
-      <c r="J25" s="60"/>
-      <c r="K25" s="61"/>
+      <c r="J25" s="144" t="n"/>
+      <c r="K25" s="145" t="n"/>
     </row>
-    <row r="26" spans="1:23" s="62" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="G26" s="76" t="s">
-        <v>30</v>
+    <row r="26" customFormat="1" s="62">
+      <c r="G26" s="76" t="inlineStr">
+        <is>
+          <t>Liên Sơn, ngày 21/05/2026</t>
+        </is>
       </c>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="63"/>
+      <c r="K26" s="146" t="n"/>
     </row>
-    <row r="27" spans="1:23" s="62" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="77" t="s">
-        <v>15</v>
+    <row r="27" ht="18.75" customFormat="1" customHeight="1" s="62">
+      <c r="A27" s="77" t="inlineStr">
+        <is>
+          <t>Tổng Giám Đốc</t>
+        </is>
       </c>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="78" t="s">
-        <v>16</v>
+      <c r="D27" s="78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Kế toán trưởng</t>
+        </is>
       </c>
-      <c r="E27" s="78"/>
-      <c r="F27" s="65" t="s">
-        <v>17</v>
+      <c r="F27" s="78" t="inlineStr">
+        <is>
+          <t>Cán bộ theo dõi</t>
+        </is>
       </c>
-      <c r="G27" s="77" t="s">
-        <v>18</v>
+      <c r="G27" s="77" t="inlineStr">
+        <is>
+          <t>Người đề nghị</t>
+        </is>
       </c>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="77"/>
-      <c r="K27" s="64"/>
+      <c r="K27" s="77" t="n"/>
     </row>
-    <row r="28" spans="1:23" s="62" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="65"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
+    <row r="28" customFormat="1" s="62">
+      <c r="D28" s="66" t="n"/>
+      <c r="E28" s="66" t="n"/>
+      <c r="F28" s="78" t="n"/>
+      <c r="I28" s="67" t="n"/>
+      <c r="J28" s="146" t="n"/>
+      <c r="K28" s="146" t="n"/>
     </row>
-    <row r="29" spans="1:23" s="62" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="67"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="63"/>
-      <c r="K29" s="63"/>
+    <row r="29" customFormat="1" s="62">
+      <c r="E29" s="68" t="n"/>
+      <c r="F29" s="68" t="n"/>
+      <c r="G29" s="68" t="n"/>
+      <c r="H29" s="67" t="n"/>
+      <c r="I29" s="67" t="n"/>
+      <c r="J29" s="146" t="n"/>
+      <c r="K29" s="146" t="n"/>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="I30" s="5"/>
-      <c r="N30" s="69"/>
+    <row r="30">
+      <c r="I30" s="103" t="n"/>
+      <c r="N30" s="147" t="n"/>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="I31" s="5"/>
-      <c r="N31" s="69"/>
+    <row r="31">
+      <c r="I31" s="103" t="n"/>
+      <c r="N31" s="147" t="n"/>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>19</v>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">         ………………….</t>
+        </is>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>20</v>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Nguyễn Văn Thuân</t>
+        </is>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>21</v>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Lê Thị Kim Thanh</t>
+        </is>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>22</v>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>………………….</t>
+        </is>
       </c>
-      <c r="G32" s="74" t="s">
-        <v>31</v>
+      <c r="G32" s="74" t="inlineStr">
+        <is>
+          <t>Lê Anh Huy</t>
+        </is>
       </c>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-      <c r="J32" s="74"/>
-      <c r="K32" s="14"/>
-      <c r="N32" s="69"/>
+      <c r="K32" s="74" t="n"/>
+      <c r="N32" s="147" t="n"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="14"/>
-      <c r="N33" s="69"/>
+    <row r="33">
+      <c r="G33" s="74" t="n"/>
+      <c r="K33" s="74" t="n"/>
+      <c r="N33" s="147" t="n"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F34" s="70"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="N34" s="69"/>
+    <row r="34">
+      <c r="F34" s="70" t="n"/>
+      <c r="G34" s="71" t="n"/>
+      <c r="H34" s="71" t="n"/>
+      <c r="I34" s="71" t="n"/>
+      <c r="J34" s="71" t="n"/>
+      <c r="K34" s="71" t="n"/>
+      <c r="N34" s="147" t="n"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" s="62"/>
-      <c r="B35" s="62"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="62"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="N35" s="69"/>
+    <row r="35">
+      <c r="A35" s="62" t="n"/>
+      <c r="B35" s="62" t="n"/>
+      <c r="C35" s="62" t="n"/>
+      <c r="D35" s="62" t="n"/>
+      <c r="E35" s="62" t="n"/>
+      <c r="F35" s="70" t="n"/>
+      <c r="G35" s="71" t="n"/>
+      <c r="H35" s="71" t="n"/>
+      <c r="I35" s="71" t="n"/>
+      <c r="J35" s="71" t="n"/>
+      <c r="K35" s="71" t="n"/>
+      <c r="N35" s="147" t="n"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F36" s="70"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="N36" s="69"/>
+    <row r="36">
+      <c r="F36" s="70" t="n"/>
+      <c r="G36" s="71" t="n"/>
+      <c r="H36" s="71" t="n"/>
+      <c r="I36" s="71" t="n"/>
+      <c r="J36" s="71" t="n"/>
+      <c r="K36" s="71" t="n"/>
+      <c r="N36" s="147" t="n"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F37" s="70"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="71"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
-      <c r="K37" s="71"/>
-      <c r="N37" s="69"/>
+    <row r="37">
+      <c r="F37" s="70" t="n"/>
+      <c r="G37" s="71" t="n"/>
+      <c r="H37" s="71" t="n"/>
+      <c r="I37" s="71" t="n"/>
+      <c r="J37" s="71" t="n"/>
+      <c r="K37" s="71" t="n"/>
+      <c r="N37" s="147" t="n"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F38" s="70"/>
-      <c r="G38" s="71"/>
-      <c r="H38" s="71"/>
-      <c r="I38" s="71"/>
-      <c r="J38" s="71"/>
-      <c r="K38" s="71"/>
-      <c r="N38" s="69"/>
+    <row r="38">
+      <c r="F38" s="70" t="n"/>
+      <c r="G38" s="71" t="n"/>
+      <c r="H38" s="71" t="n"/>
+      <c r="I38" s="71" t="n"/>
+      <c r="J38" s="71" t="n"/>
+      <c r="K38" s="71" t="n"/>
+      <c r="N38" s="147" t="n"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F39" s="70"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="71"/>
-      <c r="I39" s="71"/>
-      <c r="J39" s="71"/>
-      <c r="K39" s="71"/>
-      <c r="N39" s="69"/>
+    <row r="39">
+      <c r="F39" s="70" t="n"/>
+      <c r="G39" s="71" t="n"/>
+      <c r="H39" s="71" t="n"/>
+      <c r="I39" s="71" t="n"/>
+      <c r="J39" s="71" t="n"/>
+      <c r="K39" s="71" t="n"/>
+      <c r="N39" s="147" t="n"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F40" s="70"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="71"/>
-      <c r="K40" s="71"/>
-      <c r="N40" s="69"/>
+    <row r="40">
+      <c r="F40" s="70" t="n"/>
+      <c r="G40" s="71" t="n"/>
+      <c r="H40" s="71" t="n"/>
+      <c r="I40" s="71" t="n"/>
+      <c r="J40" s="71" t="n"/>
+      <c r="K40" s="71" t="n"/>
+      <c r="N40" s="147" t="n"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F41" s="70"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
+    <row r="41">
+      <c r="F41" s="70" t="n"/>
+      <c r="G41" s="71" t="n"/>
+      <c r="H41" s="71" t="n"/>
+      <c r="I41" s="71" t="n"/>
+      <c r="J41" s="71" t="n"/>
+      <c r="K41" s="71" t="n"/>
+      <c r="N41" s="103" t="n"/>
+      <c r="O41" s="103" t="n"/>
+      <c r="P41" s="103" t="n"/>
+      <c r="Q41" s="103" t="n"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F42" s="70"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="71"/>
-      <c r="I42" s="71"/>
-      <c r="J42" s="71"/>
-      <c r="K42" s="71"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
+    <row r="42">
+      <c r="F42" s="70" t="n"/>
+      <c r="G42" s="71" t="n"/>
+      <c r="H42" s="71" t="n"/>
+      <c r="I42" s="71" t="n"/>
+      <c r="J42" s="71" t="n"/>
+      <c r="K42" s="71" t="n"/>
+      <c r="N42" s="103" t="n"/>
+      <c r="O42" s="103" t="n"/>
+      <c r="P42" s="103" t="n"/>
+      <c r="Q42" s="103" t="n"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F43" s="70"/>
-      <c r="G43" s="71"/>
-      <c r="H43" s="71"/>
-      <c r="I43" s="71"/>
-      <c r="J43" s="71"/>
-      <c r="K43" s="71"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
+    <row r="43">
+      <c r="F43" s="70" t="n"/>
+      <c r="G43" s="71" t="n"/>
+      <c r="H43" s="71" t="n"/>
+      <c r="I43" s="71" t="n"/>
+      <c r="J43" s="71" t="n"/>
+      <c r="K43" s="71" t="n"/>
+      <c r="N43" s="103" t="n"/>
+      <c r="O43" s="103" t="n"/>
+      <c r="P43" s="103" t="n"/>
+      <c r="Q43" s="103" t="n"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F44" s="70"/>
-      <c r="G44" s="71"/>
-      <c r="H44" s="71"/>
-      <c r="I44" s="71"/>
-      <c r="J44" s="71"/>
-      <c r="K44" s="71"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
+    <row r="44">
+      <c r="F44" s="70" t="n"/>
+      <c r="G44" s="71" t="n"/>
+      <c r="H44" s="71" t="n"/>
+      <c r="I44" s="71" t="n"/>
+      <c r="J44" s="71" t="n"/>
+      <c r="K44" s="71" t="n"/>
+      <c r="N44" s="103" t="n"/>
+      <c r="O44" s="103" t="n"/>
+      <c r="P44" s="103" t="n"/>
+      <c r="Q44" s="103" t="n"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F45" s="70"/>
-      <c r="G45" s="71"/>
-      <c r="H45" s="71"/>
-      <c r="I45" s="71"/>
-      <c r="J45" s="71"/>
-      <c r="K45" s="71"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
+    <row r="45">
+      <c r="F45" s="70" t="n"/>
+      <c r="G45" s="71" t="n"/>
+      <c r="H45" s="71" t="n"/>
+      <c r="I45" s="71" t="n"/>
+      <c r="J45" s="71" t="n"/>
+      <c r="K45" s="71" t="n"/>
+      <c r="N45" s="103" t="n"/>
+      <c r="O45" s="103" t="n"/>
+      <c r="P45" s="103" t="n"/>
+      <c r="Q45" s="103" t="n"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F46" s="70"/>
-      <c r="G46" s="71"/>
-      <c r="H46" s="71"/>
-      <c r="I46" s="71"/>
-      <c r="J46" s="71"/>
-      <c r="K46" s="71"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
+    <row r="46">
+      <c r="F46" s="70" t="n"/>
+      <c r="G46" s="71" t="n"/>
+      <c r="H46" s="71" t="n"/>
+      <c r="I46" s="71" t="n"/>
+      <c r="J46" s="71" t="n"/>
+      <c r="K46" s="71" t="n"/>
+      <c r="N46" s="103" t="n"/>
+      <c r="O46" s="103" t="n"/>
+      <c r="P46" s="103" t="n"/>
+      <c r="Q46" s="103" t="n"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F47" s="70"/>
-      <c r="G47" s="71"/>
-      <c r="H47" s="71"/>
-      <c r="I47" s="71"/>
-      <c r="J47" s="71"/>
-      <c r="K47" s="71"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
+    <row r="47">
+      <c r="F47" s="70" t="n"/>
+      <c r="G47" s="71" t="n"/>
+      <c r="H47" s="71" t="n"/>
+      <c r="I47" s="71" t="n"/>
+      <c r="J47" s="71" t="n"/>
+      <c r="K47" s="71" t="n"/>
+      <c r="N47" s="103" t="n"/>
+      <c r="O47" s="103" t="n"/>
+      <c r="P47" s="103" t="n"/>
+      <c r="Q47" s="103" t="n"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="F48" s="70"/>
-      <c r="G48" s="71"/>
-      <c r="H48" s="71"/>
-      <c r="I48" s="71"/>
-      <c r="J48" s="71"/>
-      <c r="K48" s="71"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
+    <row r="48">
+      <c r="F48" s="70" t="n"/>
+      <c r="G48" s="71" t="n"/>
+      <c r="H48" s="71" t="n"/>
+      <c r="I48" s="71" t="n"/>
+      <c r="J48" s="71" t="n"/>
+      <c r="K48" s="71" t="n"/>
+      <c r="N48" s="103" t="n"/>
+      <c r="O48" s="103" t="n"/>
+      <c r="P48" s="103" t="n"/>
+      <c r="Q48" s="103" t="n"/>
     </row>
-    <row r="49" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="F49" s="70"/>
-      <c r="G49" s="71"/>
-      <c r="H49" s="71"/>
-      <c r="I49" s="71"/>
-      <c r="J49" s="71"/>
-      <c r="K49" s="71"/>
-      <c r="N49" s="5"/>
-      <c r="O49" s="5"/>
-      <c r="P49" s="5"/>
-      <c r="Q49" s="5"/>
+    <row r="49">
+      <c r="F49" s="70" t="n"/>
+      <c r="G49" s="71" t="n"/>
+      <c r="H49" s="71" t="n"/>
+      <c r="I49" s="71" t="n"/>
+      <c r="J49" s="71" t="n"/>
+      <c r="K49" s="71" t="n"/>
+      <c r="N49" s="103" t="n"/>
+      <c r="O49" s="103" t="n"/>
+      <c r="P49" s="103" t="n"/>
+      <c r="Q49" s="103" t="n"/>
     </row>
-    <row r="50" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="F50" s="70"/>
-      <c r="G50" s="71"/>
-      <c r="H50" s="71"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="71"/>
-      <c r="K50" s="71"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
+    <row r="50">
+      <c r="F50" s="70" t="n"/>
+      <c r="G50" s="71" t="n"/>
+      <c r="H50" s="71" t="n"/>
+      <c r="I50" s="71" t="n"/>
+      <c r="J50" s="71" t="n"/>
+      <c r="K50" s="71" t="n"/>
+      <c r="N50" s="103" t="n"/>
+      <c r="O50" s="103" t="n"/>
+      <c r="P50" s="103" t="n"/>
+      <c r="Q50" s="103" t="n"/>
     </row>
-    <row r="51" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="F51" s="70"/>
-      <c r="G51" s="71"/>
-      <c r="H51" s="71"/>
-      <c r="I51" s="71"/>
-      <c r="J51" s="71"/>
-      <c r="K51" s="71"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5"/>
+    <row r="51">
+      <c r="F51" s="70" t="n"/>
+      <c r="G51" s="71" t="n"/>
+      <c r="H51" s="71" t="n"/>
+      <c r="I51" s="71" t="n"/>
+      <c r="J51" s="71" t="n"/>
+      <c r="K51" s="71" t="n"/>
+      <c r="N51" s="103" t="n"/>
+      <c r="O51" s="103" t="n"/>
+      <c r="P51" s="103" t="n"/>
+      <c r="Q51" s="103" t="n"/>
     </row>
-    <row r="52" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="F52" s="70"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="71"/>
-      <c r="I52" s="71"/>
-      <c r="J52" s="71"/>
-      <c r="K52" s="71"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
+    <row r="52">
+      <c r="F52" s="70" t="n"/>
+      <c r="G52" s="71" t="n"/>
+      <c r="H52" s="71" t="n"/>
+      <c r="I52" s="71" t="n"/>
+      <c r="J52" s="71" t="n"/>
+      <c r="K52" s="71" t="n"/>
+      <c r="N52" s="103" t="n"/>
+      <c r="O52" s="103" t="n"/>
+      <c r="P52" s="103" t="n"/>
+      <c r="Q52" s="103" t="n"/>
     </row>
-    <row r="53" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="G53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="5"/>
-      <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
+    <row r="53">
+      <c r="G53" s="103" t="n"/>
+      <c r="I53" s="103" t="n"/>
+      <c r="N53" s="103" t="n"/>
+      <c r="O53" s="103" t="n"/>
+      <c r="P53" s="103" t="n"/>
+      <c r="Q53" s="103" t="n"/>
     </row>
-    <row r="54" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="G54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
+    <row r="54">
+      <c r="G54" s="103" t="n"/>
+      <c r="I54" s="103" t="n"/>
+      <c r="N54" s="103" t="n"/>
+      <c r="O54" s="103" t="n"/>
+      <c r="P54" s="103" t="n"/>
+      <c r="Q54" s="103" t="n"/>
     </row>
-    <row r="55" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="G55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="5"/>
+    <row r="55">
+      <c r="G55" s="103" t="n"/>
+      <c r="I55" s="103" t="n"/>
+      <c r="N55" s="103" t="n"/>
+      <c r="O55" s="103" t="n"/>
+      <c r="P55" s="103" t="n"/>
+      <c r="Q55" s="103" t="n"/>
     </row>
-    <row r="56" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-      <c r="P56" s="5"/>
-      <c r="Q56" s="5"/>
+    <row r="56">
+      <c r="N56" s="103" t="n"/>
+      <c r="O56" s="103" t="n"/>
+      <c r="P56" s="103" t="n"/>
+      <c r="Q56" s="103" t="n"/>
     </row>
-    <row r="57" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="N57" s="5"/>
-      <c r="O57" s="5"/>
-      <c r="P57" s="5"/>
-      <c r="Q57" s="5"/>
+    <row r="57">
+      <c r="H57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+      <c r="N57" s="103" t="n"/>
+      <c r="O57" s="103" t="n"/>
+      <c r="P57" s="103" t="n"/>
+      <c r="Q57" s="103" t="n"/>
     </row>
-    <row r="58" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="N58" s="5"/>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
+    <row r="58">
+      <c r="H58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="N58" s="103" t="n"/>
+      <c r="O58" s="103" t="n"/>
+      <c r="P58" s="103" t="n"/>
+      <c r="Q58" s="103" t="n"/>
     </row>
-    <row r="59" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="N59" s="5"/>
-      <c r="O59" s="5"/>
-      <c r="P59" s="5"/>
-      <c r="Q59" s="5"/>
+    <row r="59">
+      <c r="H59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+      <c r="N59" s="103" t="n"/>
+      <c r="O59" s="103" t="n"/>
+      <c r="P59" s="103" t="n"/>
+      <c r="Q59" s="103" t="n"/>
     </row>
-    <row r="60" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
+    <row r="60">
+      <c r="H60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="N60" s="103" t="n"/>
+      <c r="O60" s="103" t="n"/>
+      <c r="P60" s="103" t="n"/>
+      <c r="Q60" s="103" t="n"/>
     </row>
-    <row r="61" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="N61" s="5"/>
-      <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
-      <c r="Q61" s="5"/>
+    <row r="61">
+      <c r="H61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="N61" s="103" t="n"/>
+      <c r="O61" s="103" t="n"/>
+      <c r="P61" s="103" t="n"/>
+      <c r="Q61" s="103" t="n"/>
     </row>
-    <row r="62" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
+    <row r="62">
+      <c r="H62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
+      <c r="N62" s="103" t="n"/>
+      <c r="O62" s="103" t="n"/>
+      <c r="P62" s="103" t="n"/>
+      <c r="Q62" s="103" t="n"/>
     </row>
-    <row r="63" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="N63" s="69"/>
+    <row r="63">
+      <c r="H63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+      <c r="N63" s="147" t="n"/>
     </row>
-    <row r="64" spans="6:17" x14ac:dyDescent="0.2">
-      <c r="H64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="N64" s="5"/>
+    <row r="64">
+      <c r="H64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="N64" s="103" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="26">
     <mergeCell ref="E19:G19"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="E20:G20"/>
     <mergeCell ref="G26:J26"/>
     <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="D27:E27"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="G27:J27"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E20:G20"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hướng dẫn sử dụng" prompt="___________________x000a__x000a_Lựa chọn phương thức_x000a_thanh toán." sqref="G9 JD9 SZ9 ACV9 AMR9 AWN9 BGJ9 BQF9 CAB9 CJX9 CTT9 DDP9 DNL9 DXH9 EHD9 EQZ9 FAV9 FKR9 FUN9 GEJ9 GOF9 GYB9 HHX9 HRT9 IBP9 ILL9 IVH9 JFD9 JOZ9 JYV9 KIR9 KSN9 LCJ9 LMF9 LWB9 MFX9 MPT9 MZP9 NJL9 NTH9 ODD9 OMZ9 OWV9 PGR9 PQN9 QAJ9 QKF9 QUB9 RDX9 RNT9 RXP9 SHL9 SRH9 TBD9 TKZ9 TUV9 UER9 UON9 UYJ9 VIF9 VSB9 WBX9 WLT9 WVP9 G65534 JD65534 SZ65534 ACV65534 AMR65534 AWN65534 BGJ65534 BQF65534 CAB65534 CJX65534 CTT65534 DDP65534 DNL65534 DXH65534 EHD65534 EQZ65534 FAV65534 FKR65534 FUN65534 GEJ65534 GOF65534 GYB65534 HHX65534 HRT65534 IBP65534 ILL65534 IVH65534 JFD65534 JOZ65534 JYV65534 KIR65534 KSN65534 LCJ65534 LMF65534 LWB65534 MFX65534 MPT65534 MZP65534 NJL65534 NTH65534 ODD65534 OMZ65534 OWV65534 PGR65534 PQN65534 QAJ65534 QKF65534 QUB65534 RDX65534 RNT65534 RXP65534 SHL65534 SRH65534 TBD65534 TKZ65534 TUV65534 UER65534 UON65534 UYJ65534 VIF65534 VSB65534 WBX65534 WLT65534 WVP65534 G131070 JD131070 SZ131070 ACV131070 AMR131070 AWN131070 BGJ131070 BQF131070 CAB131070 CJX131070 CTT131070 DDP131070 DNL131070 DXH131070 EHD131070 EQZ131070 FAV131070 FKR131070 FUN131070 GEJ131070 GOF131070 GYB131070 HHX131070 HRT131070 IBP131070 ILL131070 IVH131070 JFD131070 JOZ131070 JYV131070 KIR131070 KSN131070 LCJ131070 LMF131070 LWB131070 MFX131070 MPT131070 MZP131070 NJL131070 NTH131070 ODD131070 OMZ131070 OWV131070 PGR131070 PQN131070 QAJ131070 QKF131070 QUB131070 RDX131070 RNT131070 RXP131070 SHL131070 SRH131070 TBD131070 TKZ131070 TUV131070 UER131070 UON131070 UYJ131070 VIF131070 VSB131070 WBX131070 WLT131070 WVP131070 G196606 JD196606 SZ196606 ACV196606 AMR196606 AWN196606 BGJ196606 BQF196606 CAB196606 CJX196606 CTT196606 DDP196606 DNL196606 DXH196606 EHD196606 EQZ196606 FAV196606 FKR196606 FUN196606 GEJ196606 GOF196606 GYB196606 HHX196606 HRT196606 IBP196606 ILL196606 IVH196606 JFD196606 JOZ196606 JYV196606 KIR196606 KSN196606 LCJ196606 LMF196606 LWB196606 MFX196606 MPT196606 MZP196606 NJL196606 NTH196606 ODD196606 OMZ196606 OWV196606 PGR196606 PQN196606 QAJ196606 QKF196606 QUB196606 RDX196606 RNT196606 RXP196606 SHL196606 SRH196606 TBD196606 TKZ196606 TUV196606 UER196606 UON196606 UYJ196606 VIF196606 VSB196606 WBX196606 WLT196606 WVP196606 G262142 JD262142 SZ262142 ACV262142 AMR262142 AWN262142 BGJ262142 BQF262142 CAB262142 CJX262142 CTT262142 DDP262142 DNL262142 DXH262142 EHD262142 EQZ262142 FAV262142 FKR262142 FUN262142 GEJ262142 GOF262142 GYB262142 HHX262142 HRT262142 IBP262142 ILL262142 IVH262142 JFD262142 JOZ262142 JYV262142 KIR262142 KSN262142 LCJ262142 LMF262142 LWB262142 MFX262142 MPT262142 MZP262142 NJL262142 NTH262142 ODD262142 OMZ262142 OWV262142 PGR262142 PQN262142 QAJ262142 QKF262142 QUB262142 RDX262142 RNT262142 RXP262142 SHL262142 SRH262142 TBD262142 TKZ262142 TUV262142 UER262142 UON262142 UYJ262142 VIF262142 VSB262142 WBX262142 WLT262142 WVP262142 G327678 JD327678 SZ327678 ACV327678 AMR327678 AWN327678 BGJ327678 BQF327678 CAB327678 CJX327678 CTT327678 DDP327678 DNL327678 DXH327678 EHD327678 EQZ327678 FAV327678 FKR327678 FUN327678 GEJ327678 GOF327678 GYB327678 HHX327678 HRT327678 IBP327678 ILL327678 IVH327678 JFD327678 JOZ327678 JYV327678 KIR327678 KSN327678 LCJ327678 LMF327678 LWB327678 MFX327678 MPT327678 MZP327678 NJL327678 NTH327678 ODD327678 OMZ327678 OWV327678 PGR327678 PQN327678 QAJ327678 QKF327678 QUB327678 RDX327678 RNT327678 RXP327678 SHL327678 SRH327678 TBD327678 TKZ327678 TUV327678 UER327678 UON327678 UYJ327678 VIF327678 VSB327678 WBX327678 WLT327678 WVP327678 G393214 JD393214 SZ393214 ACV393214 AMR393214 AWN393214 BGJ393214 BQF393214 CAB393214 CJX393214 CTT393214 DDP393214 DNL393214 DXH393214 EHD393214 EQZ393214 FAV393214 FKR393214 FUN393214 GEJ393214 GOF393214 GYB393214 HHX393214 HRT393214 IBP393214 ILL393214 IVH393214 JFD393214 JOZ393214 JYV393214 KIR393214 KSN393214 LCJ393214 LMF393214 LWB393214 MFX393214 MPT393214 MZP393214 NJL393214 NTH393214 ODD393214 OMZ393214 OWV393214 PGR393214 PQN393214 QAJ393214 QKF393214 QUB393214 RDX393214 RNT393214 RXP393214 SHL393214 SRH393214 TBD393214 TKZ393214 TUV393214 UER393214 UON393214 UYJ393214 VIF393214 VSB393214 WBX393214 WLT393214 WVP393214 G458750 JD458750 SZ458750 ACV458750 AMR458750 AWN458750 BGJ458750 BQF458750 CAB458750 CJX458750 CTT458750 DDP458750 DNL458750 DXH458750 EHD458750 EQZ458750 FAV458750 FKR458750 FUN458750 GEJ458750 GOF458750 GYB458750 HHX458750 HRT458750 IBP458750 ILL458750 IVH458750 JFD458750 JOZ458750 JYV458750 KIR458750 KSN458750 LCJ458750 LMF458750 LWB458750 MFX458750 MPT458750 MZP458750 NJL458750 NTH458750 ODD458750 OMZ458750 OWV458750 PGR458750 PQN458750 QAJ458750 QKF458750 QUB458750 RDX458750 RNT458750 RXP458750 SHL458750 SRH458750 TBD458750 TKZ458750 TUV458750 UER458750 UON458750 UYJ458750 VIF458750 VSB458750 WBX458750 WLT458750 WVP458750 G524286 JD524286 SZ524286 ACV524286 AMR524286 AWN524286 BGJ524286 BQF524286 CAB524286 CJX524286 CTT524286 DDP524286 DNL524286 DXH524286 EHD524286 EQZ524286 FAV524286 FKR524286 FUN524286 GEJ524286 GOF524286 GYB524286 HHX524286 HRT524286 IBP524286 ILL524286 IVH524286 JFD524286 JOZ524286 JYV524286 KIR524286 KSN524286 LCJ524286 LMF524286 LWB524286 MFX524286 MPT524286 MZP524286 NJL524286 NTH524286 ODD524286 OMZ524286 OWV524286 PGR524286 PQN524286 QAJ524286 QKF524286 QUB524286 RDX524286 RNT524286 RXP524286 SHL524286 SRH524286 TBD524286 TKZ524286 TUV524286 UER524286 UON524286 UYJ524286 VIF524286 VSB524286 WBX524286 WLT524286 WVP524286 G589822 JD589822 SZ589822 ACV589822 AMR589822 AWN589822 BGJ589822 BQF589822 CAB589822 CJX589822 CTT589822 DDP589822 DNL589822 DXH589822 EHD589822 EQZ589822 FAV589822 FKR589822 FUN589822 GEJ589822 GOF589822 GYB589822 HHX589822 HRT589822 IBP589822 ILL589822 IVH589822 JFD589822 JOZ589822 JYV589822 KIR589822 KSN589822 LCJ589822 LMF589822 LWB589822 MFX589822 MPT589822 MZP589822 NJL589822 NTH589822 ODD589822 OMZ589822 OWV589822 PGR589822 PQN589822 QAJ589822 QKF589822 QUB589822 RDX589822 RNT589822 RXP589822 SHL589822 SRH589822 TBD589822 TKZ589822 TUV589822 UER589822 UON589822 UYJ589822 VIF589822 VSB589822 WBX589822 WLT589822 WVP589822 G655358 JD655358 SZ655358 ACV655358 AMR655358 AWN655358 BGJ655358 BQF655358 CAB655358 CJX655358 CTT655358 DDP655358 DNL655358 DXH655358 EHD655358 EQZ655358 FAV655358 FKR655358 FUN655358 GEJ655358 GOF655358 GYB655358 HHX655358 HRT655358 IBP655358 ILL655358 IVH655358 JFD655358 JOZ655358 JYV655358 KIR655358 KSN655358 LCJ655358 LMF655358 LWB655358 MFX655358 MPT655358 MZP655358 NJL655358 NTH655358 ODD655358 OMZ655358 OWV655358 PGR655358 PQN655358 QAJ655358 QKF655358 QUB655358 RDX655358 RNT655358 RXP655358 SHL655358 SRH655358 TBD655358 TKZ655358 TUV655358 UER655358 UON655358 UYJ655358 VIF655358 VSB655358 WBX655358 WLT655358 WVP655358 G720894 JD720894 SZ720894 ACV720894 AMR720894 AWN720894 BGJ720894 BQF720894 CAB720894 CJX720894 CTT720894 DDP720894 DNL720894 DXH720894 EHD720894 EQZ720894 FAV720894 FKR720894 FUN720894 GEJ720894 GOF720894 GYB720894 HHX720894 HRT720894 IBP720894 ILL720894 IVH720894 JFD720894 JOZ720894 JYV720894 KIR720894 KSN720894 LCJ720894 LMF720894 LWB720894 MFX720894 MPT720894 MZP720894 NJL720894 NTH720894 ODD720894 OMZ720894 OWV720894 PGR720894 PQN720894 QAJ720894 QKF720894 QUB720894 RDX720894 RNT720894 RXP720894 SHL720894 SRH720894 TBD720894 TKZ720894 TUV720894 UER720894 UON720894 UYJ720894 VIF720894 VSB720894 WBX720894 WLT720894 WVP720894 G786430 JD786430 SZ786430 ACV786430 AMR786430 AWN786430 BGJ786430 BQF786430 CAB786430 CJX786430 CTT786430 DDP786430 DNL786430 DXH786430 EHD786430 EQZ786430 FAV786430 FKR786430 FUN786430 GEJ786430 GOF786430 GYB786430 HHX786430 HRT786430 IBP786430 ILL786430 IVH786430 JFD786430 JOZ786430 JYV786430 KIR786430 KSN786430 LCJ786430 LMF786430 LWB786430 MFX786430 MPT786430 MZP786430 NJL786430 NTH786430 ODD786430 OMZ786430 OWV786430 PGR786430 PQN786430 QAJ786430 QKF786430 QUB786430 RDX786430 RNT786430 RXP786430 SHL786430 SRH786430 TBD786430 TKZ786430 TUV786430 UER786430 UON786430 UYJ786430 VIF786430 VSB786430 WBX786430 WLT786430 WVP786430 G851966 JD851966 SZ851966 ACV851966 AMR851966 AWN851966 BGJ851966 BQF851966 CAB851966 CJX851966 CTT851966 DDP851966 DNL851966 DXH851966 EHD851966 EQZ851966 FAV851966 FKR851966 FUN851966 GEJ851966 GOF851966 GYB851966 HHX851966 HRT851966 IBP851966 ILL851966 IVH851966 JFD851966 JOZ851966 JYV851966 KIR851966 KSN851966 LCJ851966 LMF851966 LWB851966 MFX851966 MPT851966 MZP851966 NJL851966 NTH851966 ODD851966 OMZ851966 OWV851966 PGR851966 PQN851966 QAJ851966 QKF851966 QUB851966 RDX851966 RNT851966 RXP851966 SHL851966 SRH851966 TBD851966 TKZ851966 TUV851966 UER851966 UON851966 UYJ851966 VIF851966 VSB851966 WBX851966 WLT851966 WVP851966 G917502 JD917502 SZ917502 ACV917502 AMR917502 AWN917502 BGJ917502 BQF917502 CAB917502 CJX917502 CTT917502 DDP917502 DNL917502 DXH917502 EHD917502 EQZ917502 FAV917502 FKR917502 FUN917502 GEJ917502 GOF917502 GYB917502 HHX917502 HRT917502 IBP917502 ILL917502 IVH917502 JFD917502 JOZ917502 JYV917502 KIR917502 KSN917502 LCJ917502 LMF917502 LWB917502 MFX917502 MPT917502 MZP917502 NJL917502 NTH917502 ODD917502 OMZ917502 OWV917502 PGR917502 PQN917502 QAJ917502 QKF917502 QUB917502 RDX917502 RNT917502 RXP917502 SHL917502 SRH917502 TBD917502 TKZ917502 TUV917502 UER917502 UON917502 UYJ917502 VIF917502 VSB917502 WBX917502 WLT917502 WVP917502 G983038 JD983038 SZ983038 ACV983038 AMR983038 AWN983038 BGJ983038 BQF983038 CAB983038 CJX983038 CTT983038 DDP983038 DNL983038 DXH983038 EHD983038 EQZ983038 FAV983038 FKR983038 FUN983038 GEJ983038 GOF983038 GYB983038 HHX983038 HRT983038 IBP983038 ILL983038 IVH983038 JFD983038 JOZ983038 JYV983038 KIR983038 KSN983038 LCJ983038 LMF983038 LWB983038 MFX983038 MPT983038 MZP983038 NJL983038 NTH983038 ODD983038 OMZ983038 OWV983038 PGR983038 PQN983038 QAJ983038 QKF983038 QUB983038 RDX983038 RNT983038 RXP983038 SHL983038 SRH983038 TBD983038 TKZ983038 TUV983038 UER983038 UON983038 UYJ983038 VIF983038 VSB983038 WBX983038 WLT983038 WVP983038" xr:uid="{83FC1A7C-D82A-4119-9972-901FE818F988}">
+    <dataValidation sqref="G9 G65534 G131070 G196606 G262142 G327678 G393214 G458750 G524286 G589822 G655358 G720894 G786430 G851966 G917502 G983038 JD9 JD65534 JD131070 JD196606 JD262142 JD327678 JD393214 JD458750 JD524286 JD589822 JD655358 JD720894 JD786430 JD851966 JD917502 JD983038 SZ9 SZ65534 SZ131070 SZ196606 SZ262142 SZ327678 SZ393214 SZ458750 SZ524286 SZ589822 SZ655358 SZ720894 SZ786430 SZ851966 SZ917502 SZ983038 ACV9 ACV65534 ACV131070 ACV196606 ACV262142 ACV327678 ACV393214 ACV458750 ACV524286 ACV589822 ACV655358 ACV720894 ACV786430 ACV851966 ACV917502 ACV983038 AMR9 AMR65534 AMR131070 AMR196606 AMR262142 AMR327678 AMR393214 AMR458750 AMR524286 AMR589822 AMR655358 AMR720894 AMR786430 AMR851966 AMR917502 AMR983038 AWN9 AWN65534 AWN131070 AWN196606 AWN262142 AWN327678 AWN393214 AWN458750 AWN524286 AWN589822 AWN655358 AWN720894 AWN786430 AWN851966 AWN917502 AWN983038 BGJ9 BGJ65534 BGJ131070 BGJ196606 BGJ262142 BGJ327678 BGJ393214 BGJ458750 BGJ524286 BGJ589822 BGJ655358 BGJ720894 BGJ786430 BGJ851966 BGJ917502 BGJ983038 BQF9 BQF65534 BQF131070 BQF196606 BQF262142 BQF327678 BQF393214 BQF458750 BQF524286 BQF589822 BQF655358 BQF720894 BQF786430 BQF851966 BQF917502 BQF983038 CAB9 CAB65534 CAB131070 CAB196606 CAB262142 CAB327678 CAB393214 CAB458750 CAB524286 CAB589822 CAB655358 CAB720894 CAB786430 CAB851966 CAB917502 CAB983038 CJX9 CJX65534 CJX131070 CJX196606 CJX262142 CJX327678 CJX393214 CJX458750 CJX524286 CJX589822 CJX655358 CJX720894 CJX786430 CJX851966 CJX917502 CJX983038 CTT9 CTT65534 CTT131070 CTT196606 CTT262142 CTT327678 CTT393214 CTT458750 CTT524286 CTT589822 CTT655358 CTT720894 CTT786430 CTT851966 CTT917502 CTT983038 DDP9 DDP65534 DDP131070 DDP196606 DDP262142 DDP327678 DDP393214 DDP458750 DDP524286 DDP589822 DDP655358 DDP720894 DDP786430 DDP851966 DDP917502 DDP983038 DNL9 DNL65534 DNL131070 DNL196606 DNL262142 DNL327678 DNL393214 DNL458750 DNL524286 DNL589822 DNL655358 DNL720894 DNL786430 DNL851966 DNL917502 DNL983038 DXH9 DXH65534 DXH131070 DXH196606 DXH262142 DXH327678 DXH393214 DXH458750 DXH524286 DXH589822 DXH655358 DXH720894 DXH786430 DXH851966 DXH917502 DXH983038 EHD9 EHD65534 EHD131070 EHD196606 EHD262142 EHD327678 EHD393214 EHD458750 EHD524286 EHD589822 EHD655358 EHD720894 EHD786430 EHD851966 EHD917502 EHD983038 EQZ9 EQZ65534 EQZ131070 EQZ196606 EQZ262142 EQZ327678 EQZ393214 EQZ458750 EQZ524286 EQZ589822 EQZ655358 EQZ720894 EQZ786430 EQZ851966 EQZ917502 EQZ983038 FAV9 FAV65534 FAV131070 FAV196606 FAV262142 FAV327678 FAV393214 FAV458750 FAV524286 FAV589822 FAV655358 FAV720894 FAV786430 FAV851966 FAV917502 FAV983038 FKR9 FKR65534 FKR131070 FKR196606 FKR262142 FKR327678 FKR393214 FKR458750 FKR524286 FKR589822 FKR655358 FKR720894 FKR786430 FKR851966 FKR917502 FKR983038 FUN9 FUN65534 FUN131070 FUN196606 FUN262142 FUN327678 FUN393214 FUN458750 FUN524286 FUN589822 FUN655358 FUN720894 FUN786430 FUN851966 FUN917502 FUN983038 GEJ9 GEJ65534 GEJ131070 GEJ196606 GEJ262142 GEJ327678 GEJ393214 GEJ458750 GEJ524286 GEJ589822 GEJ655358 GEJ720894 GEJ786430 GEJ851966 GEJ917502 GEJ983038 GOF9 GOF65534 GOF131070 GOF196606 GOF262142 GOF327678 GOF393214 GOF458750 GOF524286 GOF589822 GOF655358 GOF720894 GOF786430 GOF851966 GOF917502 GOF983038 GYB9 GYB65534 GYB131070 GYB196606 GYB262142 GYB327678 GYB393214 GYB458750 GYB524286 GYB589822 GYB655358 GYB720894 GYB786430 GYB851966 GYB917502 GYB983038 HHX9 HHX65534 HHX131070 HHX196606 HHX262142 HHX327678 HHX393214 HHX458750 HHX524286 HHX589822 HHX655358 HHX720894 HHX786430 HHX851966 HHX917502 HHX983038 HRT9 HRT65534 HRT131070 HRT196606 HRT262142 HRT327678 HRT393214 HRT458750 HRT524286 HRT589822 HRT655358 HRT720894 HRT786430 HRT851966 HRT917502 HRT983038 IBP9 IBP65534 IBP131070 IBP196606 IBP262142 IBP327678 IBP393214 IBP458750 IBP524286 IBP589822 IBP655358 IBP720894 IBP786430 IBP851966 IBP917502 IBP983038 ILL9 ILL65534 ILL131070 ILL196606 ILL262142 ILL327678 ILL393214 ILL458750 ILL524286 ILL589822 ILL655358 ILL720894 ILL786430 ILL851966 ILL917502 ILL983038 IVH9 IVH65534 IVH131070 IVH196606 IVH262142 IVH327678 IVH393214 IVH458750 IVH524286 IVH589822 IVH655358 IVH720894 IVH786430 IVH851966 IVH917502 IVH983038 JFD9 JFD65534 JFD131070 JFD196606 JFD262142 JFD327678 JFD393214 JFD458750 JFD524286 JFD589822 JFD655358 JFD720894 JFD786430 JFD851966 JFD917502 JFD983038 JOZ9 JOZ65534 JOZ131070 JOZ196606 JOZ262142 JOZ327678 JOZ393214 JOZ458750 JOZ524286 JOZ589822 JOZ655358 JOZ720894 JOZ786430 JOZ851966 JOZ917502 JOZ983038 JYV9 JYV65534 JYV131070 JYV196606 JYV262142 JYV327678 JYV393214 JYV458750 JYV524286 JYV589822 JYV655358 JYV720894 JYV786430 JYV851966 JYV917502 JYV983038 KIR9 KIR65534 KIR131070 KIR196606 KIR262142 KIR327678 KIR393214 KIR458750 KIR524286 KIR589822 KIR655358 KIR720894 KIR786430 KIR851966 KIR917502 KIR983038 KSN9 KSN65534 KSN131070 KSN196606 KSN262142 KSN327678 KSN393214 KSN458750 KSN524286 KSN589822 KSN655358 KSN720894 KSN786430 KSN851966 KSN917502 KSN983038 LCJ9 LCJ65534 LCJ131070 LCJ196606 LCJ262142 LCJ327678 LCJ393214 LCJ458750 LCJ524286 LCJ589822 LCJ655358 LCJ720894 LCJ786430 LCJ851966 LCJ917502 LCJ983038 LMF9 LMF65534 LMF131070 LMF196606 LMF262142 LMF327678 LMF393214 LMF458750 LMF524286 LMF589822 LMF655358 LMF720894 LMF786430 LMF851966 LMF917502 LMF983038 LWB9 LWB65534 LWB131070 LWB196606 LWB262142 LWB327678 LWB393214 LWB458750 LWB524286 LWB589822 LWB655358 LWB720894 LWB786430 LWB851966 LWB917502 LWB983038 MFX9 MFX65534 MFX131070 MFX196606 MFX262142 MFX327678 MFX393214 MFX458750 MFX524286 MFX589822 MFX655358 MFX720894 MFX786430 MFX851966 MFX917502 MFX983038 MPT9 MPT65534 MPT131070 MPT196606 MPT262142 MPT327678 MPT393214 MPT458750 MPT524286 MPT589822 MPT655358 MPT720894 MPT786430 MPT851966 MPT917502 MPT983038 MZP9 MZP65534 MZP131070 MZP196606 MZP262142 MZP327678 MZP393214 MZP458750 MZP524286 MZP589822 MZP655358 MZP720894 MZP786430 MZP851966 MZP917502 MZP983038 NJL9 NJL65534 NJL131070 NJL196606 NJL262142 NJL327678 NJL393214 NJL458750 NJL524286 NJL589822 NJL655358 NJL720894 NJL786430 NJL851966 NJL917502 NJL983038 NTH9 NTH65534 NTH131070 NTH196606 NTH262142 NTH327678 NTH393214 NTH458750 NTH524286 NTH589822 NTH655358 NTH720894 NTH786430 NTH851966 NTH917502 NTH983038 ODD9 ODD65534 ODD131070 ODD196606 ODD262142 ODD327678 ODD393214 ODD458750 ODD524286 ODD589822 ODD655358 ODD720894 ODD786430 ODD851966 ODD917502 ODD983038 OMZ9 OMZ65534 OMZ131070 OMZ196606 OMZ262142 OMZ327678 OMZ393214 OMZ458750 OMZ524286 OMZ589822 OMZ655358 OMZ720894 OMZ786430 OMZ851966 OMZ917502 OMZ983038 OWV9 OWV65534 OWV131070 OWV196606 OWV262142 OWV327678 OWV393214 OWV458750 OWV524286 OWV589822 OWV655358 OWV720894 OWV786430 OWV851966 OWV917502 OWV983038 PGR9 PGR65534 PGR131070 PGR196606 PGR262142 PGR327678 PGR393214 PGR458750 PGR524286 PGR589822 PGR655358 PGR720894 PGR786430 PGR851966 PGR917502 PGR983038 PQN9 PQN65534 PQN131070 PQN196606 PQN262142 PQN327678 PQN393214 PQN458750 PQN524286 PQN589822 PQN655358 PQN720894 PQN786430 PQN851966 PQN917502 PQN983038 QAJ9 QAJ65534 QAJ131070 QAJ196606 QAJ262142 QAJ327678 QAJ393214 QAJ458750 QAJ524286 QAJ589822 QAJ655358 QAJ720894 QAJ786430 QAJ851966 QAJ917502 QAJ983038 QKF9 QKF65534 QKF131070 QKF196606 QKF262142 QKF327678 QKF393214 QKF458750 QKF524286 QKF589822 QKF655358 QKF720894 QKF786430 QKF851966 QKF917502 QKF983038 QUB9 QUB65534 QUB131070 QUB196606 QUB262142 QUB327678 QUB393214 QUB458750 QUB524286 QUB589822 QUB655358 QUB720894 QUB786430 QUB851966 QUB917502 QUB983038 RDX9 RDX65534 RDX131070 RDX196606 RDX262142 RDX327678 RDX393214 RDX458750 RDX524286 RDX589822 RDX655358 RDX720894 RDX786430 RDX851966 RDX917502 RDX983038 RNT9 RNT65534 RNT131070 RNT196606 RNT262142 RNT327678 RNT393214 RNT458750 RNT524286 RNT589822 RNT655358 RNT720894 RNT786430 RNT851966 RNT917502 RNT983038 RXP9 RXP65534 RXP131070 RXP196606 RXP262142 RXP327678 RXP393214 RXP458750 RXP524286 RXP589822 RXP655358 RXP720894 RXP786430 RXP851966 RXP917502 RXP983038 SHL9 SHL65534 SHL131070 SHL196606 SHL262142 SHL327678 SHL393214 SHL458750 SHL524286 SHL589822 SHL655358 SHL720894 SHL786430 SHL851966 SHL917502 SHL983038 SRH9 SRH65534 SRH131070 SRH196606 SRH262142 SRH327678 SRH393214 SRH458750 SRH524286 SRH589822 SRH655358 SRH720894 SRH786430 SRH851966 SRH917502 SRH983038 TBD9 TBD65534 TBD131070 TBD196606 TBD262142 TBD327678 TBD393214 TBD458750 TBD524286 TBD589822 TBD655358 TBD720894 TBD786430 TBD851966 TBD917502 TBD983038 TKZ9 TKZ65534 TKZ131070 TKZ196606 TKZ262142 TKZ327678 TKZ393214 TKZ458750 TKZ524286 TKZ589822 TKZ655358 TKZ720894 TKZ786430 TKZ851966 TKZ917502 TKZ983038 TUV9 TUV65534 TUV131070 TUV196606 TUV262142 TUV327678 TUV393214 TUV458750 TUV524286 TUV589822 TUV655358 TUV720894 TUV786430 TUV851966 TUV917502 TUV983038 UER9 UER65534 UER131070 UER196606 UER262142 UER327678 UER393214 UER458750 UER524286 UER589822 UER655358 UER720894 UER786430 UER851966 UER917502 UER983038 UON9 UON65534 UON131070 UON196606 UON262142 UON327678 UON393214 UON458750 UON524286 UON589822 UON655358 UON720894 UON786430 UON851966 UON917502 UON983038 UYJ9 UYJ65534 UYJ131070 UYJ196606 UYJ262142 UYJ327678 UYJ393214 UYJ458750 UYJ524286 UYJ589822 UYJ655358 UYJ720894 UYJ786430 UYJ851966 UYJ917502 UYJ983038 VIF9 VIF65534 VIF131070 VIF196606 VIF262142 VIF327678 VIF393214 VIF458750 VIF524286 VIF589822 VIF655358 VIF720894 VIF786430 VIF851966 VIF917502 VIF983038 VSB9 VSB65534 VSB131070 VSB196606 VSB262142 VSB327678 VSB393214 VSB458750 VSB524286 VSB589822 VSB655358 VSB720894 VSB786430 VSB851966 VSB917502 VSB983038 WBX9 WBX65534 WBX131070 WBX196606 WBX262142 WBX327678 WBX393214 WBX458750 WBX524286 WBX589822 WBX655358 WBX720894 WBX786430 WBX851966 WBX917502 WBX983038 WLT9 WLT65534 WLT131070 WLT196606 WLT262142 WLT327678 WLT393214 WLT458750 WLT524286 WLT589822 WLT655358 WLT720894 WLT786430 WLT851966 WLT917502 WLT983038 WVP9 WVP65534 WVP131070 WVP196606 WVP262142 WVP327678 WVP393214 WVP458750 WVP524286 WVP589822 WVP655358 WVP720894 WVP786430 WVP851966 WVP917502 WVP983038" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Hướng dẫn sử dụng" prompt="___________________x000a__x000a_Lựa chọn phương thức_x000a_thanh toán." type="list">
       <formula1>"Tiền mặt, Chuyển khoản"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hướng dẫn sử dụng" prompt="____________________x000a__x000a_Lựa chọn đơn vị tiền tệ" sqref="D9 JA9 SW9 ACS9 AMO9 AWK9 BGG9 BQC9 BZY9 CJU9 CTQ9 DDM9 DNI9 DXE9 EHA9 EQW9 FAS9 FKO9 FUK9 GEG9 GOC9 GXY9 HHU9 HRQ9 IBM9 ILI9 IVE9 JFA9 JOW9 JYS9 KIO9 KSK9 LCG9 LMC9 LVY9 MFU9 MPQ9 MZM9 NJI9 NTE9 ODA9 OMW9 OWS9 PGO9 PQK9 QAG9 QKC9 QTY9 RDU9 RNQ9 RXM9 SHI9 SRE9 TBA9 TKW9 TUS9 UEO9 UOK9 UYG9 VIC9 VRY9 WBU9 WLQ9 WVM9 D65534 JA65534 SW65534 ACS65534 AMO65534 AWK65534 BGG65534 BQC65534 BZY65534 CJU65534 CTQ65534 DDM65534 DNI65534 DXE65534 EHA65534 EQW65534 FAS65534 FKO65534 FUK65534 GEG65534 GOC65534 GXY65534 HHU65534 HRQ65534 IBM65534 ILI65534 IVE65534 JFA65534 JOW65534 JYS65534 KIO65534 KSK65534 LCG65534 LMC65534 LVY65534 MFU65534 MPQ65534 MZM65534 NJI65534 NTE65534 ODA65534 OMW65534 OWS65534 PGO65534 PQK65534 QAG65534 QKC65534 QTY65534 RDU65534 RNQ65534 RXM65534 SHI65534 SRE65534 TBA65534 TKW65534 TUS65534 UEO65534 UOK65534 UYG65534 VIC65534 VRY65534 WBU65534 WLQ65534 WVM65534 D131070 JA131070 SW131070 ACS131070 AMO131070 AWK131070 BGG131070 BQC131070 BZY131070 CJU131070 CTQ131070 DDM131070 DNI131070 DXE131070 EHA131070 EQW131070 FAS131070 FKO131070 FUK131070 GEG131070 GOC131070 GXY131070 HHU131070 HRQ131070 IBM131070 ILI131070 IVE131070 JFA131070 JOW131070 JYS131070 KIO131070 KSK131070 LCG131070 LMC131070 LVY131070 MFU131070 MPQ131070 MZM131070 NJI131070 NTE131070 ODA131070 OMW131070 OWS131070 PGO131070 PQK131070 QAG131070 QKC131070 QTY131070 RDU131070 RNQ131070 RXM131070 SHI131070 SRE131070 TBA131070 TKW131070 TUS131070 UEO131070 UOK131070 UYG131070 VIC131070 VRY131070 WBU131070 WLQ131070 WVM131070 D196606 JA196606 SW196606 ACS196606 AMO196606 AWK196606 BGG196606 BQC196606 BZY196606 CJU196606 CTQ196606 DDM196606 DNI196606 DXE196606 EHA196606 EQW196606 FAS196606 FKO196606 FUK196606 GEG196606 GOC196606 GXY196606 HHU196606 HRQ196606 IBM196606 ILI196606 IVE196606 JFA196606 JOW196606 JYS196606 KIO196606 KSK196606 LCG196606 LMC196606 LVY196606 MFU196606 MPQ196606 MZM196606 NJI196606 NTE196606 ODA196606 OMW196606 OWS196606 PGO196606 PQK196606 QAG196606 QKC196606 QTY196606 RDU196606 RNQ196606 RXM196606 SHI196606 SRE196606 TBA196606 TKW196606 TUS196606 UEO196606 UOK196606 UYG196606 VIC196606 VRY196606 WBU196606 WLQ196606 WVM196606 D262142 JA262142 SW262142 ACS262142 AMO262142 AWK262142 BGG262142 BQC262142 BZY262142 CJU262142 CTQ262142 DDM262142 DNI262142 DXE262142 EHA262142 EQW262142 FAS262142 FKO262142 FUK262142 GEG262142 GOC262142 GXY262142 HHU262142 HRQ262142 IBM262142 ILI262142 IVE262142 JFA262142 JOW262142 JYS262142 KIO262142 KSK262142 LCG262142 LMC262142 LVY262142 MFU262142 MPQ262142 MZM262142 NJI262142 NTE262142 ODA262142 OMW262142 OWS262142 PGO262142 PQK262142 QAG262142 QKC262142 QTY262142 RDU262142 RNQ262142 RXM262142 SHI262142 SRE262142 TBA262142 TKW262142 TUS262142 UEO262142 UOK262142 UYG262142 VIC262142 VRY262142 WBU262142 WLQ262142 WVM262142 D327678 JA327678 SW327678 ACS327678 AMO327678 AWK327678 BGG327678 BQC327678 BZY327678 CJU327678 CTQ327678 DDM327678 DNI327678 DXE327678 EHA327678 EQW327678 FAS327678 FKO327678 FUK327678 GEG327678 GOC327678 GXY327678 HHU327678 HRQ327678 IBM327678 ILI327678 IVE327678 JFA327678 JOW327678 JYS327678 KIO327678 KSK327678 LCG327678 LMC327678 LVY327678 MFU327678 MPQ327678 MZM327678 NJI327678 NTE327678 ODA327678 OMW327678 OWS327678 PGO327678 PQK327678 QAG327678 QKC327678 QTY327678 RDU327678 RNQ327678 RXM327678 SHI327678 SRE327678 TBA327678 TKW327678 TUS327678 UEO327678 UOK327678 UYG327678 VIC327678 VRY327678 WBU327678 WLQ327678 WVM327678 D393214 JA393214 SW393214 ACS393214 AMO393214 AWK393214 BGG393214 BQC393214 BZY393214 CJU393214 CTQ393214 DDM393214 DNI393214 DXE393214 EHA393214 EQW393214 FAS393214 FKO393214 FUK393214 GEG393214 GOC393214 GXY393214 HHU393214 HRQ393214 IBM393214 ILI393214 IVE393214 JFA393214 JOW393214 JYS393214 KIO393214 KSK393214 LCG393214 LMC393214 LVY393214 MFU393214 MPQ393214 MZM393214 NJI393214 NTE393214 ODA393214 OMW393214 OWS393214 PGO393214 PQK393214 QAG393214 QKC393214 QTY393214 RDU393214 RNQ393214 RXM393214 SHI393214 SRE393214 TBA393214 TKW393214 TUS393214 UEO393214 UOK393214 UYG393214 VIC393214 VRY393214 WBU393214 WLQ393214 WVM393214 D458750 JA458750 SW458750 ACS458750 AMO458750 AWK458750 BGG458750 BQC458750 BZY458750 CJU458750 CTQ458750 DDM458750 DNI458750 DXE458750 EHA458750 EQW458750 FAS458750 FKO458750 FUK458750 GEG458750 GOC458750 GXY458750 HHU458750 HRQ458750 IBM458750 ILI458750 IVE458750 JFA458750 JOW458750 JYS458750 KIO458750 KSK458750 LCG458750 LMC458750 LVY458750 MFU458750 MPQ458750 MZM458750 NJI458750 NTE458750 ODA458750 OMW458750 OWS458750 PGO458750 PQK458750 QAG458750 QKC458750 QTY458750 RDU458750 RNQ458750 RXM458750 SHI458750 SRE458750 TBA458750 TKW458750 TUS458750 UEO458750 UOK458750 UYG458750 VIC458750 VRY458750 WBU458750 WLQ458750 WVM458750 D524286 JA524286 SW524286 ACS524286 AMO524286 AWK524286 BGG524286 BQC524286 BZY524286 CJU524286 CTQ524286 DDM524286 DNI524286 DXE524286 EHA524286 EQW524286 FAS524286 FKO524286 FUK524286 GEG524286 GOC524286 GXY524286 HHU524286 HRQ524286 IBM524286 ILI524286 IVE524286 JFA524286 JOW524286 JYS524286 KIO524286 KSK524286 LCG524286 LMC524286 LVY524286 MFU524286 MPQ524286 MZM524286 NJI524286 NTE524286 ODA524286 OMW524286 OWS524286 PGO524286 PQK524286 QAG524286 QKC524286 QTY524286 RDU524286 RNQ524286 RXM524286 SHI524286 SRE524286 TBA524286 TKW524286 TUS524286 UEO524286 UOK524286 UYG524286 VIC524286 VRY524286 WBU524286 WLQ524286 WVM524286 D589822 JA589822 SW589822 ACS589822 AMO589822 AWK589822 BGG589822 BQC589822 BZY589822 CJU589822 CTQ589822 DDM589822 DNI589822 DXE589822 EHA589822 EQW589822 FAS589822 FKO589822 FUK589822 GEG589822 GOC589822 GXY589822 HHU589822 HRQ589822 IBM589822 ILI589822 IVE589822 JFA589822 JOW589822 JYS589822 KIO589822 KSK589822 LCG589822 LMC589822 LVY589822 MFU589822 MPQ589822 MZM589822 NJI589822 NTE589822 ODA589822 OMW589822 OWS589822 PGO589822 PQK589822 QAG589822 QKC589822 QTY589822 RDU589822 RNQ589822 RXM589822 SHI589822 SRE589822 TBA589822 TKW589822 TUS589822 UEO589822 UOK589822 UYG589822 VIC589822 VRY589822 WBU589822 WLQ589822 WVM589822 D655358 JA655358 SW655358 ACS655358 AMO655358 AWK655358 BGG655358 BQC655358 BZY655358 CJU655358 CTQ655358 DDM655358 DNI655358 DXE655358 EHA655358 EQW655358 FAS655358 FKO655358 FUK655358 GEG655358 GOC655358 GXY655358 HHU655358 HRQ655358 IBM655358 ILI655358 IVE655358 JFA655358 JOW655358 JYS655358 KIO655358 KSK655358 LCG655358 LMC655358 LVY655358 MFU655358 MPQ655358 MZM655358 NJI655358 NTE655358 ODA655358 OMW655358 OWS655358 PGO655358 PQK655358 QAG655358 QKC655358 QTY655358 RDU655358 RNQ655358 RXM655358 SHI655358 SRE655358 TBA655358 TKW655358 TUS655358 UEO655358 UOK655358 UYG655358 VIC655358 VRY655358 WBU655358 WLQ655358 WVM655358 D720894 JA720894 SW720894 ACS720894 AMO720894 AWK720894 BGG720894 BQC720894 BZY720894 CJU720894 CTQ720894 DDM720894 DNI720894 DXE720894 EHA720894 EQW720894 FAS720894 FKO720894 FUK720894 GEG720894 GOC720894 GXY720894 HHU720894 HRQ720894 IBM720894 ILI720894 IVE720894 JFA720894 JOW720894 JYS720894 KIO720894 KSK720894 LCG720894 LMC720894 LVY720894 MFU720894 MPQ720894 MZM720894 NJI720894 NTE720894 ODA720894 OMW720894 OWS720894 PGO720894 PQK720894 QAG720894 QKC720894 QTY720894 RDU720894 RNQ720894 RXM720894 SHI720894 SRE720894 TBA720894 TKW720894 TUS720894 UEO720894 UOK720894 UYG720894 VIC720894 VRY720894 WBU720894 WLQ720894 WVM720894 D786430 JA786430 SW786430 ACS786430 AMO786430 AWK786430 BGG786430 BQC786430 BZY786430 CJU786430 CTQ786430 DDM786430 DNI786430 DXE786430 EHA786430 EQW786430 FAS786430 FKO786430 FUK786430 GEG786430 GOC786430 GXY786430 HHU786430 HRQ786430 IBM786430 ILI786430 IVE786430 JFA786430 JOW786430 JYS786430 KIO786430 KSK786430 LCG786430 LMC786430 LVY786430 MFU786430 MPQ786430 MZM786430 NJI786430 NTE786430 ODA786430 OMW786430 OWS786430 PGO786430 PQK786430 QAG786430 QKC786430 QTY786430 RDU786430 RNQ786430 RXM786430 SHI786430 SRE786430 TBA786430 TKW786430 TUS786430 UEO786430 UOK786430 UYG786430 VIC786430 VRY786430 WBU786430 WLQ786430 WVM786430 D851966 JA851966 SW851966 ACS851966 AMO851966 AWK851966 BGG851966 BQC851966 BZY851966 CJU851966 CTQ851966 DDM851966 DNI851966 DXE851966 EHA851966 EQW851966 FAS851966 FKO851966 FUK851966 GEG851966 GOC851966 GXY851966 HHU851966 HRQ851966 IBM851966 ILI851966 IVE851966 JFA851966 JOW851966 JYS851966 KIO851966 KSK851966 LCG851966 LMC851966 LVY851966 MFU851966 MPQ851966 MZM851966 NJI851966 NTE851966 ODA851966 OMW851966 OWS851966 PGO851966 PQK851966 QAG851966 QKC851966 QTY851966 RDU851966 RNQ851966 RXM851966 SHI851966 SRE851966 TBA851966 TKW851966 TUS851966 UEO851966 UOK851966 UYG851966 VIC851966 VRY851966 WBU851966 WLQ851966 WVM851966 D917502 JA917502 SW917502 ACS917502 AMO917502 AWK917502 BGG917502 BQC917502 BZY917502 CJU917502 CTQ917502 DDM917502 DNI917502 DXE917502 EHA917502 EQW917502 FAS917502 FKO917502 FUK917502 GEG917502 GOC917502 GXY917502 HHU917502 HRQ917502 IBM917502 ILI917502 IVE917502 JFA917502 JOW917502 JYS917502 KIO917502 KSK917502 LCG917502 LMC917502 LVY917502 MFU917502 MPQ917502 MZM917502 NJI917502 NTE917502 ODA917502 OMW917502 OWS917502 PGO917502 PQK917502 QAG917502 QKC917502 QTY917502 RDU917502 RNQ917502 RXM917502 SHI917502 SRE917502 TBA917502 TKW917502 TUS917502 UEO917502 UOK917502 UYG917502 VIC917502 VRY917502 WBU917502 WLQ917502 WVM917502 D983038 JA983038 SW983038 ACS983038 AMO983038 AWK983038 BGG983038 BQC983038 BZY983038 CJU983038 CTQ983038 DDM983038 DNI983038 DXE983038 EHA983038 EQW983038 FAS983038 FKO983038 FUK983038 GEG983038 GOC983038 GXY983038 HHU983038 HRQ983038 IBM983038 ILI983038 IVE983038 JFA983038 JOW983038 JYS983038 KIO983038 KSK983038 LCG983038 LMC983038 LVY983038 MFU983038 MPQ983038 MZM983038 NJI983038 NTE983038 ODA983038 OMW983038 OWS983038 PGO983038 PQK983038 QAG983038 QKC983038 QTY983038 RDU983038 RNQ983038 RXM983038 SHI983038 SRE983038 TBA983038 TKW983038 TUS983038 UEO983038 UOK983038 UYG983038 VIC983038 VRY983038 WBU983038 WLQ983038 WVM983038" xr:uid="{269021AE-3AF4-4D2A-A8C2-FDD27E11B385}">
+    <dataValidation sqref="D9 D65534 D131070 D196606 D262142 D327678 D393214 D458750 D524286 D589822 D655358 D720894 D786430 D851966 D917502 D983038 JA9 JA65534 JA131070 JA196606 JA262142 JA327678 JA393214 JA458750 JA524286 JA589822 JA655358 JA720894 JA786430 JA851966 JA917502 JA983038 SW9 SW65534 SW131070 SW196606 SW262142 SW327678 SW393214 SW458750 SW524286 SW589822 SW655358 SW720894 SW786430 SW851966 SW917502 SW983038 ACS9 ACS65534 ACS131070 ACS196606 ACS262142 ACS327678 ACS393214 ACS458750 ACS524286 ACS589822 ACS655358 ACS720894 ACS786430 ACS851966 ACS917502 ACS983038 AMO9 AMO65534 AMO131070 AMO196606 AMO262142 AMO327678 AMO393214 AMO458750 AMO524286 AMO589822 AMO655358 AMO720894 AMO786430 AMO851966 AMO917502 AMO983038 AWK9 AWK65534 AWK131070 AWK196606 AWK262142 AWK327678 AWK393214 AWK458750 AWK524286 AWK589822 AWK655358 AWK720894 AWK786430 AWK851966 AWK917502 AWK983038 BGG9 BGG65534 BGG131070 BGG196606 BGG262142 BGG327678 BGG393214 BGG458750 BGG524286 BGG589822 BGG655358 BGG720894 BGG786430 BGG851966 BGG917502 BGG983038 BQC9 BQC65534 BQC131070 BQC196606 BQC262142 BQC327678 BQC393214 BQC458750 BQC524286 BQC589822 BQC655358 BQC720894 BQC786430 BQC851966 BQC917502 BQC983038 BZY9 BZY65534 BZY131070 BZY196606 BZY262142 BZY327678 BZY393214 BZY458750 BZY524286 BZY589822 BZY655358 BZY720894 BZY786430 BZY851966 BZY917502 BZY983038 CJU9 CJU65534 CJU131070 CJU196606 CJU262142 CJU327678 CJU393214 CJU458750 CJU524286 CJU589822 CJU655358 CJU720894 CJU786430 CJU851966 CJU917502 CJU983038 CTQ9 CTQ65534 CTQ131070 CTQ196606 CTQ262142 CTQ327678 CTQ393214 CTQ458750 CTQ524286 CTQ589822 CTQ655358 CTQ720894 CTQ786430 CTQ851966 CTQ917502 CTQ983038 DDM9 DDM65534 DDM131070 DDM196606 DDM262142 DDM327678 DDM393214 DDM458750 DDM524286 DDM589822 DDM655358 DDM720894 DDM786430 DDM851966 DDM917502 DDM983038 DNI9 DNI65534 DNI131070 DNI196606 DNI262142 DNI327678 DNI393214 DNI458750 DNI524286 DNI589822 DNI655358 DNI720894 DNI786430 DNI851966 DNI917502 DNI983038 DXE9 DXE65534 DXE131070 DXE196606 DXE262142 DXE327678 DXE393214 DXE458750 DXE524286 DXE589822 DXE655358 DXE720894 DXE786430 DXE851966 DXE917502 DXE983038 EHA9 EHA65534 EHA131070 EHA196606 EHA262142 EHA327678 EHA393214 EHA458750 EHA524286 EHA589822 EHA655358 EHA720894 EHA786430 EHA851966 EHA917502 EHA983038 EQW9 EQW65534 EQW131070 EQW196606 EQW262142 EQW327678 EQW393214 EQW458750 EQW524286 EQW589822 EQW655358 EQW720894 EQW786430 EQW851966 EQW917502 EQW983038 FAS9 FAS65534 FAS131070 FAS196606 FAS262142 FAS327678 FAS393214 FAS458750 FAS524286 FAS589822 FAS655358 FAS720894 FAS786430 FAS851966 FAS917502 FAS983038 FKO9 FKO65534 FKO131070 FKO196606 FKO262142 FKO327678 FKO393214 FKO458750 FKO524286 FKO589822 FKO655358 FKO720894 FKO786430 FKO851966 FKO917502 FKO983038 FUK9 FUK65534 FUK131070 FUK196606 FUK262142 FUK327678 FUK393214 FUK458750 FUK524286 FUK589822 FUK655358 FUK720894 FUK786430 FUK851966 FUK917502 FUK983038 GEG9 GEG65534 GEG131070 GEG196606 GEG262142 GEG327678 GEG393214 GEG458750 GEG524286 GEG589822 GEG655358 GEG720894 GEG786430 GEG851966 GEG917502 GEG983038 GOC9 GOC65534 GOC131070 GOC196606 GOC262142 GOC327678 GOC393214 GOC458750 GOC524286 GOC589822 GOC655358 GOC720894 GOC786430 GOC851966 GOC917502 GOC983038 GXY9 GXY65534 GXY131070 GXY196606 GXY262142 GXY327678 GXY393214 GXY458750 GXY524286 GXY589822 GXY655358 GXY720894 GXY786430 GXY851966 GXY917502 GXY983038 HHU9 HHU65534 HHU131070 HHU196606 HHU262142 HHU327678 HHU393214 HHU458750 HHU524286 HHU589822 HHU655358 HHU720894 HHU786430 HHU851966 HHU917502 HHU983038 HRQ9 HRQ65534 HRQ131070 HRQ196606 HRQ262142 HRQ327678 HRQ393214 HRQ458750 HRQ524286 HRQ589822 HRQ655358 HRQ720894 HRQ786430 HRQ851966 HRQ917502 HRQ983038 IBM9 IBM65534 IBM131070 IBM196606 IBM262142 IBM327678 IBM393214 IBM458750 IBM524286 IBM589822 IBM655358 IBM720894 IBM786430 IBM851966 IBM917502 IBM983038 ILI9 ILI65534 ILI131070 ILI196606 ILI262142 ILI327678 ILI393214 ILI458750 ILI524286 ILI589822 ILI655358 ILI720894 ILI786430 ILI851966 ILI917502 ILI983038 IVE9 IVE65534 IVE131070 IVE196606 IVE262142 IVE327678 IVE393214 IVE458750 IVE524286 IVE589822 IVE655358 IVE720894 IVE786430 IVE851966 IVE917502 IVE983038 JFA9 JFA65534 JFA131070 JFA196606 JFA262142 JFA327678 JFA393214 JFA458750 JFA524286 JFA589822 JFA655358 JFA720894 JFA786430 JFA851966 JFA917502 JFA983038 JOW9 JOW65534 JOW131070 JOW196606 JOW262142 JOW327678 JOW393214 JOW458750 JOW524286 JOW589822 JOW655358 JOW720894 JOW786430 JOW851966 JOW917502 JOW983038 JYS9 JYS65534 JYS131070 JYS196606 JYS262142 JYS327678 JYS393214 JYS458750 JYS524286 JYS589822 JYS655358 JYS720894 JYS786430 JYS851966 JYS917502 JYS983038 KIO9 KIO65534 KIO131070 KIO196606 KIO262142 KIO327678 KIO393214 KIO458750 KIO524286 KIO589822 KIO655358 KIO720894 KIO786430 KIO851966 KIO917502 KIO983038 KSK9 KSK65534 KSK131070 KSK196606 KSK262142 KSK327678 KSK393214 KSK458750 KSK524286 KSK589822 KSK655358 KSK720894 KSK786430 KSK851966 KSK917502 KSK983038 LCG9 LCG65534 LCG131070 LCG196606 LCG262142 LCG327678 LCG393214 LCG458750 LCG524286 LCG589822 LCG655358 LCG720894 LCG786430 LCG851966 LCG917502 LCG983038 LMC9 LMC65534 LMC131070 LMC196606 LMC262142 LMC327678 LMC393214 LMC458750 LMC524286 LMC589822 LMC655358 LMC720894 LMC786430 LMC851966 LMC917502 LMC983038 LVY9 LVY65534 LVY131070 LVY196606 LVY262142 LVY327678 LVY393214 LVY458750 LVY524286 LVY589822 LVY655358 LVY720894 LVY786430 LVY851966 LVY917502 LVY983038 MFU9 MFU65534 MFU131070 MFU196606 MFU262142 MFU327678 MFU393214 MFU458750 MFU524286 MFU589822 MFU655358 MFU720894 MFU786430 MFU851966 MFU917502 MFU983038 MPQ9 MPQ65534 MPQ131070 MPQ196606 MPQ262142 MPQ327678 MPQ393214 MPQ458750 MPQ524286 MPQ589822 MPQ655358 MPQ720894 MPQ786430 MPQ851966 MPQ917502 MPQ983038 MZM9 MZM65534 MZM131070 MZM196606 MZM262142 MZM327678 MZM393214 MZM458750 MZM524286 MZM589822 MZM655358 MZM720894 MZM786430 MZM851966 MZM917502 MZM983038 NJI9 NJI65534 NJI131070 NJI196606 NJI262142 NJI327678 NJI393214 NJI458750 NJI524286 NJI589822 NJI655358 NJI720894 NJI786430 NJI851966 NJI917502 NJI983038 NTE9 NTE65534 NTE131070 NTE196606 NTE262142 NTE327678 NTE393214 NTE458750 NTE524286 NTE589822 NTE655358 NTE720894 NTE786430 NTE851966 NTE917502 NTE983038 ODA9 ODA65534 ODA131070 ODA196606 ODA262142 ODA327678 ODA393214 ODA458750 ODA524286 ODA589822 ODA655358 ODA720894 ODA786430 ODA851966 ODA917502 ODA983038 OMW9 OMW65534 OMW131070 OMW196606 OMW262142 OMW327678 OMW393214 OMW458750 OMW524286 OMW589822 OMW655358 OMW720894 OMW786430 OMW851966 OMW917502 OMW983038 OWS9 OWS65534 OWS131070 OWS196606 OWS262142 OWS327678 OWS393214 OWS458750 OWS524286 OWS589822 OWS655358 OWS720894 OWS786430 OWS851966 OWS917502 OWS983038 PGO9 PGO65534 PGO131070 PGO196606 PGO262142 PGO327678 PGO393214 PGO458750 PGO524286 PGO589822 PGO655358 PGO720894 PGO786430 PGO851966 PGO917502 PGO983038 PQK9 PQK65534 PQK131070 PQK196606 PQK262142 PQK327678 PQK393214 PQK458750 PQK524286 PQK589822 PQK655358 PQK720894 PQK786430 PQK851966 PQK917502 PQK983038 QAG9 QAG65534 QAG131070 QAG196606 QAG262142 QAG327678 QAG393214 QAG458750 QAG524286 QAG589822 QAG655358 QAG720894 QAG786430 QAG851966 QAG917502 QAG983038 QKC9 QKC65534 QKC131070 QKC196606 QKC262142 QKC327678 QKC393214 QKC458750 QKC524286 QKC589822 QKC655358 QKC720894 QKC786430 QKC851966 QKC917502 QKC983038 QTY9 QTY65534 QTY131070 QTY196606 QTY262142 QTY327678 QTY393214 QTY458750 QTY524286 QTY589822 QTY655358 QTY720894 QTY786430 QTY851966 QTY917502 QTY983038 RDU9 RDU65534 RDU131070 RDU196606 RDU262142 RDU327678 RDU393214 RDU458750 RDU524286 RDU589822 RDU655358 RDU720894 RDU786430 RDU851966 RDU917502 RDU983038 RNQ9 RNQ65534 RNQ131070 RNQ196606 RNQ262142 RNQ327678 RNQ393214 RNQ458750 RNQ524286 RNQ589822 RNQ655358 RNQ720894 RNQ786430 RNQ851966 RNQ917502 RNQ983038 RXM9 RXM65534 RXM131070 RXM196606 RXM262142 RXM327678 RXM393214 RXM458750 RXM524286 RXM589822 RXM655358 RXM720894 RXM786430 RXM851966 RXM917502 RXM983038 SHI9 SHI65534 SHI131070 SHI196606 SHI262142 SHI327678 SHI393214 SHI458750 SHI524286 SHI589822 SHI655358 SHI720894 SHI786430 SHI851966 SHI917502 SHI983038 SRE9 SRE65534 SRE131070 SRE196606 SRE262142 SRE327678 SRE393214 SRE458750 SRE524286 SRE589822 SRE655358 SRE720894 SRE786430 SRE851966 SRE917502 SRE983038 TBA9 TBA65534 TBA131070 TBA196606 TBA262142 TBA327678 TBA393214 TBA458750 TBA524286 TBA589822 TBA655358 TBA720894 TBA786430 TBA851966 TBA917502 TBA983038 TKW9 TKW65534 TKW131070 TKW196606 TKW262142 TKW327678 TKW393214 TKW458750 TKW524286 TKW589822 TKW655358 TKW720894 TKW786430 TKW851966 TKW917502 TKW983038 TUS9 TUS65534 TUS131070 TUS196606 TUS262142 TUS327678 TUS393214 TUS458750 TUS524286 TUS589822 TUS655358 TUS720894 TUS786430 TUS851966 TUS917502 TUS983038 UEO9 UEO65534 UEO131070 UEO196606 UEO262142 UEO327678 UEO393214 UEO458750 UEO524286 UEO589822 UEO655358 UEO720894 UEO786430 UEO851966 UEO917502 UEO983038 UOK9 UOK65534 UOK131070 UOK196606 UOK262142 UOK327678 UOK393214 UOK458750 UOK524286 UOK589822 UOK655358 UOK720894 UOK786430 UOK851966 UOK917502 UOK983038 UYG9 UYG65534 UYG131070 UYG196606 UYG262142 UYG327678 UYG393214 UYG458750 UYG524286 UYG589822 UYG655358 UYG720894 UYG786430 UYG851966 UYG917502 UYG983038 VIC9 VIC65534 VIC131070 VIC196606 VIC262142 VIC327678 VIC393214 VIC458750 VIC524286 VIC589822 VIC655358 VIC720894 VIC786430 VIC851966 VIC917502 VIC983038 VRY9 VRY65534 VRY131070 VRY196606 VRY262142 VRY327678 VRY393214 VRY458750 VRY524286 VRY589822 VRY655358 VRY720894 VRY786430 VRY851966 VRY917502 VRY983038 WBU9 WBU65534 WBU131070 WBU196606 WBU262142 WBU327678 WBU393214 WBU458750 WBU524286 WBU589822 WBU655358 WBU720894 WBU786430 WBU851966 WBU917502 WBU983038 WLQ9 WLQ65534 WLQ131070 WLQ196606 WLQ262142 WLQ327678 WLQ393214 WLQ458750 WLQ524286 WLQ589822 WLQ655358 WLQ720894 WLQ786430 WLQ851966 WLQ917502 WLQ983038 WVM9 WVM65534 WVM131070 WVM196606 WVM262142 WVM327678 WVM393214 WVM458750 WVM524286 WVM589822 WVM655358 WVM720894 WVM786430 WVM851966 WVM917502 WVM983038" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Hướng dẫn sử dụng" prompt="____________________x000a__x000a_Lựa chọn đơn vị tiền tệ" type="list">
       <formula1>"VND,USD,EUR,JPY,CNY,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hướng dẫn sử dụng" prompt="____________________x000a__x000a_Lựa chọn Bộ phận " sqref="D7 JA7 SW7 ACS7 AMO7 AWK7 BGG7 BQC7 BZY7 CJU7 CTQ7 DDM7 DNI7 DXE7 EHA7 EQW7 FAS7 FKO7 FUK7 GEG7 GOC7 GXY7 HHU7 HRQ7 IBM7 ILI7 IVE7 JFA7 JOW7 JYS7 KIO7 KSK7 LCG7 LMC7 LVY7 MFU7 MPQ7 MZM7 NJI7 NTE7 ODA7 OMW7 OWS7 PGO7 PQK7 QAG7 QKC7 QTY7 RDU7 RNQ7 RXM7 SHI7 SRE7 TBA7 TKW7 TUS7 UEO7 UOK7 UYG7 VIC7 VRY7 WBU7 WLQ7 WVM7 D65532 JA65532 SW65532 ACS65532 AMO65532 AWK65532 BGG65532 BQC65532 BZY65532 CJU65532 CTQ65532 DDM65532 DNI65532 DXE65532 EHA65532 EQW65532 FAS65532 FKO65532 FUK65532 GEG65532 GOC65532 GXY65532 HHU65532 HRQ65532 IBM65532 ILI65532 IVE65532 JFA65532 JOW65532 JYS65532 KIO65532 KSK65532 LCG65532 LMC65532 LVY65532 MFU65532 MPQ65532 MZM65532 NJI65532 NTE65532 ODA65532 OMW65532 OWS65532 PGO65532 PQK65532 QAG65532 QKC65532 QTY65532 RDU65532 RNQ65532 RXM65532 SHI65532 SRE65532 TBA65532 TKW65532 TUS65532 UEO65532 UOK65532 UYG65532 VIC65532 VRY65532 WBU65532 WLQ65532 WVM65532 D131068 JA131068 SW131068 ACS131068 AMO131068 AWK131068 BGG131068 BQC131068 BZY131068 CJU131068 CTQ131068 DDM131068 DNI131068 DXE131068 EHA131068 EQW131068 FAS131068 FKO131068 FUK131068 GEG131068 GOC131068 GXY131068 HHU131068 HRQ131068 IBM131068 ILI131068 IVE131068 JFA131068 JOW131068 JYS131068 KIO131068 KSK131068 LCG131068 LMC131068 LVY131068 MFU131068 MPQ131068 MZM131068 NJI131068 NTE131068 ODA131068 OMW131068 OWS131068 PGO131068 PQK131068 QAG131068 QKC131068 QTY131068 RDU131068 RNQ131068 RXM131068 SHI131068 SRE131068 TBA131068 TKW131068 TUS131068 UEO131068 UOK131068 UYG131068 VIC131068 VRY131068 WBU131068 WLQ131068 WVM131068 D196604 JA196604 SW196604 ACS196604 AMO196604 AWK196604 BGG196604 BQC196604 BZY196604 CJU196604 CTQ196604 DDM196604 DNI196604 DXE196604 EHA196604 EQW196604 FAS196604 FKO196604 FUK196604 GEG196604 GOC196604 GXY196604 HHU196604 HRQ196604 IBM196604 ILI196604 IVE196604 JFA196604 JOW196604 JYS196604 KIO196604 KSK196604 LCG196604 LMC196604 LVY196604 MFU196604 MPQ196604 MZM196604 NJI196604 NTE196604 ODA196604 OMW196604 OWS196604 PGO196604 PQK196604 QAG196604 QKC196604 QTY196604 RDU196604 RNQ196604 RXM196604 SHI196604 SRE196604 TBA196604 TKW196604 TUS196604 UEO196604 UOK196604 UYG196604 VIC196604 VRY196604 WBU196604 WLQ196604 WVM196604 D262140 JA262140 SW262140 ACS262140 AMO262140 AWK262140 BGG262140 BQC262140 BZY262140 CJU262140 CTQ262140 DDM262140 DNI262140 DXE262140 EHA262140 EQW262140 FAS262140 FKO262140 FUK262140 GEG262140 GOC262140 GXY262140 HHU262140 HRQ262140 IBM262140 ILI262140 IVE262140 JFA262140 JOW262140 JYS262140 KIO262140 KSK262140 LCG262140 LMC262140 LVY262140 MFU262140 MPQ262140 MZM262140 NJI262140 NTE262140 ODA262140 OMW262140 OWS262140 PGO262140 PQK262140 QAG262140 QKC262140 QTY262140 RDU262140 RNQ262140 RXM262140 SHI262140 SRE262140 TBA262140 TKW262140 TUS262140 UEO262140 UOK262140 UYG262140 VIC262140 VRY262140 WBU262140 WLQ262140 WVM262140 D327676 JA327676 SW327676 ACS327676 AMO327676 AWK327676 BGG327676 BQC327676 BZY327676 CJU327676 CTQ327676 DDM327676 DNI327676 DXE327676 EHA327676 EQW327676 FAS327676 FKO327676 FUK327676 GEG327676 GOC327676 GXY327676 HHU327676 HRQ327676 IBM327676 ILI327676 IVE327676 JFA327676 JOW327676 JYS327676 KIO327676 KSK327676 LCG327676 LMC327676 LVY327676 MFU327676 MPQ327676 MZM327676 NJI327676 NTE327676 ODA327676 OMW327676 OWS327676 PGO327676 PQK327676 QAG327676 QKC327676 QTY327676 RDU327676 RNQ327676 RXM327676 SHI327676 SRE327676 TBA327676 TKW327676 TUS327676 UEO327676 UOK327676 UYG327676 VIC327676 VRY327676 WBU327676 WLQ327676 WVM327676 D393212 JA393212 SW393212 ACS393212 AMO393212 AWK393212 BGG393212 BQC393212 BZY393212 CJU393212 CTQ393212 DDM393212 DNI393212 DXE393212 EHA393212 EQW393212 FAS393212 FKO393212 FUK393212 GEG393212 GOC393212 GXY393212 HHU393212 HRQ393212 IBM393212 ILI393212 IVE393212 JFA393212 JOW393212 JYS393212 KIO393212 KSK393212 LCG393212 LMC393212 LVY393212 MFU393212 MPQ393212 MZM393212 NJI393212 NTE393212 ODA393212 OMW393212 OWS393212 PGO393212 PQK393212 QAG393212 QKC393212 QTY393212 RDU393212 RNQ393212 RXM393212 SHI393212 SRE393212 TBA393212 TKW393212 TUS393212 UEO393212 UOK393212 UYG393212 VIC393212 VRY393212 WBU393212 WLQ393212 WVM393212 D458748 JA458748 SW458748 ACS458748 AMO458748 AWK458748 BGG458748 BQC458748 BZY458748 CJU458748 CTQ458748 DDM458748 DNI458748 DXE458748 EHA458748 EQW458748 FAS458748 FKO458748 FUK458748 GEG458748 GOC458748 GXY458748 HHU458748 HRQ458748 IBM458748 ILI458748 IVE458748 JFA458748 JOW458748 JYS458748 KIO458748 KSK458748 LCG458748 LMC458748 LVY458748 MFU458748 MPQ458748 MZM458748 NJI458748 NTE458748 ODA458748 OMW458748 OWS458748 PGO458748 PQK458748 QAG458748 QKC458748 QTY458748 RDU458748 RNQ458748 RXM458748 SHI458748 SRE458748 TBA458748 TKW458748 TUS458748 UEO458748 UOK458748 UYG458748 VIC458748 VRY458748 WBU458748 WLQ458748 WVM458748 D524284 JA524284 SW524284 ACS524284 AMO524284 AWK524284 BGG524284 BQC524284 BZY524284 CJU524284 CTQ524284 DDM524284 DNI524284 DXE524284 EHA524284 EQW524284 FAS524284 FKO524284 FUK524284 GEG524284 GOC524284 GXY524284 HHU524284 HRQ524284 IBM524284 ILI524284 IVE524284 JFA524284 JOW524284 JYS524284 KIO524284 KSK524284 LCG524284 LMC524284 LVY524284 MFU524284 MPQ524284 MZM524284 NJI524284 NTE524284 ODA524284 OMW524284 OWS524284 PGO524284 PQK524284 QAG524284 QKC524284 QTY524284 RDU524284 RNQ524284 RXM524284 SHI524284 SRE524284 TBA524284 TKW524284 TUS524284 UEO524284 UOK524284 UYG524284 VIC524284 VRY524284 WBU524284 WLQ524284 WVM524284 D589820 JA589820 SW589820 ACS589820 AMO589820 AWK589820 BGG589820 BQC589820 BZY589820 CJU589820 CTQ589820 DDM589820 DNI589820 DXE589820 EHA589820 EQW589820 FAS589820 FKO589820 FUK589820 GEG589820 GOC589820 GXY589820 HHU589820 HRQ589820 IBM589820 ILI589820 IVE589820 JFA589820 JOW589820 JYS589820 KIO589820 KSK589820 LCG589820 LMC589820 LVY589820 MFU589820 MPQ589820 MZM589820 NJI589820 NTE589820 ODA589820 OMW589820 OWS589820 PGO589820 PQK589820 QAG589820 QKC589820 QTY589820 RDU589820 RNQ589820 RXM589820 SHI589820 SRE589820 TBA589820 TKW589820 TUS589820 UEO589820 UOK589820 UYG589820 VIC589820 VRY589820 WBU589820 WLQ589820 WVM589820 D655356 JA655356 SW655356 ACS655356 AMO655356 AWK655356 BGG655356 BQC655356 BZY655356 CJU655356 CTQ655356 DDM655356 DNI655356 DXE655356 EHA655356 EQW655356 FAS655356 FKO655356 FUK655356 GEG655356 GOC655356 GXY655356 HHU655356 HRQ655356 IBM655356 ILI655356 IVE655356 JFA655356 JOW655356 JYS655356 KIO655356 KSK655356 LCG655356 LMC655356 LVY655356 MFU655356 MPQ655356 MZM655356 NJI655356 NTE655356 ODA655356 OMW655356 OWS655356 PGO655356 PQK655356 QAG655356 QKC655356 QTY655356 RDU655356 RNQ655356 RXM655356 SHI655356 SRE655356 TBA655356 TKW655356 TUS655356 UEO655356 UOK655356 UYG655356 VIC655356 VRY655356 WBU655356 WLQ655356 WVM655356 D720892 JA720892 SW720892 ACS720892 AMO720892 AWK720892 BGG720892 BQC720892 BZY720892 CJU720892 CTQ720892 DDM720892 DNI720892 DXE720892 EHA720892 EQW720892 FAS720892 FKO720892 FUK720892 GEG720892 GOC720892 GXY720892 HHU720892 HRQ720892 IBM720892 ILI720892 IVE720892 JFA720892 JOW720892 JYS720892 KIO720892 KSK720892 LCG720892 LMC720892 LVY720892 MFU720892 MPQ720892 MZM720892 NJI720892 NTE720892 ODA720892 OMW720892 OWS720892 PGO720892 PQK720892 QAG720892 QKC720892 QTY720892 RDU720892 RNQ720892 RXM720892 SHI720892 SRE720892 TBA720892 TKW720892 TUS720892 UEO720892 UOK720892 UYG720892 VIC720892 VRY720892 WBU720892 WLQ720892 WVM720892 D786428 JA786428 SW786428 ACS786428 AMO786428 AWK786428 BGG786428 BQC786428 BZY786428 CJU786428 CTQ786428 DDM786428 DNI786428 DXE786428 EHA786428 EQW786428 FAS786428 FKO786428 FUK786428 GEG786428 GOC786428 GXY786428 HHU786428 HRQ786428 IBM786428 ILI786428 IVE786428 JFA786428 JOW786428 JYS786428 KIO786428 KSK786428 LCG786428 LMC786428 LVY786428 MFU786428 MPQ786428 MZM786428 NJI786428 NTE786428 ODA786428 OMW786428 OWS786428 PGO786428 PQK786428 QAG786428 QKC786428 QTY786428 RDU786428 RNQ786428 RXM786428 SHI786428 SRE786428 TBA786428 TKW786428 TUS786428 UEO786428 UOK786428 UYG786428 VIC786428 VRY786428 WBU786428 WLQ786428 WVM786428 D851964 JA851964 SW851964 ACS851964 AMO851964 AWK851964 BGG851964 BQC851964 BZY851964 CJU851964 CTQ851964 DDM851964 DNI851964 DXE851964 EHA851964 EQW851964 FAS851964 FKO851964 FUK851964 GEG851964 GOC851964 GXY851964 HHU851964 HRQ851964 IBM851964 ILI851964 IVE851964 JFA851964 JOW851964 JYS851964 KIO851964 KSK851964 LCG851964 LMC851964 LVY851964 MFU851964 MPQ851964 MZM851964 NJI851964 NTE851964 ODA851964 OMW851964 OWS851964 PGO851964 PQK851964 QAG851964 QKC851964 QTY851964 RDU851964 RNQ851964 RXM851964 SHI851964 SRE851964 TBA851964 TKW851964 TUS851964 UEO851964 UOK851964 UYG851964 VIC851964 VRY851964 WBU851964 WLQ851964 WVM851964 D917500 JA917500 SW917500 ACS917500 AMO917500 AWK917500 BGG917500 BQC917500 BZY917500 CJU917500 CTQ917500 DDM917500 DNI917500 DXE917500 EHA917500 EQW917500 FAS917500 FKO917500 FUK917500 GEG917500 GOC917500 GXY917500 HHU917500 HRQ917500 IBM917500 ILI917500 IVE917500 JFA917500 JOW917500 JYS917500 KIO917500 KSK917500 LCG917500 LMC917500 LVY917500 MFU917500 MPQ917500 MZM917500 NJI917500 NTE917500 ODA917500 OMW917500 OWS917500 PGO917500 PQK917500 QAG917500 QKC917500 QTY917500 RDU917500 RNQ917500 RXM917500 SHI917500 SRE917500 TBA917500 TKW917500 TUS917500 UEO917500 UOK917500 UYG917500 VIC917500 VRY917500 WBU917500 WLQ917500 WVM917500 D983036 JA983036 SW983036 ACS983036 AMO983036 AWK983036 BGG983036 BQC983036 BZY983036 CJU983036 CTQ983036 DDM983036 DNI983036 DXE983036 EHA983036 EQW983036 FAS983036 FKO983036 FUK983036 GEG983036 GOC983036 GXY983036 HHU983036 HRQ983036 IBM983036 ILI983036 IVE983036 JFA983036 JOW983036 JYS983036 KIO983036 KSK983036 LCG983036 LMC983036 LVY983036 MFU983036 MPQ983036 MZM983036 NJI983036 NTE983036 ODA983036 OMW983036 OWS983036 PGO983036 PQK983036 QAG983036 QKC983036 QTY983036 RDU983036 RNQ983036 RXM983036 SHI983036 SRE983036 TBA983036 TKW983036 TUS983036 UEO983036 UOK983036 UYG983036 VIC983036 VRY983036 WBU983036 WLQ983036 WVM983036" xr:uid="{57998CC8-A4B8-4D2E-93A1-4D128F341CD1}">
+    <dataValidation sqref="D7 D65532 D131068 D196604 D262140 D327676 D393212 D458748 D524284 D589820 D655356 D720892 D786428 D851964 D917500 D983036 JA7 JA65532 JA131068 JA196604 JA262140 JA327676 JA393212 JA458748 JA524284 JA589820 JA655356 JA720892 JA786428 JA851964 JA917500 JA983036 SW7 SW65532 SW131068 SW196604 SW262140 SW327676 SW393212 SW458748 SW524284 SW589820 SW655356 SW720892 SW786428 SW851964 SW917500 SW983036 ACS7 ACS65532 ACS131068 ACS196604 ACS262140 ACS327676 ACS393212 ACS458748 ACS524284 ACS589820 ACS655356 ACS720892 ACS786428 ACS851964 ACS917500 ACS983036 AMO7 AMO65532 AMO131068 AMO196604 AMO262140 AMO327676 AMO393212 AMO458748 AMO524284 AMO589820 AMO655356 AMO720892 AMO786428 AMO851964 AMO917500 AMO983036 AWK7 AWK65532 AWK131068 AWK196604 AWK262140 AWK327676 AWK393212 AWK458748 AWK524284 AWK589820 AWK655356 AWK720892 AWK786428 AWK851964 AWK917500 AWK983036 BGG7 BGG65532 BGG131068 BGG196604 BGG262140 BGG327676 BGG393212 BGG458748 BGG524284 BGG589820 BGG655356 BGG720892 BGG786428 BGG851964 BGG917500 BGG983036 BQC7 BQC65532 BQC131068 BQC196604 BQC262140 BQC327676 BQC393212 BQC458748 BQC524284 BQC589820 BQC655356 BQC720892 BQC786428 BQC851964 BQC917500 BQC983036 BZY7 BZY65532 BZY131068 BZY196604 BZY262140 BZY327676 BZY393212 BZY458748 BZY524284 BZY589820 BZY655356 BZY720892 BZY786428 BZY851964 BZY917500 BZY983036 CJU7 CJU65532 CJU131068 CJU196604 CJU262140 CJU327676 CJU393212 CJU458748 CJU524284 CJU589820 CJU655356 CJU720892 CJU786428 CJU851964 CJU917500 CJU983036 CTQ7 CTQ65532 CTQ131068 CTQ196604 CTQ262140 CTQ327676 CTQ393212 CTQ458748 CTQ524284 CTQ589820 CTQ655356 CTQ720892 CTQ786428 CTQ851964 CTQ917500 CTQ983036 DDM7 DDM65532 DDM131068 DDM196604 DDM262140 DDM327676 DDM393212 DDM458748 DDM524284 DDM589820 DDM655356 DDM720892 DDM786428 DDM851964 DDM917500 DDM983036 DNI7 DNI65532 DNI131068 DNI196604 DNI262140 DNI327676 DNI393212 DNI458748 DNI524284 DNI589820 DNI655356 DNI720892 DNI786428 DNI851964 DNI917500 DNI983036 DXE7 DXE65532 DXE131068 DXE196604 DXE262140 DXE327676 DXE393212 DXE458748 DXE524284 DXE589820 DXE655356 DXE720892 DXE786428 DXE851964 DXE917500 DXE983036 EHA7 EHA65532 EHA131068 EHA196604 EHA262140 EHA327676 EHA393212 EHA458748 EHA524284 EHA589820 EHA655356 EHA720892 EHA786428 EHA851964 EHA917500 EHA983036 EQW7 EQW65532 EQW131068 EQW196604 EQW262140 EQW327676 EQW393212 EQW458748 EQW524284 EQW589820 EQW655356 EQW720892 EQW786428 EQW851964 EQW917500 EQW983036 FAS7 FAS65532 FAS131068 FAS196604 FAS262140 FAS327676 FAS393212 FAS458748 FAS524284 FAS589820 FAS655356 FAS720892 FAS786428 FAS851964 FAS917500 FAS983036 FKO7 FKO65532 FKO131068 FKO196604 FKO262140 FKO327676 FKO393212 FKO458748 FKO524284 FKO589820 FKO655356 FKO720892 FKO786428 FKO851964 FKO917500 FKO983036 FUK7 FUK65532 FUK131068 FUK196604 FUK262140 FUK327676 FUK393212 FUK458748 FUK524284 FUK589820 FUK655356 FUK720892 FUK786428 FUK851964 FUK917500 FUK983036 GEG7 GEG65532 GEG131068 GEG196604 GEG262140 GEG327676 GEG393212 GEG458748 GEG524284 GEG589820 GEG655356 GEG720892 GEG786428 GEG851964 GEG917500 GEG983036 GOC7 GOC65532 GOC131068 GOC196604 GOC262140 GOC327676 GOC393212 GOC458748 GOC524284 GOC589820 GOC655356 GOC720892 GOC786428 GOC851964 GOC917500 GOC983036 GXY7 GXY65532 GXY131068 GXY196604 GXY262140 GXY327676 GXY393212 GXY458748 GXY524284 GXY589820 GXY655356 GXY720892 GXY786428 GXY851964 GXY917500 GXY983036 HHU7 HHU65532 HHU131068 HHU196604 HHU262140 HHU327676 HHU393212 HHU458748 HHU524284 HHU589820 HHU655356 HHU720892 HHU786428 HHU851964 HHU917500 HHU983036 HRQ7 HRQ65532 HRQ131068 HRQ196604 HRQ262140 HRQ327676 HRQ393212 HRQ458748 HRQ524284 HRQ589820 HRQ655356 HRQ720892 HRQ786428 HRQ851964 HRQ917500 HRQ983036 IBM7 IBM65532 IBM131068 IBM196604 IBM262140 IBM327676 IBM393212 IBM458748 IBM524284 IBM589820 IBM655356 IBM720892 IBM786428 IBM851964 IBM917500 IBM983036 ILI7 ILI65532 ILI131068 ILI196604 ILI262140 ILI327676 ILI393212 ILI458748 ILI524284 ILI589820 ILI655356 ILI720892 ILI786428 ILI851964 ILI917500 ILI983036 IVE7 IVE65532 IVE131068 IVE196604 IVE262140 IVE327676 IVE393212 IVE458748 IVE524284 IVE589820 IVE655356 IVE720892 IVE786428 IVE851964 IVE917500 IVE983036 JFA7 JFA65532 JFA131068 JFA196604 JFA262140 JFA327676 JFA393212 JFA458748 JFA524284 JFA589820 JFA655356 JFA720892 JFA786428 JFA851964 JFA917500 JFA983036 JOW7 JOW65532 JOW131068 JOW196604 JOW262140 JOW327676 JOW393212 JOW458748 JOW524284 JOW589820 JOW655356 JOW720892 JOW786428 JOW851964 JOW917500 JOW983036 JYS7 JYS65532 JYS131068 JYS196604 JYS262140 JYS327676 JYS393212 JYS458748 JYS524284 JYS589820 JYS655356 JYS720892 JYS786428 JYS851964 JYS917500 JYS983036 KIO7 KIO65532 KIO131068 KIO196604 KIO262140 KIO327676 KIO393212 KIO458748 KIO524284 KIO589820 KIO655356 KIO720892 KIO786428 KIO851964 KIO917500 KIO983036 KSK7 KSK65532 KSK131068 KSK196604 KSK262140 KSK327676 KSK393212 KSK458748 KSK524284 KSK589820 KSK655356 KSK720892 KSK786428 KSK851964 KSK917500 KSK983036 LCG7 LCG65532 LCG131068 LCG196604 LCG262140 LCG327676 LCG393212 LCG458748 LCG524284 LCG589820 LCG655356 LCG720892 LCG786428 LCG851964 LCG917500 LCG983036 LMC7 LMC65532 LMC131068 LMC196604 LMC262140 LMC327676 LMC393212 LMC458748 LMC524284 LMC589820 LMC655356 LMC720892 LMC786428 LMC851964 LMC917500 LMC983036 LVY7 LVY65532 LVY131068 LVY196604 LVY262140 LVY327676 LVY393212 LVY458748 LVY524284 LVY589820 LVY655356 LVY720892 LVY786428 LVY851964 LVY917500 LVY983036 MFU7 MFU65532 MFU131068 MFU196604 MFU262140 MFU327676 MFU393212 MFU458748 MFU524284 MFU589820 MFU655356 MFU720892 MFU786428 MFU851964 MFU917500 MFU983036 MPQ7 MPQ65532 MPQ131068 MPQ196604 MPQ262140 MPQ327676 MPQ393212 MPQ458748 MPQ524284 MPQ589820 MPQ655356 MPQ720892 MPQ786428 MPQ851964 MPQ917500 MPQ983036 MZM7 MZM65532 MZM131068 MZM196604 MZM262140 MZM327676 MZM393212 MZM458748 MZM524284 MZM589820 MZM655356 MZM720892 MZM786428 MZM851964 MZM917500 MZM983036 NJI7 NJI65532 NJI131068 NJI196604 NJI262140 NJI327676 NJI393212 NJI458748 NJI524284 NJI589820 NJI655356 NJI720892 NJI786428 NJI851964 NJI917500 NJI983036 NTE7 NTE65532 NTE131068 NTE196604 NTE262140 NTE327676 NTE393212 NTE458748 NTE524284 NTE589820 NTE655356 NTE720892 NTE786428 NTE851964 NTE917500 NTE983036 ODA7 ODA65532 ODA131068 ODA196604 ODA262140 ODA327676 ODA393212 ODA458748 ODA524284 ODA589820 ODA655356 ODA720892 ODA786428 ODA851964 ODA917500 ODA983036 OMW7 OMW65532 OMW131068 OMW196604 OMW262140 OMW327676 OMW393212 OMW458748 OMW524284 OMW589820 OMW655356 OMW720892 OMW786428 OMW851964 OMW917500 OMW983036 OWS7 OWS65532 OWS131068 OWS196604 OWS262140 OWS327676 OWS393212 OWS458748 OWS524284 OWS589820 OWS655356 OWS720892 OWS786428 OWS851964 OWS917500 OWS983036 PGO7 PGO65532 PGO131068 PGO196604 PGO262140 PGO327676 PGO393212 PGO458748 PGO524284 PGO589820 PGO655356 PGO720892 PGO786428 PGO851964 PGO917500 PGO983036 PQK7 PQK65532 PQK131068 PQK196604 PQK262140 PQK327676 PQK393212 PQK458748 PQK524284 PQK589820 PQK655356 PQK720892 PQK786428 PQK851964 PQK917500 PQK983036 QAG7 QAG65532 QAG131068 QAG196604 QAG262140 QAG327676 QAG393212 QAG458748 QAG524284 QAG589820 QAG655356 QAG720892 QAG786428 QAG851964 QAG917500 QAG983036 QKC7 QKC65532 QKC131068 QKC196604 QKC262140 QKC327676 QKC393212 QKC458748 QKC524284 QKC589820 QKC655356 QKC720892 QKC786428 QKC851964 QKC917500 QKC983036 QTY7 QTY65532 QTY131068 QTY196604 QTY262140 QTY327676 QTY393212 QTY458748 QTY524284 QTY589820 QTY655356 QTY720892 QTY786428 QTY851964 QTY917500 QTY983036 RDU7 RDU65532 RDU131068 RDU196604 RDU262140 RDU327676 RDU393212 RDU458748 RDU524284 RDU589820 RDU655356 RDU720892 RDU786428 RDU851964 RDU917500 RDU983036 RNQ7 RNQ65532 RNQ131068 RNQ196604 RNQ262140 RNQ327676 RNQ393212 RNQ458748 RNQ524284 RNQ589820 RNQ655356 RNQ720892 RNQ786428 RNQ851964 RNQ917500 RNQ983036 RXM7 RXM65532 RXM131068 RXM196604 RXM262140 RXM327676 RXM393212 RXM458748 RXM524284 RXM589820 RXM655356 RXM720892 RXM786428 RXM851964 RXM917500 RXM983036 SHI7 SHI65532 SHI131068 SHI196604 SHI262140 SHI327676 SHI393212 SHI458748 SHI524284 SHI589820 SHI655356 SHI720892 SHI786428 SHI851964 SHI917500 SHI983036 SRE7 SRE65532 SRE131068 SRE196604 SRE262140 SRE327676 SRE393212 SRE458748 SRE524284 SRE589820 SRE655356 SRE720892 SRE786428 SRE851964 SRE917500 SRE983036 TBA7 TBA65532 TBA131068 TBA196604 TBA262140 TBA327676 TBA393212 TBA458748 TBA524284 TBA589820 TBA655356 TBA720892 TBA786428 TBA851964 TBA917500 TBA983036 TKW7 TKW65532 TKW131068 TKW196604 TKW262140 TKW327676 TKW393212 TKW458748 TKW524284 TKW589820 TKW655356 TKW720892 TKW786428 TKW851964 TKW917500 TKW983036 TUS7 TUS65532 TUS131068 TUS196604 TUS262140 TUS327676 TUS393212 TUS458748 TUS524284 TUS589820 TUS655356 TUS720892 TUS786428 TUS851964 TUS917500 TUS983036 UEO7 UEO65532 UEO131068 UEO196604 UEO262140 UEO327676 UEO393212 UEO458748 UEO524284 UEO589820 UEO655356 UEO720892 UEO786428 UEO851964 UEO917500 UEO983036 UOK7 UOK65532 UOK131068 UOK196604 UOK262140 UOK327676 UOK393212 UOK458748 UOK524284 UOK589820 UOK655356 UOK720892 UOK786428 UOK851964 UOK917500 UOK983036 UYG7 UYG65532 UYG131068 UYG196604 UYG262140 UYG327676 UYG393212 UYG458748 UYG524284 UYG589820 UYG655356 UYG720892 UYG786428 UYG851964 UYG917500 UYG983036 VIC7 VIC65532 VIC131068 VIC196604 VIC262140 VIC327676 VIC393212 VIC458748 VIC524284 VIC589820 VIC655356 VIC720892 VIC786428 VIC851964 VIC917500 VIC983036 VRY7 VRY65532 VRY131068 VRY196604 VRY262140 VRY327676 VRY393212 VRY458748 VRY524284 VRY589820 VRY655356 VRY720892 VRY786428 VRY851964 VRY917500 VRY983036 WBU7 WBU65532 WBU131068 WBU196604 WBU262140 WBU327676 WBU393212 WBU458748 WBU524284 WBU589820 WBU655356 WBU720892 WBU786428 WBU851964 WBU917500 WBU983036 WLQ7 WLQ65532 WLQ131068 WLQ196604 WLQ262140 WLQ327676 WLQ393212 WLQ458748 WLQ524284 WLQ589820 WLQ655356 WLQ720892 WLQ786428 WLQ851964 WLQ917500 WLQ983036 WVM7 WVM65532 WVM131068 WVM196604 WVM262140 WVM327676 WVM393212 WVM458748 WVM524284 WVM589820 WVM655356 WVM720892 WVM786428 WVM851964 WVM917500 WVM983036" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Hướng dẫn sử dụng" prompt="____________________x000a__x000a_Lựa chọn Bộ phận " type="list">
       <formula1>"HĐQT,Ban giám đốc,Tổ chức-hành chính,Tài chính-Kế toán,Phát triển DA,Ban quản lý DA,Trạm trộn BT, Kế hoạch-Vật tư"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="95" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="95" verticalDpi="0"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/public/templates/yctt_template.xlsx
+++ b/public/templates/yctt_template.xlsx
@@ -987,23 +987,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Author</author>
-  </authors>
-  <commentList>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">Author:
-Bấm vào đây để thay đổi số thứ tự in chứng từ
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12189,6 +12172,5 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="95" verticalDpi="0"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>